--- a/public/reports/weekly_briefing/2026-09-21.xlsx
+++ b/public/reports/weekly_briefing/2026-09-21.xlsx
@@ -22,15 +22,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="6">
     <numFmt numFmtId="164" formatCode="+0.0&quot;%&quot;;-0.0&quot;%&quot;;0.0&quot;%&quot;"/>
     <numFmt numFmtId="165" formatCode="+0;-0;0"/>
     <numFmt numFmtId="166" formatCode="+#,##0;-#,##0;0"/>
     <numFmt numFmtId="167" formatCode="+#,##0.0;-#,##0.0;0.0"/>
     <numFmt numFmtId="168" formatCode="+0.00;-0.00;0"/>
-    <numFmt numFmtId="169" formatCode="0.000"/>
-    <numFmt numFmtId="170" formatCode="#,##0.0"/>
-    <numFmt numFmtId="171" formatCode="+0.00;-0.00;0.00"/>
+    <numFmt numFmtId="169" formatCode="+0.00;-0.00;0.00"/>
   </numFmts>
   <fonts count="31">
     <font>
@@ -336,7 +334,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="78">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -526,22 +524,16 @@
     <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="2" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="27" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="25" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="24" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="23" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -559,7 +551,7 @@
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="169" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -8782,15 +8774,15 @@
     <col width="16" customWidth="1" style="15" min="8" max="8"/>
     <col width="12.5" customWidth="1" style="15" min="9" max="9"/>
     <col width="10.5" customWidth="1" style="15" min="10" max="10"/>
-    <col width="10" customWidth="1" style="15" min="11" max="11"/>
-    <col width="9" customWidth="1" style="15" min="12" max="12"/>
+    <col width="12.5" customWidth="1" style="15" min="11" max="11"/>
+    <col width="10.5" customWidth="1" style="15" min="12" max="12"/>
     <col width="2" customWidth="1" style="15" min="13" max="13"/>
     <col width="4.5" customWidth="1" style="15" min="14" max="14"/>
     <col width="16" customWidth="1" style="15" min="15" max="15"/>
     <col width="12.5" customWidth="1" style="15" min="16" max="16"/>
     <col width="10.5" customWidth="1" style="15" min="17" max="17"/>
-    <col width="10" customWidth="1" style="15" min="18" max="18"/>
-    <col width="9" customWidth="1" style="15" min="19" max="19"/>
+    <col width="12.5" customWidth="1" style="15" min="18" max="18"/>
+    <col width="10.5" customWidth="1" style="15" min="19" max="19"/>
   </cols>
   <sheetData>
     <row r="1" ht="20.25" customHeight="1" s="15">
@@ -8876,7 +8868,7 @@
       </c>
       <c r="K4" s="46" t="inlineStr">
         <is>
-          <t>잔고(억)</t>
+          <t>대차잔고(억)</t>
         </is>
       </c>
       <c r="L4" s="46" t="inlineStr">
@@ -8906,7 +8898,7 @@
       </c>
       <c r="R4" s="46" t="inlineStr">
         <is>
-          <t>잔고(억)</t>
+          <t>대차잔고(억)</t>
         </is>
       </c>
       <c r="S4" s="46" t="inlineStr">
@@ -8944,13 +8936,13 @@
         </is>
       </c>
       <c r="I5" s="35" t="inlineStr"/>
-      <c r="J5" s="50" t="n">
+      <c r="J5" s="48" t="n">
         <v>2179.8</v>
       </c>
       <c r="K5" s="66" t="n">
         <v>29995.7</v>
       </c>
-      <c r="L5" s="67" t="n">
+      <c r="L5" s="65" t="n">
         <v>1.78</v>
       </c>
       <c r="N5" s="30" t="n">
@@ -8966,13 +8958,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q5" s="68" t="n">
+      <c r="Q5" s="62" t="n">
         <v>-11175.8</v>
       </c>
       <c r="R5" s="66" t="n">
         <v>208999.9</v>
       </c>
-      <c r="S5" s="67" t="n">
+      <c r="S5" s="65" t="n">
         <v>1.53</v>
       </c>
     </row>
@@ -8994,7 +8986,7 @@
         <v>1136</v>
       </c>
       <c r="E6" s="65" t="n">
-        <v>0.007</v>
+        <v>0.01</v>
       </c>
       <c r="G6" s="30" t="n">
         <v>2</v>
@@ -9009,13 +9001,13 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="J6" s="50" t="n">
+      <c r="J6" s="48" t="n">
         <v>1243.3</v>
       </c>
       <c r="K6" s="66" t="n">
         <v>30455.7</v>
       </c>
-      <c r="L6" s="67" t="n">
+      <c r="L6" s="65" t="n">
         <v>2.05</v>
       </c>
       <c r="N6" s="30" t="n">
@@ -9031,13 +9023,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q6" s="68" t="n">
+      <c r="Q6" s="62" t="n">
         <v>-1020.2</v>
       </c>
       <c r="R6" s="66" t="n">
         <v>31793.9</v>
       </c>
-      <c r="S6" s="67" t="n">
+      <c r="S6" s="65" t="n">
         <v>3.86</v>
       </c>
     </row>
@@ -9059,7 +9051,7 @@
         <v>941</v>
       </c>
       <c r="E7" s="65" t="n">
-        <v>0.172</v>
+        <v>0.17</v>
       </c>
       <c r="G7" s="30" t="n">
         <v>3</v>
@@ -9074,13 +9066,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J7" s="50" t="n">
+      <c r="J7" s="48" t="n">
         <v>1128.2</v>
       </c>
       <c r="K7" s="66" t="n">
         <v>240805.1</v>
       </c>
-      <c r="L7" s="67" t="n">
+      <c r="L7" s="65" t="n">
         <v>1.5</v>
       </c>
       <c r="N7" s="30" t="n">
@@ -9092,13 +9084,13 @@
         </is>
       </c>
       <c r="P7" s="35" t="inlineStr"/>
-      <c r="Q7" s="68" t="n">
+      <c r="Q7" s="62" t="n">
         <v>-910.3</v>
       </c>
       <c r="R7" s="66" t="n">
         <v>28648.3</v>
       </c>
-      <c r="S7" s="67" t="n">
+      <c r="S7" s="65" t="n">
         <v>3.92</v>
       </c>
     </row>
@@ -9116,7 +9108,7 @@
         <v>775</v>
       </c>
       <c r="E8" s="65" t="n">
-        <v>0.106</v>
+        <v>0.11</v>
       </c>
       <c r="G8" s="30" t="n">
         <v>4</v>
@@ -9131,13 +9123,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J8" s="50" t="n">
+      <c r="J8" s="48" t="n">
         <v>995.5</v>
       </c>
       <c r="K8" s="66" t="n">
         <v>35178.7</v>
       </c>
-      <c r="L8" s="67" t="n">
+      <c r="L8" s="65" t="n">
         <v>3.3</v>
       </c>
       <c r="N8" s="30" t="n">
@@ -9153,13 +9145,13 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="Q8" s="68" t="n">
+      <c r="Q8" s="62" t="n">
         <v>-439.5</v>
       </c>
       <c r="R8" s="66" t="n">
         <v>28937.4</v>
       </c>
-      <c r="S8" s="67" t="n">
+      <c r="S8" s="65" t="n">
         <v>6.12</v>
       </c>
     </row>
@@ -9196,13 +9188,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J9" s="50" t="n">
+      <c r="J9" s="48" t="n">
         <v>746.1</v>
       </c>
       <c r="K9" s="66" t="n">
         <v>8289.5</v>
       </c>
-      <c r="L9" s="67" t="n">
+      <c r="L9" s="65" t="n">
         <v>16.48</v>
       </c>
       <c r="N9" s="30" t="n">
@@ -9218,13 +9210,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q9" s="68" t="n">
+      <c r="Q9" s="62" t="n">
         <v>-416.3</v>
       </c>
       <c r="R9" s="66" t="n">
         <v>13137.9</v>
       </c>
-      <c r="S9" s="67" t="n">
+      <c r="S9" s="65" t="n">
         <v>8.289999999999999</v>
       </c>
     </row>
@@ -9246,7 +9238,7 @@
         <v>507</v>
       </c>
       <c r="E10" s="65" t="n">
-        <v>0.034</v>
+        <v>0.03</v>
       </c>
       <c r="G10" s="30" t="n">
         <v>6</v>
@@ -9261,13 +9253,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J10" s="50" t="n">
+      <c r="J10" s="48" t="n">
         <v>704.9</v>
       </c>
       <c r="K10" s="66" t="n">
         <v>5952.1</v>
       </c>
-      <c r="L10" s="67" t="n">
+      <c r="L10" s="65" t="n">
         <v>7.35</v>
       </c>
       <c r="N10" s="30" t="n">
@@ -9283,13 +9275,13 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="Q10" s="68" t="n">
+      <c r="Q10" s="62" t="n">
         <v>-217</v>
       </c>
       <c r="R10" s="66" t="n">
         <v>667.6</v>
       </c>
-      <c r="S10" s="67" t="n">
+      <c r="S10" s="65" t="n">
         <v>11.24</v>
       </c>
     </row>
@@ -9311,7 +9303,7 @@
         <v>402</v>
       </c>
       <c r="E11" s="65" t="n">
-        <v>0.049</v>
+        <v>0.05</v>
       </c>
       <c r="G11" s="30" t="n">
         <v>7</v>
@@ -9326,13 +9318,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J11" s="50" t="n">
+      <c r="J11" s="48" t="n">
         <v>646.9</v>
       </c>
       <c r="K11" s="66" t="n">
         <v>8494.6</v>
       </c>
-      <c r="L11" s="67" t="n">
+      <c r="L11" s="65" t="n">
         <v>3.66</v>
       </c>
       <c r="N11" s="30" t="n">
@@ -9348,13 +9340,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q11" s="68" t="n">
+      <c r="Q11" s="62" t="n">
         <v>-197.1</v>
       </c>
       <c r="R11" s="66" t="n">
         <v>6111</v>
       </c>
-      <c r="S11" s="67" t="n">
+      <c r="S11" s="65" t="n">
         <v>13.97</v>
       </c>
     </row>
@@ -9376,7 +9368,7 @@
         <v>397</v>
       </c>
       <c r="E12" s="65" t="n">
-        <v>0.626</v>
+        <v>0.63</v>
       </c>
       <c r="G12" s="30" t="n">
         <v>8</v>
@@ -9391,13 +9383,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="50" t="n">
+      <c r="J12" s="48" t="n">
         <v>587.4</v>
       </c>
       <c r="K12" s="66" t="n">
         <v>10110.4</v>
       </c>
-      <c r="L12" s="67" t="n">
+      <c r="L12" s="65" t="n">
         <v>15.97</v>
       </c>
       <c r="N12" s="30" t="n">
@@ -9413,13 +9405,13 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="Q12" s="68" t="n">
+      <c r="Q12" s="62" t="n">
         <v>-188.3</v>
       </c>
       <c r="R12" s="66" t="n">
         <v>5343.7</v>
       </c>
-      <c r="S12" s="67" t="n">
+      <c r="S12" s="65" t="n">
         <v>7.11</v>
       </c>
     </row>
@@ -9441,7 +9433,7 @@
         <v>341</v>
       </c>
       <c r="E13" s="65" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="G13" s="30" t="n">
         <v>9</v>
@@ -9456,13 +9448,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="50" t="n">
+      <c r="J13" s="48" t="n">
         <v>577.5</v>
       </c>
       <c r="K13" s="66" t="n">
         <v>12285.4</v>
       </c>
-      <c r="L13" s="67" t="n">
+      <c r="L13" s="65" t="n">
         <v>12.15</v>
       </c>
       <c r="N13" s="30" t="n">
@@ -9478,13 +9470,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="Q13" s="68" t="n">
+      <c r="Q13" s="62" t="n">
         <v>-187.9</v>
       </c>
       <c r="R13" s="66" t="n">
         <v>13002.5</v>
       </c>
-      <c r="S13" s="67" t="n">
+      <c r="S13" s="65" t="n">
         <v>3.03</v>
       </c>
     </row>
@@ -9506,7 +9498,7 @@
         <v>299</v>
       </c>
       <c r="E14" s="65" t="n">
-        <v>0.244</v>
+        <v>0.24</v>
       </c>
       <c r="G14" s="30" t="n">
         <v>10</v>
@@ -9521,13 +9513,13 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J14" s="50" t="n">
+      <c r="J14" s="48" t="n">
         <v>542.3</v>
       </c>
       <c r="K14" s="66" t="n">
         <v>8074.2</v>
       </c>
-      <c r="L14" s="67" t="n">
+      <c r="L14" s="65" t="n">
         <v>13.54</v>
       </c>
       <c r="N14" s="30" t="n">
@@ -9543,13 +9535,13 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="Q14" s="68" t="n">
+      <c r="Q14" s="62" t="n">
         <v>-173</v>
       </c>
       <c r="R14" s="66" t="n">
         <v>6242.2</v>
       </c>
-      <c r="S14" s="67" t="n">
+      <c r="S14" s="65" t="n">
         <v>3.91</v>
       </c>
     </row>
@@ -9730,43 +9722,43 @@
           <t>의료·정밀기기</t>
         </is>
       </c>
-      <c r="B5" s="69" t="n">
+      <c r="B5" s="67" t="n">
         <v>21.13</v>
       </c>
-      <c r="C5" s="70" t="n">
+      <c r="C5" s="68" t="n">
         <v>-3.99</v>
       </c>
-      <c r="D5" s="69" t="n">
+      <c r="D5" s="67" t="n">
         <v>21.21</v>
       </c>
-      <c r="E5" s="69" t="n">
+      <c r="E5" s="67" t="n">
         <v>6.29</v>
       </c>
-      <c r="F5" s="71" t="n">
+      <c r="F5" s="69" t="n">
         <v>24</v>
       </c>
-      <c r="G5" s="71" t="n">
+      <c r="G5" s="69" t="n">
         <v>230</v>
       </c>
-      <c r="H5" s="71" t="n">
+      <c r="H5" s="69" t="n">
         <v>255</v>
       </c>
-      <c r="I5" s="71" t="n">
+      <c r="I5" s="69" t="n">
         <v>43</v>
       </c>
-      <c r="J5" s="71" t="n">
+      <c r="J5" s="69" t="n">
         <v>118</v>
       </c>
-      <c r="K5" s="71" t="n">
+      <c r="K5" s="69" t="n">
         <v>56</v>
       </c>
-      <c r="L5" s="71" t="n">
+      <c r="L5" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="M5" s="72" t="n">
+      <c r="M5" s="70" t="n">
         <v>-242</v>
       </c>
-      <c r="N5" s="72" t="n">
+      <c r="N5" s="70" t="n">
         <v>-13</v>
       </c>
       <c r="O5" s="60" t="inlineStr">
@@ -9781,43 +9773,43 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="B6" s="69" t="n">
+      <c r="B6" s="67" t="n">
         <v>16.22</v>
       </c>
-      <c r="C6" s="70" t="n">
+      <c r="C6" s="68" t="n">
         <v>-21.35</v>
       </c>
-      <c r="D6" s="70" t="n">
+      <c r="D6" s="68" t="n">
         <v>-3.12</v>
       </c>
-      <c r="E6" s="69" t="n">
+      <c r="E6" s="67" t="n">
         <v>2.72</v>
       </c>
-      <c r="F6" s="71" t="n">
+      <c r="F6" s="69" t="n">
         <v>128</v>
       </c>
-      <c r="G6" s="71" t="n">
+      <c r="G6" s="69" t="n">
         <v>222</v>
       </c>
-      <c r="H6" s="71" t="n">
+      <c r="H6" s="69" t="n">
         <v>350</v>
       </c>
-      <c r="I6" s="71" t="n">
+      <c r="I6" s="69" t="n">
         <v>74</v>
       </c>
-      <c r="J6" s="71" t="n">
+      <c r="J6" s="69" t="n">
         <v>43</v>
       </c>
-      <c r="K6" s="71" t="n">
+      <c r="K6" s="69" t="n">
         <v>53</v>
       </c>
-      <c r="L6" s="71" t="n">
+      <c r="L6" s="69" t="n">
         <v>31</v>
       </c>
-      <c r="M6" s="72" t="n">
+      <c r="M6" s="70" t="n">
         <v>-352</v>
       </c>
-      <c r="N6" s="71" t="n">
+      <c r="N6" s="69" t="n">
         <v>2</v>
       </c>
       <c r="O6" s="30" t="inlineStr"/>
@@ -9828,43 +9820,43 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="B7" s="69" t="n">
+      <c r="B7" s="67" t="n">
         <v>122.14</v>
       </c>
-      <c r="C7" s="70" t="n">
+      <c r="C7" s="68" t="n">
         <v>-28.1</v>
       </c>
-      <c r="D7" s="69" t="n">
+      <c r="D7" s="67" t="n">
         <v>3.05</v>
       </c>
-      <c r="E7" s="69" t="n">
+      <c r="E7" s="67" t="n">
         <v>2.51</v>
       </c>
-      <c r="F7" s="71" t="n">
+      <c r="F7" s="69" t="n">
         <v>4877</v>
       </c>
-      <c r="G7" s="71" t="n">
+      <c r="G7" s="69" t="n">
         <v>13836</v>
       </c>
-      <c r="H7" s="71" t="n">
+      <c r="H7" s="69" t="n">
         <v>18714</v>
       </c>
-      <c r="I7" s="71" t="n">
+      <c r="I7" s="69" t="n">
         <v>10592</v>
       </c>
-      <c r="J7" s="71" t="n">
+      <c r="J7" s="69" t="n">
         <v>4484</v>
       </c>
-      <c r="K7" s="72" t="n">
+      <c r="K7" s="70" t="n">
         <v>-1535</v>
       </c>
-      <c r="L7" s="71" t="n">
+      <c r="L7" s="69" t="n">
         <v>247</v>
       </c>
-      <c r="M7" s="72" t="n">
+      <c r="M7" s="70" t="n">
         <v>-51286</v>
       </c>
-      <c r="N7" s="71" t="n">
+      <c r="N7" s="69" t="n">
         <v>32573</v>
       </c>
       <c r="O7" s="60" t="inlineStr">
@@ -9879,43 +9871,43 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="B8" s="69" t="n">
+      <c r="B8" s="67" t="n">
         <v>10.99</v>
       </c>
-      <c r="C8" s="69" t="n">
+      <c r="C8" s="67" t="n">
         <v>6.6</v>
       </c>
-      <c r="D8" s="69" t="n">
+      <c r="D8" s="67" t="n">
         <v>4.36</v>
       </c>
-      <c r="E8" s="69" t="n">
+      <c r="E8" s="67" t="n">
         <v>2.37</v>
       </c>
-      <c r="F8" s="71" t="n">
+      <c r="F8" s="69" t="n">
         <v>712</v>
       </c>
-      <c r="G8" s="71" t="n">
+      <c r="G8" s="69" t="n">
         <v>445</v>
       </c>
-      <c r="H8" s="71" t="n">
+      <c r="H8" s="69" t="n">
         <v>1157</v>
       </c>
-      <c r="I8" s="71" t="n">
+      <c r="I8" s="69" t="n">
         <v>231</v>
       </c>
-      <c r="J8" s="71" t="n">
+      <c r="J8" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="K8" s="71" t="n">
+      <c r="K8" s="69" t="n">
         <v>196</v>
       </c>
-      <c r="L8" s="71" t="n">
+      <c r="L8" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="M8" s="72" t="n">
+      <c r="M8" s="70" t="n">
         <v>-1146</v>
       </c>
-      <c r="N8" s="72" t="n">
+      <c r="N8" s="70" t="n">
         <v>-10</v>
       </c>
       <c r="O8" s="60" t="inlineStr">
@@ -9930,43 +9922,43 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="B9" s="69" t="n">
+      <c r="B9" s="67" t="n">
         <v>44.44</v>
       </c>
-      <c r="C9" s="70" t="n">
+      <c r="C9" s="68" t="n">
         <v>-15.68</v>
       </c>
-      <c r="D9" s="69" t="n">
+      <c r="D9" s="67" t="n">
         <v>1.28</v>
       </c>
-      <c r="E9" s="69" t="n">
+      <c r="E9" s="67" t="n">
         <v>2.2</v>
       </c>
-      <c r="F9" s="71" t="n">
+      <c r="F9" s="69" t="n">
         <v>611</v>
       </c>
-      <c r="G9" s="71" t="n">
+      <c r="G9" s="69" t="n">
         <v>1820</v>
       </c>
-      <c r="H9" s="71" t="n">
+      <c r="H9" s="69" t="n">
         <v>2431</v>
       </c>
-      <c r="I9" s="71" t="n">
+      <c r="I9" s="69" t="n">
         <v>1826</v>
       </c>
-      <c r="J9" s="72" t="n">
+      <c r="J9" s="70" t="n">
         <v>-162</v>
       </c>
-      <c r="K9" s="72" t="n">
+      <c r="K9" s="70" t="n">
         <v>-281</v>
       </c>
-      <c r="L9" s="71" t="n">
+      <c r="L9" s="69" t="n">
         <v>23</v>
       </c>
-      <c r="M9" s="72" t="n">
+      <c r="M9" s="70" t="n">
         <v>-2500</v>
       </c>
-      <c r="N9" s="71" t="n">
+      <c r="N9" s="69" t="n">
         <v>69</v>
       </c>
       <c r="O9" s="60" t="inlineStr">
@@ -9981,43 +9973,43 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="B10" s="69" t="n">
+      <c r="B10" s="67" t="n">
         <v>28.65</v>
       </c>
-      <c r="C10" s="70" t="n">
+      <c r="C10" s="68" t="n">
         <v>-22.79</v>
       </c>
-      <c r="D10" s="70" t="n">
+      <c r="D10" s="68" t="n">
         <v>-3.52</v>
       </c>
-      <c r="E10" s="69" t="n">
+      <c r="E10" s="67" t="n">
         <v>2.11</v>
       </c>
-      <c r="F10" s="72" t="n">
+      <c r="F10" s="70" t="n">
         <v>-498</v>
       </c>
-      <c r="G10" s="71" t="n">
+      <c r="G10" s="69" t="n">
         <v>146</v>
       </c>
-      <c r="H10" s="72" t="n">
+      <c r="H10" s="70" t="n">
         <v>-352</v>
       </c>
-      <c r="I10" s="71" t="n">
+      <c r="I10" s="69" t="n">
         <v>121</v>
       </c>
-      <c r="J10" s="71" t="n">
+      <c r="J10" s="69" t="n">
         <v>33</v>
       </c>
-      <c r="K10" s="72" t="n">
+      <c r="K10" s="70" t="n">
         <v>-1</v>
       </c>
-      <c r="L10" s="72" t="n">
+      <c r="L10" s="70" t="n">
         <v>-8</v>
       </c>
-      <c r="M10" s="71" t="n">
+      <c r="M10" s="69" t="n">
         <v>131</v>
       </c>
-      <c r="N10" s="71" t="n">
+      <c r="N10" s="69" t="n">
         <v>221</v>
       </c>
       <c r="O10" s="30" t="inlineStr"/>
@@ -10028,46 +10020,46 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="B11" s="70" t="n">
+      <c r="B11" s="68" t="n">
         <v>-11.8</v>
       </c>
-      <c r="C11" s="70" t="n">
+      <c r="C11" s="68" t="n">
         <v>-10.13</v>
       </c>
-      <c r="D11" s="70" t="n">
+      <c r="D11" s="68" t="n">
         <v>-6.43</v>
       </c>
-      <c r="E11" s="69" t="n">
+      <c r="E11" s="67" t="n">
         <v>1.91</v>
       </c>
-      <c r="F11" s="71" t="n">
+      <c r="F11" s="69" t="n">
         <v>587</v>
       </c>
-      <c r="G11" s="72" t="n">
+      <c r="G11" s="70" t="n">
         <v>-146</v>
       </c>
-      <c r="H11" s="71" t="n">
+      <c r="H11" s="69" t="n">
         <v>441</v>
       </c>
-      <c r="I11" s="71" t="n">
+      <c r="I11" s="69" t="n">
         <v>251</v>
       </c>
-      <c r="J11" s="72" t="n">
+      <c r="J11" s="70" t="n">
         <v>-224</v>
       </c>
-      <c r="K11" s="72" t="n">
+      <c r="K11" s="70" t="n">
         <v>-138</v>
       </c>
-      <c r="L11" s="72" t="n">
+      <c r="L11" s="70" t="n">
         <v>-38</v>
       </c>
-      <c r="M11" s="72" t="n">
+      <c r="M11" s="70" t="n">
         <v>-437</v>
       </c>
-      <c r="N11" s="72" t="n">
+      <c r="N11" s="70" t="n">
         <v>-3</v>
       </c>
-      <c r="O11" s="73" t="inlineStr">
+      <c r="O11" s="71" t="inlineStr">
         <is>
           <t>수급유입</t>
         </is>
@@ -10079,43 +10071,43 @@
           <t>제조</t>
         </is>
       </c>
-      <c r="B12" s="69" t="n">
+      <c r="B12" s="67" t="n">
         <v>77.28</v>
       </c>
-      <c r="C12" s="70" t="n">
+      <c r="C12" s="68" t="n">
         <v>-25.39</v>
       </c>
-      <c r="D12" s="69" t="n">
+      <c r="D12" s="67" t="n">
         <v>1.79</v>
       </c>
-      <c r="E12" s="69" t="n">
+      <c r="E12" s="67" t="n">
         <v>1.78</v>
       </c>
-      <c r="F12" s="71" t="n">
+      <c r="F12" s="69" t="n">
         <v>734</v>
       </c>
-      <c r="G12" s="71" t="n">
+      <c r="G12" s="69" t="n">
         <v>11861</v>
       </c>
-      <c r="H12" s="71" t="n">
+      <c r="H12" s="69" t="n">
         <v>12595</v>
       </c>
-      <c r="I12" s="71" t="n">
+      <c r="I12" s="69" t="n">
         <v>12144</v>
       </c>
-      <c r="J12" s="71" t="n">
+      <c r="J12" s="69" t="n">
         <v>2353</v>
       </c>
-      <c r="K12" s="72" t="n">
+      <c r="K12" s="70" t="n">
         <v>-2686</v>
       </c>
-      <c r="L12" s="71" t="n">
+      <c r="L12" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="M12" s="72" t="n">
+      <c r="M12" s="70" t="n">
         <v>-45408</v>
       </c>
-      <c r="N12" s="71" t="n">
+      <c r="N12" s="69" t="n">
         <v>32813</v>
       </c>
       <c r="O12" s="60" t="inlineStr">
@@ -10130,46 +10122,46 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="B13" s="69" t="n">
+      <c r="B13" s="67" t="n">
         <v>80.48</v>
       </c>
-      <c r="C13" s="69" t="n">
+      <c r="C13" s="67" t="n">
         <v>2.43</v>
       </c>
-      <c r="D13" s="69" t="n">
+      <c r="D13" s="67" t="n">
         <v>15.18</v>
       </c>
-      <c r="E13" s="69" t="n">
+      <c r="E13" s="67" t="n">
         <v>1.5</v>
       </c>
-      <c r="F13" s="72" t="n">
+      <c r="F13" s="70" t="n">
         <v>-677</v>
       </c>
-      <c r="G13" s="71" t="n">
+      <c r="G13" s="69" t="n">
         <v>170</v>
       </c>
-      <c r="H13" s="72" t="n">
+      <c r="H13" s="70" t="n">
         <v>-507</v>
       </c>
-      <c r="I13" s="72" t="n">
+      <c r="I13" s="70" t="n">
         <v>-5</v>
       </c>
-      <c r="J13" s="71" t="n">
+      <c r="J13" s="69" t="n">
         <v>10</v>
       </c>
-      <c r="K13" s="71" t="n">
+      <c r="K13" s="69" t="n">
         <v>159</v>
       </c>
-      <c r="L13" s="71" t="n">
+      <c r="L13" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="M13" s="71" t="n">
+      <c r="M13" s="69" t="n">
         <v>478</v>
       </c>
-      <c r="N13" s="71" t="n">
+      <c r="N13" s="69" t="n">
         <v>29</v>
       </c>
-      <c r="O13" s="74" t="inlineStr">
+      <c r="O13" s="72" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10181,43 +10173,43 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="B14" s="69" t="n">
+      <c r="B14" s="67" t="n">
         <v>56.78</v>
       </c>
-      <c r="C14" s="70" t="n">
+      <c r="C14" s="68" t="n">
         <v>-19.36</v>
       </c>
-      <c r="D14" s="70" t="n">
+      <c r="D14" s="68" t="n">
         <v>-6.23</v>
       </c>
-      <c r="E14" s="69" t="n">
+      <c r="E14" s="67" t="n">
         <v>1.27</v>
       </c>
-      <c r="F14" s="72" t="n">
+      <c r="F14" s="70" t="n">
         <v>-42</v>
       </c>
-      <c r="G14" s="71" t="n">
+      <c r="G14" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="H14" s="72" t="n">
+      <c r="H14" s="70" t="n">
         <v>-31</v>
       </c>
-      <c r="I14" s="71" t="n">
+      <c r="I14" s="69" t="n">
         <v>333</v>
       </c>
-      <c r="J14" s="72" t="n">
+      <c r="J14" s="70" t="n">
         <v>-119</v>
       </c>
-      <c r="K14" s="72" t="n">
+      <c r="K14" s="70" t="n">
         <v>-171</v>
       </c>
-      <c r="L14" s="72" t="n">
+      <c r="L14" s="70" t="n">
         <v>-22</v>
       </c>
-      <c r="M14" s="72" t="n">
+      <c r="M14" s="70" t="n">
         <v>-15</v>
       </c>
-      <c r="N14" s="71" t="n">
+      <c r="N14" s="69" t="n">
         <v>45</v>
       </c>
       <c r="O14" s="30" t="inlineStr"/>
@@ -10228,43 +10220,43 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="B15" s="70" t="n">
+      <c r="B15" s="68" t="n">
         <v>-9.84</v>
       </c>
-      <c r="C15" s="69" t="n">
+      <c r="C15" s="67" t="n">
         <v>3.05</v>
       </c>
-      <c r="D15" s="69" t="n">
+      <c r="D15" s="67" t="n">
         <v>0.25</v>
       </c>
-      <c r="E15" s="69" t="n">
+      <c r="E15" s="67" t="n">
         <v>1.05</v>
       </c>
-      <c r="F15" s="72" t="n">
+      <c r="F15" s="70" t="n">
         <v>-23</v>
       </c>
-      <c r="G15" s="71" t="n">
+      <c r="G15" s="69" t="n">
         <v>44</v>
       </c>
-      <c r="H15" s="71" t="n">
+      <c r="H15" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="I15" s="71" t="n">
+      <c r="I15" s="69" t="n">
         <v>46</v>
       </c>
-      <c r="J15" s="72" t="n">
+      <c r="J15" s="70" t="n">
         <v>-10</v>
       </c>
-      <c r="K15" s="71" t="n">
+      <c r="K15" s="69" t="n">
         <v>12</v>
       </c>
-      <c r="L15" s="72" t="n">
+      <c r="L15" s="70" t="n">
         <v>-5</v>
       </c>
-      <c r="M15" s="72" t="n">
+      <c r="M15" s="70" t="n">
         <v>-16</v>
       </c>
-      <c r="N15" s="72" t="n">
+      <c r="N15" s="70" t="n">
         <v>-5</v>
       </c>
       <c r="O15" s="60" t="inlineStr">
@@ -10279,46 +10271,46 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="B16" s="69" t="n">
+      <c r="B16" s="67" t="n">
         <v>16.02</v>
       </c>
-      <c r="C16" s="70" t="n">
+      <c r="C16" s="68" t="n">
         <v>-12.44</v>
       </c>
-      <c r="D16" s="69" t="n">
+      <c r="D16" s="67" t="n">
         <v>13.18</v>
       </c>
-      <c r="E16" s="69" t="n">
+      <c r="E16" s="67" t="n">
         <v>0.86</v>
       </c>
-      <c r="F16" s="72" t="n">
+      <c r="F16" s="70" t="n">
         <v>-969</v>
       </c>
-      <c r="G16" s="72" t="n">
+      <c r="G16" s="70" t="n">
         <v>-326</v>
       </c>
-      <c r="H16" s="72" t="n">
+      <c r="H16" s="70" t="n">
         <v>-1295</v>
       </c>
-      <c r="I16" s="71" t="n">
+      <c r="I16" s="69" t="n">
         <v>65</v>
       </c>
-      <c r="J16" s="72" t="n">
+      <c r="J16" s="70" t="n">
         <v>-336</v>
       </c>
-      <c r="K16" s="72" t="n">
+      <c r="K16" s="70" t="n">
         <v>-41</v>
       </c>
-      <c r="L16" s="72" t="n">
+      <c r="L16" s="70" t="n">
         <v>-15</v>
       </c>
-      <c r="M16" s="71" t="n">
+      <c r="M16" s="69" t="n">
         <v>1281</v>
       </c>
-      <c r="N16" s="71" t="n">
+      <c r="N16" s="69" t="n">
         <v>14</v>
       </c>
-      <c r="O16" s="74" t="inlineStr">
+      <c r="O16" s="72" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10330,43 +10322,43 @@
           <t>전기·가스</t>
         </is>
       </c>
-      <c r="B17" s="70" t="n">
+      <c r="B17" s="68" t="n">
         <v>-27.82</v>
       </c>
-      <c r="C17" s="70" t="n">
+      <c r="C17" s="68" t="n">
         <v>-13.54</v>
       </c>
-      <c r="D17" s="70" t="n">
+      <c r="D17" s="68" t="n">
         <v>-2.36</v>
       </c>
-      <c r="E17" s="69" t="n">
+      <c r="E17" s="67" t="n">
         <v>0.43</v>
       </c>
-      <c r="F17" s="72" t="n">
+      <c r="F17" s="70" t="n">
         <v>-138</v>
       </c>
-      <c r="G17" s="71" t="n">
+      <c r="G17" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="H17" s="72" t="n">
+      <c r="H17" s="70" t="n">
         <v>-136</v>
       </c>
-      <c r="I17" s="71" t="n">
+      <c r="I17" s="69" t="n">
         <v>30</v>
       </c>
-      <c r="J17" s="71" t="n">
+      <c r="J17" s="69" t="n">
         <v>28</v>
       </c>
-      <c r="K17" s="72" t="n">
+      <c r="K17" s="70" t="n">
         <v>-55</v>
       </c>
-      <c r="L17" s="72" t="n">
+      <c r="L17" s="70" t="n">
         <v>-1</v>
       </c>
-      <c r="M17" s="71" t="n">
+      <c r="M17" s="69" t="n">
         <v>138</v>
       </c>
-      <c r="N17" s="72" t="n">
+      <c r="N17" s="70" t="n">
         <v>-2</v>
       </c>
       <c r="O17" s="61" t="inlineStr">
@@ -10381,46 +10373,46 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="B18" s="69" t="n">
+      <c r="B18" s="67" t="n">
         <v>4.41</v>
       </c>
-      <c r="C18" s="69" t="n">
+      <c r="C18" s="67" t="n">
         <v>3.49</v>
       </c>
-      <c r="D18" s="70" t="n">
+      <c r="D18" s="68" t="n">
         <v>-2.99</v>
       </c>
-      <c r="E18" s="69" t="n">
+      <c r="E18" s="67" t="n">
         <v>0.22</v>
       </c>
-      <c r="F18" s="71" t="n">
+      <c r="F18" s="69" t="n">
         <v>47</v>
       </c>
-      <c r="G18" s="72" t="n">
+      <c r="G18" s="70" t="n">
         <v>-461</v>
       </c>
-      <c r="H18" s="72" t="n">
+      <c r="H18" s="70" t="n">
         <v>-413</v>
       </c>
-      <c r="I18" s="71" t="n">
+      <c r="I18" s="69" t="n">
         <v>55</v>
       </c>
-      <c r="J18" s="72" t="n">
+      <c r="J18" s="70" t="n">
         <v>-287</v>
       </c>
-      <c r="K18" s="72" t="n">
+      <c r="K18" s="70" t="n">
         <v>-168</v>
       </c>
-      <c r="L18" s="72" t="n">
+      <c r="L18" s="70" t="n">
         <v>-62</v>
       </c>
-      <c r="M18" s="71" t="n">
+      <c r="M18" s="69" t="n">
         <v>406</v>
       </c>
-      <c r="N18" s="71" t="n">
+      <c r="N18" s="69" t="n">
         <v>7</v>
       </c>
-      <c r="O18" s="74" t="inlineStr">
+      <c r="O18" s="72" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10432,43 +10424,43 @@
           <t>섬유·의류</t>
         </is>
       </c>
-      <c r="B19" s="70" t="n">
+      <c r="B19" s="68" t="n">
         <v>-5.45</v>
       </c>
-      <c r="C19" s="70" t="n">
+      <c r="C19" s="68" t="n">
         <v>-1.57</v>
       </c>
-      <c r="D19" s="69" t="n">
+      <c r="D19" s="67" t="n">
         <v>4.14</v>
       </c>
-      <c r="E19" s="70" t="n">
+      <c r="E19" s="68" t="n">
         <v>-0.1</v>
       </c>
-      <c r="F19" s="72" t="n">
+      <c r="F19" s="70" t="n">
         <v>-45</v>
       </c>
-      <c r="G19" s="71" t="n">
+      <c r="G19" s="69" t="n">
         <v>34</v>
       </c>
-      <c r="H19" s="72" t="n">
+      <c r="H19" s="70" t="n">
         <v>-11</v>
       </c>
-      <c r="I19" s="71" t="n">
+      <c r="I19" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="71" t="n">
+      <c r="J19" s="69" t="n">
         <v>9</v>
       </c>
-      <c r="K19" s="71" t="n">
+      <c r="K19" s="69" t="n">
         <v>18</v>
       </c>
-      <c r="L19" s="71" t="n">
+      <c r="L19" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="M19" s="72" t="n">
+      <c r="M19" s="70" t="n">
         <v>-15</v>
       </c>
-      <c r="N19" s="71" t="n">
+      <c r="N19" s="69" t="n">
         <v>26</v>
       </c>
       <c r="O19" s="61" t="inlineStr">
@@ -10483,43 +10475,43 @@
           <t>통신</t>
         </is>
       </c>
-      <c r="B20" s="69" t="n">
+      <c r="B20" s="67" t="n">
         <v>25.11</v>
       </c>
-      <c r="C20" s="70" t="n">
+      <c r="C20" s="68" t="n">
         <v>-3.08</v>
       </c>
-      <c r="D20" s="70" t="n">
+      <c r="D20" s="68" t="n">
         <v>-7.51</v>
       </c>
-      <c r="E20" s="70" t="n">
+      <c r="E20" s="68" t="n">
         <v>-0.43</v>
       </c>
-      <c r="F20" s="71" t="n">
+      <c r="F20" s="69" t="n">
         <v>232</v>
       </c>
-      <c r="G20" s="72" t="n">
+      <c r="G20" s="70" t="n">
         <v>-240</v>
       </c>
-      <c r="H20" s="72" t="n">
+      <c r="H20" s="70" t="n">
         <v>-8</v>
       </c>
-      <c r="I20" s="71" t="n">
+      <c r="I20" s="69" t="n">
         <v>21</v>
       </c>
-      <c r="J20" s="72" t="n">
+      <c r="J20" s="70" t="n">
         <v>-64</v>
       </c>
-      <c r="K20" s="72" t="n">
+      <c r="K20" s="70" t="n">
         <v>-200</v>
       </c>
-      <c r="L20" s="71" t="n">
+      <c r="L20" s="69" t="n">
         <v>2</v>
       </c>
-      <c r="M20" s="71" t="n">
+      <c r="M20" s="69" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="72" t="n">
+      <c r="N20" s="70" t="n">
         <v>-3</v>
       </c>
       <c r="O20" s="30" t="inlineStr"/>
@@ -10530,43 +10522,43 @@
           <t>종이·목재</t>
         </is>
       </c>
-      <c r="B21" s="70" t="n">
+      <c r="B21" s="68" t="n">
         <v>-20.68</v>
       </c>
-      <c r="C21" s="69" t="n">
+      <c r="C21" s="67" t="n">
         <v>0.96</v>
       </c>
-      <c r="D21" s="69" t="n">
+      <c r="D21" s="67" t="n">
         <v>0.42</v>
       </c>
-      <c r="E21" s="70" t="n">
+      <c r="E21" s="68" t="n">
         <v>-0.51</v>
       </c>
-      <c r="F21" s="72" t="n">
+      <c r="F21" s="70" t="n">
         <v>-4</v>
       </c>
-      <c r="G21" s="71" t="n">
+      <c r="G21" s="69" t="n">
         <v>4</v>
       </c>
-      <c r="H21" s="75" t="n">
+      <c r="H21" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="I21" s="71" t="n">
+      <c r="I21" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="J21" s="75" t="n">
+      <c r="J21" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="K21" s="75" t="n">
+      <c r="K21" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="L21" s="75" t="n">
+      <c r="L21" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="M21" s="71" t="n">
+      <c r="M21" s="69" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="72" t="n">
+      <c r="N21" s="70" t="n">
         <v>-2</v>
       </c>
       <c r="O21" s="30" t="inlineStr"/>
@@ -10577,40 +10569,40 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="B22" s="76" t="inlineStr"/>
-      <c r="C22" s="76" t="inlineStr"/>
-      <c r="D22" s="76" t="inlineStr"/>
-      <c r="E22" s="70" t="n">
+      <c r="B22" s="74" t="inlineStr"/>
+      <c r="C22" s="74" t="inlineStr"/>
+      <c r="D22" s="74" t="inlineStr"/>
+      <c r="E22" s="68" t="n">
         <v>-0.52</v>
       </c>
-      <c r="F22" s="72" t="n">
+      <c r="F22" s="70" t="n">
         <v>-338</v>
       </c>
-      <c r="G22" s="71" t="n">
+      <c r="G22" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="H22" s="72" t="n">
+      <c r="H22" s="70" t="n">
         <v>-337</v>
       </c>
-      <c r="I22" s="71" t="n">
+      <c r="I22" s="69" t="n">
         <v>142</v>
       </c>
-      <c r="J22" s="72" t="n">
+      <c r="J22" s="70" t="n">
         <v>-34</v>
       </c>
-      <c r="K22" s="72" t="n">
+      <c r="K22" s="70" t="n">
         <v>-113</v>
       </c>
-      <c r="L22" s="71" t="n">
+      <c r="L22" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="M22" s="71" t="n">
+      <c r="M22" s="69" t="n">
         <v>338</v>
       </c>
-      <c r="N22" s="72" t="n">
+      <c r="N22" s="70" t="n">
         <v>-1</v>
       </c>
-      <c r="O22" s="77" t="inlineStr">
+      <c r="O22" s="75" t="inlineStr">
         <is>
           <t>데이터부족</t>
         </is>
@@ -10622,43 +10614,43 @@
           <t>제약</t>
         </is>
       </c>
-      <c r="B23" s="70" t="n">
+      <c r="B23" s="68" t="n">
         <v>-15.02</v>
       </c>
-      <c r="C23" s="69" t="n">
+      <c r="C23" s="67" t="n">
         <v>5.87</v>
       </c>
-      <c r="D23" s="70" t="n">
+      <c r="D23" s="68" t="n">
         <v>-7.4</v>
       </c>
-      <c r="E23" s="70" t="n">
+      <c r="E23" s="68" t="n">
         <v>-0.54</v>
       </c>
-      <c r="F23" s="72" t="n">
+      <c r="F23" s="70" t="n">
         <v>-32</v>
       </c>
-      <c r="G23" s="72" t="n">
+      <c r="G23" s="70" t="n">
         <v>-159</v>
       </c>
-      <c r="H23" s="72" t="n">
+      <c r="H23" s="70" t="n">
         <v>-191</v>
       </c>
-      <c r="I23" s="71" t="n">
+      <c r="I23" s="69" t="n">
         <v>274</v>
       </c>
-      <c r="J23" s="72" t="n">
+      <c r="J23" s="70" t="n">
         <v>-136</v>
       </c>
-      <c r="K23" s="72" t="n">
+      <c r="K23" s="70" t="n">
         <v>-257</v>
       </c>
-      <c r="L23" s="72" t="n">
+      <c r="L23" s="70" t="n">
         <v>-35</v>
       </c>
-      <c r="M23" s="71" t="n">
+      <c r="M23" s="69" t="n">
         <v>183</v>
       </c>
-      <c r="N23" s="71" t="n">
+      <c r="N23" s="69" t="n">
         <v>8</v>
       </c>
       <c r="O23" s="61" t="inlineStr">
@@ -10673,46 +10665,46 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="B24" s="69" t="n">
+      <c r="B24" s="67" t="n">
         <v>14.97</v>
       </c>
-      <c r="C24" s="69" t="n">
+      <c r="C24" s="67" t="n">
         <v>2.95</v>
       </c>
-      <c r="D24" s="69" t="n">
+      <c r="D24" s="67" t="n">
         <v>1.94</v>
       </c>
-      <c r="E24" s="70" t="n">
+      <c r="E24" s="68" t="n">
         <v>-0.68</v>
       </c>
-      <c r="F24" s="72" t="n">
+      <c r="F24" s="70" t="n">
         <v>-212</v>
       </c>
-      <c r="G24" s="72" t="n">
+      <c r="G24" s="70" t="n">
         <v>-382</v>
       </c>
-      <c r="H24" s="72" t="n">
+      <c r="H24" s="70" t="n">
         <v>-594</v>
       </c>
-      <c r="I24" s="71" t="n">
+      <c r="I24" s="69" t="n">
         <v>95</v>
       </c>
-      <c r="J24" s="72" t="n">
+      <c r="J24" s="70" t="n">
         <v>-503</v>
       </c>
-      <c r="K24" s="71" t="n">
+      <c r="K24" s="69" t="n">
         <v>52</v>
       </c>
-      <c r="L24" s="72" t="n">
+      <c r="L24" s="70" t="n">
         <v>-24</v>
       </c>
-      <c r="M24" s="71" t="n">
+      <c r="M24" s="69" t="n">
         <v>594</v>
       </c>
-      <c r="N24" s="71" t="n">
+      <c r="N24" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="O24" s="74" t="inlineStr">
+      <c r="O24" s="72" t="inlineStr">
         <is>
           <t>수급이탈</t>
         </is>
@@ -10724,43 +10716,43 @@
           <t>비금속</t>
         </is>
       </c>
-      <c r="B25" s="70" t="n">
+      <c r="B25" s="68" t="n">
         <v>-13.78</v>
       </c>
-      <c r="C25" s="70" t="n">
+      <c r="C25" s="68" t="n">
         <v>-0.86</v>
       </c>
-      <c r="D25" s="69" t="n">
+      <c r="D25" s="67" t="n">
         <v>1.42</v>
       </c>
-      <c r="E25" s="70" t="n">
+      <c r="E25" s="68" t="n">
         <v>-1.42</v>
       </c>
-      <c r="F25" s="72" t="n">
+      <c r="F25" s="70" t="n">
         <v>-17</v>
       </c>
-      <c r="G25" s="71" t="n">
+      <c r="G25" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="H25" s="72" t="n">
+      <c r="H25" s="70" t="n">
         <v>-12</v>
       </c>
-      <c r="I25" s="71" t="n">
+      <c r="I25" s="69" t="n">
         <v>6</v>
       </c>
-      <c r="J25" s="71" t="n">
+      <c r="J25" s="69" t="n">
         <v>1</v>
       </c>
-      <c r="K25" s="72" t="n">
+      <c r="K25" s="70" t="n">
         <v>-2</v>
       </c>
-      <c r="L25" s="75" t="n">
+      <c r="L25" s="73" t="n">
         <v>0</v>
       </c>
-      <c r="M25" s="71" t="n">
+      <c r="M25" s="69" t="n">
         <v>19</v>
       </c>
-      <c r="N25" s="72" t="n">
+      <c r="N25" s="70" t="n">
         <v>-7</v>
       </c>
       <c r="O25" s="61" t="inlineStr">
@@ -10775,43 +10767,43 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="B26" s="70" t="n">
+      <c r="B26" s="68" t="n">
         <v>-3.37</v>
       </c>
-      <c r="C26" s="70" t="n">
+      <c r="C26" s="68" t="n">
         <v>-27.34</v>
       </c>
-      <c r="D26" s="70" t="n">
+      <c r="D26" s="68" t="n">
         <v>-8.300000000000001</v>
       </c>
-      <c r="E26" s="70" t="n">
+      <c r="E26" s="68" t="n">
         <v>-1.67</v>
       </c>
-      <c r="F26" s="72" t="n">
+      <c r="F26" s="70" t="n">
         <v>-1966</v>
       </c>
-      <c r="G26" s="72" t="n">
+      <c r="G26" s="70" t="n">
         <v>-993</v>
       </c>
-      <c r="H26" s="72" t="n">
+      <c r="H26" s="70" t="n">
         <v>-2959</v>
       </c>
-      <c r="I26" s="71" t="n">
+      <c r="I26" s="69" t="n">
         <v>807</v>
       </c>
-      <c r="J26" s="72" t="n">
+      <c r="J26" s="70" t="n">
         <v>-893</v>
       </c>
-      <c r="K26" s="72" t="n">
+      <c r="K26" s="70" t="n">
         <v>-809</v>
       </c>
-      <c r="L26" s="72" t="n">
+      <c r="L26" s="70" t="n">
         <v>-100</v>
       </c>
-      <c r="M26" s="71" t="n">
+      <c r="M26" s="69" t="n">
         <v>2968</v>
       </c>
-      <c r="N26" s="72" t="n">
+      <c r="N26" s="70" t="n">
         <v>-9</v>
       </c>
       <c r="O26" s="61" t="inlineStr">
@@ -10826,43 +10818,43 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="B27" s="69" t="n">
+      <c r="B27" s="67" t="n">
         <v>3.29</v>
       </c>
-      <c r="C27" s="70" t="n">
+      <c r="C27" s="68" t="n">
         <v>-6.01</v>
       </c>
-      <c r="D27" s="69" t="n">
+      <c r="D27" s="67" t="n">
         <v>0.02</v>
       </c>
-      <c r="E27" s="70" t="n">
+      <c r="E27" s="68" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F27" s="72" t="n">
+      <c r="F27" s="70" t="n">
         <v>-968</v>
       </c>
-      <c r="G27" s="71" t="n">
+      <c r="G27" s="69" t="n">
         <v>72</v>
       </c>
-      <c r="H27" s="72" t="n">
+      <c r="H27" s="70" t="n">
         <v>-896</v>
       </c>
-      <c r="I27" s="71" t="n">
+      <c r="I27" s="69" t="n">
         <v>202</v>
       </c>
-      <c r="J27" s="72" t="n">
+      <c r="J27" s="70" t="n">
         <v>-105</v>
       </c>
-      <c r="K27" s="72" t="n">
+      <c r="K27" s="70" t="n">
         <v>-1</v>
       </c>
-      <c r="L27" s="72" t="n">
+      <c r="L27" s="70" t="n">
         <v>-24</v>
       </c>
-      <c r="M27" s="71" t="n">
+      <c r="M27" s="69" t="n">
         <v>681</v>
       </c>
-      <c r="N27" s="71" t="n">
+      <c r="N27" s="69" t="n">
         <v>216</v>
       </c>
       <c r="O27" s="30" t="inlineStr"/>
@@ -10873,43 +10865,43 @@
           <t>오락·문화</t>
         </is>
       </c>
-      <c r="B28" s="70" t="n">
+      <c r="B28" s="68" t="n">
         <v>-45.3</v>
       </c>
-      <c r="C28" s="70" t="n">
+      <c r="C28" s="68" t="n">
         <v>-19.57</v>
       </c>
-      <c r="D28" s="70" t="n">
+      <c r="D28" s="68" t="n">
         <v>-3.54</v>
       </c>
-      <c r="E28" s="70" t="n">
+      <c r="E28" s="68" t="n">
         <v>-3.07</v>
       </c>
-      <c r="F28" s="72" t="n">
+      <c r="F28" s="70" t="n">
         <v>-355</v>
       </c>
-      <c r="G28" s="72" t="n">
+      <c r="G28" s="70" t="n">
         <v>-166</v>
       </c>
-      <c r="H28" s="72" t="n">
+      <c r="H28" s="70" t="n">
         <v>-522</v>
       </c>
-      <c r="I28" s="71" t="n">
+      <c r="I28" s="69" t="n">
         <v>5</v>
       </c>
-      <c r="J28" s="72" t="n">
+      <c r="J28" s="70" t="n">
         <v>-56</v>
       </c>
-      <c r="K28" s="72" t="n">
+      <c r="K28" s="70" t="n">
         <v>-111</v>
       </c>
-      <c r="L28" s="72" t="n">
+      <c r="L28" s="70" t="n">
         <v>-4</v>
       </c>
-      <c r="M28" s="71" t="n">
+      <c r="M28" s="69" t="n">
         <v>516</v>
       </c>
-      <c r="N28" s="71" t="n">
+      <c r="N28" s="69" t="n">
         <v>6</v>
       </c>
       <c r="O28" s="61" t="inlineStr">
@@ -10950,7 +10942,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{559D44B6-007C-4578-B593-136E884AE58A}</x14:id>
+          <x14:id>{23B8B059-819D-44A4-AA54-8EAA20F7D17E}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10964,7 +10956,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{3C4AADBC-4848-4ADA-B7EE-AF3E076F94CA}</x14:id>
+          <x14:id>{4C8454EB-E545-4837-8B75-94A608092593}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10978,7 +10970,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{24AE0BE9-7D93-44BF-BF4A-68093BD59934}</x14:id>
+          <x14:id>{F9AA6A9C-FADD-4575-B897-9C0CDCC96C04}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -10992,7 +10984,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{52A90BA0-61A2-4989-857E-0D09E0EFD4AA}</x14:id>
+          <x14:id>{1BEA54C3-4A93-4041-AA52-CB178403F134}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11002,7 +10994,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{559D44B6-007C-4578-B593-136E884AE58A}">
+          <x14:cfRule type="dataBar" id="{23B8B059-819D-44A4-AA54-8EAA20F7D17E}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11015,7 +11007,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{3C4AADBC-4848-4ADA-B7EE-AF3E076F94CA}">
+          <x14:cfRule type="dataBar" id="{4C8454EB-E545-4837-8B75-94A608092593}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11028,7 +11020,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{24AE0BE9-7D93-44BF-BF4A-68093BD59934}">
+          <x14:cfRule type="dataBar" id="{F9AA6A9C-FADD-4575-B897-9C0CDCC96C04}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11041,7 +11033,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{52A90BA0-61A2-4989-857E-0D09E0EFD4AA}">
+          <x14:cfRule type="dataBar" id="{1BEA54C3-4A93-4041-AA52-CB178403F134}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/weekly_briefing/2026-09-21.xlsx
+++ b/public/reports/weekly_briefing/2026-09-21.xlsx
@@ -13,7 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="섹터x수급" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'신고가 근접'!$A$5:$L$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'섹터x수급'!$A$4:$O$28</definedName>
   </definedNames>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -456,26 +456,14 @@
     <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -483,16 +471,28 @@
     <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="168" fontId="18" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="168" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -939,7 +939,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K137"/>
+  <dimension ref="A1:K133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="12.9" customWidth="1" style="15" min="1" max="1"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="I1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21 ~ 2026-09-24</t>
+          <t>2026-09-21 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -980,7 +980,7 @@
       </c>
       <c r="I2" s="25" t="inlineStr">
         <is>
-          <t>2026-09-24 16:14 KST</t>
+          <t>2026-09-24 17:03 KST</t>
         </is>
       </c>
     </row>
@@ -993,7 +993,7 @@
       </c>
       <c r="C4" s="27" t="inlineStr">
         <is>
-          <t>반도체·AI 훈풍 속 기관 주도 랠리와 건설 섹터의 차별화</t>
+          <t>반도체와 AI 모멘텀이 이끈 지수 상승 랠리</t>
         </is>
       </c>
     </row>
@@ -1089,13 +1089,13 @@
         </is>
       </c>
       <c r="B8" s="28" t="n">
-        <v>-74920</v>
+        <v>-60271</v>
       </c>
       <c r="C8" s="28" t="n">
-        <v>-11003</v>
+        <v>-6061</v>
       </c>
       <c r="D8" s="29" t="n">
-        <v>20090</v>
+        <v>16901</v>
       </c>
       <c r="E8" s="29" t="n">
         <v>0.73</v>
@@ -1107,7 +1107,7 @@
         <v>1.56</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>2.5</v>
+        <v>6.68</v>
       </c>
       <c r="I8" s="29" t="n">
         <v>5.14</v>
@@ -1120,13 +1120,13 @@
         </is>
       </c>
       <c r="B9" s="29" t="n">
-        <v>3573</v>
+        <v>3298</v>
       </c>
       <c r="C9" s="28" t="n">
-        <v>-2515</v>
+        <v>-2053</v>
       </c>
       <c r="D9" s="28" t="n">
-        <v>-1102</v>
+        <v>-1178</v>
       </c>
     </row>
     <row r="10"/>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="G32" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체주 강세와 VIX 하락에 힘입어 국내 증시는 반도체 및 전력망 관련주를 중심으로 상승하며 7000선을 회복함.</t>
+          <t>미국 필라델피아 반도체 지수 급등(2.78%)이 국내 반도체 및 전력망 관련주로 이어지며 기관 매수세와 함께 지수 상승을 견인함.</t>
         </is>
       </c>
     </row>
@@ -1713,7 +1713,7 @@
       </c>
       <c r="G33" s="17" t="inlineStr">
         <is>
-          <t>미국 기술주 랠리에도 불구하고 개인의 대규모 매도세가 출회되었으나, 외국인 매수세가 지수를 방어하며 반도체 소부장 중심의 강세가 이어짐.</t>
+          <t>미국 기술주 랠리(SOX +4.29%)에 힘입어 국내 AI 데이터센터 관련주와 반도체 소부장이 강세를 보였으나, 에너지 섹터 약세가 상승폭을 일부 제한함.</t>
         </is>
       </c>
     </row>
@@ -1782,215 +1782,187 @@
       </c>
       <c r="G34" s="17" t="inlineStr">
         <is>
-          <t>미국 반도체 섹터의 강세가 국내 AI 밸류체인으로 확산되었으나, 외국인의 대규모 매도세가 지수 상단을 제한하며 건설 섹터의 급락이 시장의 발목을 잡음.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="44.5" customHeight="1" s="15">
-      <c r="A35" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B35" s="29" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="C35" s="31" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00D64545"/>
-              <sz val="10"/>
-            </rPr>
-            <t>311▲</t>
-          </r>
-          <r>
-            <t>/</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="003182F6"/>
-              <sz val="10"/>
-            </rPr>
-            <t>548▼</t>
-          </r>
-        </is>
-      </c>
-      <c r="D35" s="29" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="E35" s="17" t="inlineStr">
-        <is>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="00D64545"/>
-              <sz val="10"/>
-            </rPr>
-            <t>856▲ 상한4</t>
-          </r>
-          <r>
-            <t>/</t>
-          </r>
-          <r>
-            <rPr>
-              <rFont val="맑은 고딕"/>
-              <color rgb="003182F6"/>
-              <sz val="10"/>
-            </rPr>
-            <t>786▼</t>
-          </r>
-        </is>
-      </c>
-      <c r="F35" s="17" t="inlineStr">
-        <is>
-          <t>의료·정밀기기, 전기·전자</t>
-        </is>
-      </c>
-      <c r="G35" s="17" t="inlineStr">
-        <is>
-          <t>미국 증시의 지정학적 리스크와 인플레이션 우려로 인한 하락세가 국내 증시에도 반영되어 외국인 매도세가 지속되었으나, 기관의 순매수가 지수 방어를 주도함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36"/>
+          <t>미국 반도체 섹터 강세(2.06%)가 국내 HBM 밸류체인으로 확산되었으나, 외국인의 대규모 매도세가 지수 상단을 압박함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="B36" s="3" t="inlineStr">
+        <is>
+          <t>주간 종합 코멘트 — 매크로·수급</t>
+        </is>
+      </c>
+      <c r="C36" s="3" t="inlineStr"/>
+      <c r="D36" s="3" t="inlineStr"/>
+      <c r="E36" s="3" t="inlineStr"/>
+      <c r="F36" s="3" t="inlineStr"/>
+      <c r="G36" s="3" t="inlineStr"/>
+      <c r="H36" s="3" t="inlineStr"/>
+      <c r="I36" s="3" t="inlineStr"/>
+      <c r="J36" s="3" t="inlineStr"/>
+      <c r="K36" s="3" t="inlineStr"/>
+    </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="B37" s="3" t="inlineStr">
-        <is>
-          <t>주간 종합 코멘트 — 매크로·수급</t>
-        </is>
-      </c>
-      <c r="C37" s="3" t="inlineStr"/>
-      <c r="D37" s="3" t="inlineStr"/>
-      <c r="E37" s="3" t="inlineStr"/>
-      <c r="F37" s="3" t="inlineStr"/>
-      <c r="G37" s="3" t="inlineStr"/>
-      <c r="H37" s="3" t="inlineStr"/>
-      <c r="I37" s="3" t="inlineStr"/>
-      <c r="J37" s="3" t="inlineStr"/>
-      <c r="K37" s="3" t="inlineStr"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B38" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>Comment</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="31" customHeight="1" s="15">
+      <c r="A38" s="17" t="inlineStr">
+        <is>
+          <t>- 매크로 환경은 미국 산업생산이 0%로 이전치(0.2%)를 하회했으나, 국내 소비자심리지수는 106.6으로 이전치(104.5)를 상회하며 내수 개선 기대감을 높임.</t>
         </is>
       </c>
     </row>
     <row r="39" ht="31" customHeight="1" s="15">
       <c r="A39" s="17" t="inlineStr">
         <is>
-          <t>- 매크로 환경: 미국 산업생산은 전월 대비 0%로 부진했으나, 한국 소비자심리지수는 106.6으로 이전치(104.5)를 상회하며 내수 개선 기대감을 높임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="31" customHeight="1" s="15">
+          <t>- 수급 구도는 전기·전자 섹터에 기관(20,095억)과 외국인(4,964억)의 매수세가 집중되며 주간 4.51% 상승했으나, 건설(-4.25%)과 운송장비(-3.98%)는 외국인 매도세가 뚜렷함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="15" customHeight="1" s="15">
       <c r="A40" s="17" t="inlineStr">
         <is>
-          <t>- 수급 구도: 전기·전자 섹터에 기관(20,095억)과 외국인(4,964억)의 매수세가 집중되며 주간 4.51% 상승했으나, 건설 섹터는 외국인(-1,734억)과 기관(-790억)의 동반 이탈로 4.25% 하락함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="31" customHeight="1" s="15">
-      <c r="A41" s="17" t="inlineStr">
-        <is>
-          <t>- 종합 관점: 반도체 중심의 기술주 모멘텀이 시장을 견인하고 있으나, 외국인 수급의 변동성과 건설 등 특정 섹터의 악재가 시장의 상승 탄력을 둔화시키는 양상임.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42"/>
+          <t>- 반도체 중심의 기술주 모멘텀은 견고하나, 외국인의 수급 방향성이 지수 변동성을 결정하는 핵심 변수로 작용하고 있음.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="B42" s="3" t="inlineStr">
+        <is>
+          <t>투자자 합산 순매수 상위/하위</t>
+        </is>
+      </c>
+      <c r="C42" s="3" t="inlineStr"/>
+      <c r="D42" s="3" t="inlineStr"/>
+      <c r="E42" s="3" t="inlineStr"/>
+      <c r="F42" s="3" t="inlineStr"/>
+      <c r="G42" s="3" t="inlineStr"/>
+      <c r="H42" s="3" t="inlineStr"/>
+      <c r="I42" s="3" t="inlineStr"/>
+      <c r="J42" s="18" t="inlineStr">
+        <is>
+          <t>외인+기관계, 억원</t>
+        </is>
+      </c>
+      <c r="K42" s="3" t="inlineStr"/>
+    </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="B43" s="3" t="inlineStr">
-        <is>
-          <t>투자자 합산 순매수 상위/하위</t>
-        </is>
-      </c>
-      <c r="C43" s="3" t="inlineStr"/>
-      <c r="D43" s="3" t="inlineStr"/>
-      <c r="E43" s="3" t="inlineStr"/>
-      <c r="F43" s="3" t="inlineStr"/>
-      <c r="G43" s="3" t="inlineStr"/>
-      <c r="H43" s="3" t="inlineStr"/>
-      <c r="I43" s="3" t="inlineStr"/>
-      <c r="J43" s="18" t="inlineStr">
-        <is>
-          <t>외인+기관계, 억원</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr"/>
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>순위</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>섹터명</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>합산</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>외인</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="inlineStr">
+        <is>
+          <t>기관</t>
+        </is>
+      </c>
+      <c r="H43" s="4" t="inlineStr">
+        <is>
+          <t>개인</t>
+        </is>
+      </c>
+      <c r="I43" s="4" t="inlineStr">
+        <is>
+          <t>공매도</t>
+        </is>
+      </c>
+      <c r="J43" s="4" t="inlineStr">
+        <is>
+          <t>대차잔고</t>
+        </is>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>대차증감</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
-        <is>
-          <t>구분</t>
-        </is>
-      </c>
-      <c r="B44" s="4" t="inlineStr">
-        <is>
-          <t>순위</t>
-        </is>
-      </c>
-      <c r="C44" s="4" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="D44" s="4" t="inlineStr">
-        <is>
-          <t>섹터명</t>
-        </is>
-      </c>
-      <c r="E44" s="4" t="inlineStr">
-        <is>
-          <t>합산</t>
-        </is>
-      </c>
-      <c r="F44" s="4" t="inlineStr">
-        <is>
-          <t>외인</t>
-        </is>
-      </c>
-      <c r="G44" s="4" t="inlineStr">
-        <is>
-          <t>기관</t>
-        </is>
-      </c>
-      <c r="H44" s="4" t="inlineStr">
-        <is>
-          <t>개인</t>
-        </is>
-      </c>
-      <c r="I44" s="4" t="inlineStr">
-        <is>
-          <t>공매도</t>
-        </is>
-      </c>
-      <c r="J44" s="4" t="inlineStr">
-        <is>
-          <t>대차잔고</t>
-        </is>
-      </c>
-      <c r="K44" s="4" t="inlineStr">
-        <is>
-          <t>대차증감</t>
-        </is>
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>순매수 상위</t>
+        </is>
+      </c>
+      <c r="B44" s="31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" s="31" t="inlineStr">
+        <is>
+          <t>삼성전자</t>
+        </is>
+      </c>
+      <c r="D44" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E44" s="29" t="n">
+        <v>41338</v>
+      </c>
+      <c r="F44" s="29" t="n">
+        <v>25488</v>
+      </c>
+      <c r="G44" s="29" t="n">
+        <v>15850</v>
+      </c>
+      <c r="H44" s="28" t="n">
+        <v>-56555</v>
+      </c>
+      <c r="I44" s="31" t="n">
+        <v>2176.5</v>
+      </c>
+      <c r="J44" s="31" t="n">
+        <v>246411.2</v>
+      </c>
+      <c r="K44" s="31" t="n">
+        <v>6734.3</v>
       </c>
     </row>
     <row r="45">
@@ -2000,11 +1972,11 @@
         </is>
       </c>
       <c r="B45" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C45" s="31" t="inlineStr">
         <is>
-          <t>삼성전자</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="D45" s="34" t="inlineStr">
@@ -2013,25 +1985,25 @@
         </is>
       </c>
       <c r="E45" s="29" t="n">
-        <v>49119</v>
+        <v>4065</v>
       </c>
       <c r="F45" s="29" t="n">
-        <v>31006</v>
+        <v>1076</v>
       </c>
       <c r="G45" s="29" t="n">
-        <v>18113</v>
+        <v>2989</v>
       </c>
       <c r="H45" s="28" t="n">
-        <v>-56555</v>
+        <v>-4072</v>
       </c>
       <c r="I45" s="31" t="n">
-        <v>2176.5</v>
+        <v>321.8</v>
       </c>
       <c r="J45" s="31" t="n">
-        <v>246411.2</v>
+        <v>37037.9</v>
       </c>
       <c r="K45" s="31" t="n">
-        <v>6734.3</v>
+        <v>2854.7</v>
       </c>
     </row>
     <row r="46">
@@ -2041,38 +2013,38 @@
         </is>
       </c>
       <c r="B46" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C46" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>SK스퀘어</t>
         </is>
       </c>
       <c r="D46" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="E46" s="29" t="n">
-        <v>4139</v>
+        <v>3426</v>
       </c>
       <c r="F46" s="29" t="n">
-        <v>4636</v>
-      </c>
-      <c r="G46" s="28" t="n">
-        <v>-496</v>
+        <v>2380</v>
+      </c>
+      <c r="G46" s="29" t="n">
+        <v>1046</v>
       </c>
       <c r="H46" s="28" t="n">
-        <v>-2629</v>
+        <v>-3389</v>
       </c>
       <c r="I46" s="31" t="n">
-        <v>327</v>
+        <v>710.7</v>
       </c>
       <c r="J46" s="31" t="n">
-        <v>28532.1</v>
+        <v>32724.5</v>
       </c>
       <c r="K46" s="31" t="n">
-        <v>716.2</v>
+        <v>3512.1</v>
       </c>
     </row>
     <row r="47">
@@ -2082,38 +2054,38 @@
         </is>
       </c>
       <c r="B47" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C47" s="31" t="inlineStr">
         <is>
-          <t>SK스퀘어</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="D47" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E47" s="29" t="n">
-        <v>3343</v>
+        <v>2668</v>
       </c>
       <c r="F47" s="29" t="n">
-        <v>2108</v>
-      </c>
-      <c r="G47" s="29" t="n">
-        <v>1235</v>
+        <v>3048</v>
+      </c>
+      <c r="G47" s="28" t="n">
+        <v>-381</v>
       </c>
       <c r="H47" s="28" t="n">
-        <v>-3389</v>
+        <v>-2629</v>
       </c>
       <c r="I47" s="31" t="n">
-        <v>710.7</v>
+        <v>327</v>
       </c>
       <c r="J47" s="31" t="n">
-        <v>32724.5</v>
+        <v>28532.1</v>
       </c>
       <c r="K47" s="31" t="n">
-        <v>3512.1</v>
+        <v>716.2</v>
       </c>
     </row>
     <row r="48">
@@ -2123,11 +2095,11 @@
         </is>
       </c>
       <c r="B48" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C48" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="D48" s="34" t="inlineStr">
@@ -2136,25 +2108,25 @@
         </is>
       </c>
       <c r="E48" s="29" t="n">
-        <v>2954</v>
-      </c>
-      <c r="F48" s="28" t="n">
-        <v>-350</v>
+        <v>1410</v>
+      </c>
+      <c r="F48" s="29" t="n">
+        <v>687</v>
       </c>
       <c r="G48" s="29" t="n">
-        <v>3304</v>
+        <v>723</v>
       </c>
       <c r="H48" s="28" t="n">
-        <v>-4072</v>
+        <v>-1455</v>
       </c>
       <c r="I48" s="31" t="n">
-        <v>321.8</v>
+        <v>307.3</v>
       </c>
       <c r="J48" s="31" t="n">
-        <v>37037.9</v>
+        <v>9879.700000000001</v>
       </c>
       <c r="K48" s="31" t="n">
-        <v>2854.7</v>
+        <v>476.2</v>
       </c>
     </row>
     <row r="49">
@@ -2164,7 +2136,7 @@
         </is>
       </c>
       <c r="B49" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C49" s="31" t="inlineStr">
         <is>
@@ -2177,13 +2149,13 @@
         </is>
       </c>
       <c r="E49" s="29" t="n">
-        <v>1369</v>
+        <v>1325</v>
       </c>
       <c r="F49" s="29" t="n">
-        <v>717</v>
+        <v>742</v>
       </c>
       <c r="G49" s="29" t="n">
-        <v>652</v>
+        <v>583</v>
       </c>
       <c r="H49" s="28" t="n">
         <v>-1306</v>
@@ -2205,7 +2177,7 @@
         </is>
       </c>
       <c r="B50" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C50" s="31" t="inlineStr">
         <is>
@@ -2218,13 +2190,13 @@
         </is>
       </c>
       <c r="E50" s="29" t="n">
-        <v>1128</v>
+        <v>871</v>
       </c>
       <c r="F50" s="29" t="n">
-        <v>544</v>
+        <v>334</v>
       </c>
       <c r="G50" s="29" t="n">
-        <v>584</v>
+        <v>537</v>
       </c>
       <c r="H50" s="28" t="n">
         <v>-866</v>
@@ -2246,38 +2218,38 @@
         </is>
       </c>
       <c r="B51" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C51" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="D51" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="E51" s="29" t="n">
-        <v>1124</v>
+        <v>718</v>
       </c>
       <c r="F51" s="29" t="n">
-        <v>401</v>
+        <v>578</v>
       </c>
       <c r="G51" s="29" t="n">
-        <v>723</v>
+        <v>140</v>
       </c>
       <c r="H51" s="28" t="n">
-        <v>-1455</v>
+        <v>-704</v>
       </c>
       <c r="I51" s="31" t="n">
-        <v>307.3</v>
+        <v>141.3</v>
       </c>
       <c r="J51" s="31" t="n">
-        <v>9879.700000000001</v>
+        <v>3634.4</v>
       </c>
       <c r="K51" s="31" t="n">
-        <v>476.2</v>
+        <v>446.2</v>
       </c>
     </row>
     <row r="52">
@@ -2287,38 +2259,38 @@
         </is>
       </c>
       <c r="B52" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C52" s="31" t="inlineStr">
         <is>
-          <t>SK이노베이션</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="D52" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E52" s="29" t="n">
-        <v>1041</v>
+        <v>537</v>
       </c>
       <c r="F52" s="29" t="n">
-        <v>818</v>
+        <v>467</v>
       </c>
       <c r="G52" s="29" t="n">
-        <v>223</v>
+        <v>70</v>
       </c>
       <c r="H52" s="28" t="n">
-        <v>-704</v>
+        <v>-535</v>
       </c>
       <c r="I52" s="31" t="n">
-        <v>141.3</v>
+        <v>94.90000000000001</v>
       </c>
       <c r="J52" s="31" t="n">
-        <v>3634.4</v>
+        <v>9947.200000000001</v>
       </c>
       <c r="K52" s="31" t="n">
-        <v>446.2</v>
+        <v>2403.8</v>
       </c>
     </row>
     <row r="53">
@@ -2328,52 +2300,52 @@
         </is>
       </c>
       <c r="B53" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C53" s="31" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="D53" s="34" t="inlineStr">
         <is>
-          <t>증권</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E53" s="29" t="n">
-        <v>550</v>
+        <v>462</v>
       </c>
       <c r="F53" s="29" t="n">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="G53" s="29" t="n">
-        <v>186</v>
+        <v>95</v>
       </c>
       <c r="H53" s="28" t="n">
-        <v>-403</v>
+        <v>-464</v>
       </c>
       <c r="I53" s="31" t="n">
-        <v>46.9</v>
+        <v>69.40000000000001</v>
       </c>
       <c r="J53" s="31" t="n">
-        <v>1648.6</v>
+        <v>2275.4</v>
       </c>
       <c r="K53" s="31" t="n">
-        <v>110.2</v>
+        <v>328.1</v>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>순매수 상위</t>
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t>순매도 상위</t>
         </is>
       </c>
       <c r="B54" s="31" t="n">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="C54" s="31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="D54" s="34" t="inlineStr">
@@ -2381,26 +2353,26 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="E54" s="29" t="n">
-        <v>537</v>
-      </c>
-      <c r="F54" s="29" t="n">
-        <v>467</v>
+      <c r="E54" s="28" t="n">
+        <v>-23119</v>
+      </c>
+      <c r="F54" s="28" t="n">
+        <v>-24228</v>
       </c>
       <c r="G54" s="29" t="n">
-        <v>70</v>
+        <v>1109</v>
       </c>
       <c r="H54" s="28" t="n">
-        <v>-535</v>
+        <v>-10659</v>
       </c>
       <c r="I54" s="31" t="n">
-        <v>94.90000000000001</v>
+        <v>5332.8</v>
       </c>
       <c r="J54" s="31" t="n">
-        <v>9947.200000000001</v>
+        <v>204586.6</v>
       </c>
       <c r="K54" s="31" t="n">
-        <v>2403.8</v>
+        <v>-15589.1</v>
       </c>
     </row>
     <row r="55">
@@ -2410,38 +2382,38 @@
         </is>
       </c>
       <c r="B55" s="31" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C55" s="31" t="inlineStr">
         <is>
-          <t>SK하이닉스</t>
+          <t>두산에너빌리티</t>
         </is>
       </c>
       <c r="D55" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>기계·장비</t>
         </is>
       </c>
       <c r="E55" s="28" t="n">
-        <v>-31410</v>
+        <v>-3021</v>
       </c>
       <c r="F55" s="28" t="n">
-        <v>-34214</v>
-      </c>
-      <c r="G55" s="29" t="n">
-        <v>2804</v>
-      </c>
-      <c r="H55" s="28" t="n">
-        <v>-10659</v>
+        <v>-2057</v>
+      </c>
+      <c r="G55" s="28" t="n">
+        <v>-964</v>
+      </c>
+      <c r="H55" s="29" t="n">
+        <v>2994</v>
       </c>
       <c r="I55" s="31" t="n">
-        <v>5332.8</v>
+        <v>1797.4</v>
       </c>
       <c r="J55" s="31" t="n">
-        <v>204586.6</v>
+        <v>19557</v>
       </c>
       <c r="K55" s="31" t="n">
-        <v>-15589.1</v>
+        <v>378.6</v>
       </c>
     </row>
     <row r="56">
@@ -2451,38 +2423,38 @@
         </is>
       </c>
       <c r="B56" s="31" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C56" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>현대차</t>
         </is>
       </c>
       <c r="D56" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E56" s="28" t="n">
-        <v>-4180</v>
+        <v>-1804</v>
       </c>
       <c r="F56" s="28" t="n">
-        <v>-3029</v>
+        <v>-1286</v>
       </c>
       <c r="G56" s="28" t="n">
-        <v>-1151</v>
+        <v>-518</v>
       </c>
       <c r="H56" s="29" t="n">
-        <v>2994</v>
+        <v>1781</v>
       </c>
       <c r="I56" s="31" t="n">
-        <v>1797.4</v>
+        <v>1262.2</v>
       </c>
       <c r="J56" s="31" t="n">
-        <v>19557</v>
+        <v>30043</v>
       </c>
       <c r="K56" s="31" t="n">
-        <v>378.6</v>
+        <v>484.4</v>
       </c>
     </row>
     <row r="57">
@@ -2492,38 +2464,38 @@
         </is>
       </c>
       <c r="B57" s="31" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C57" s="31" t="inlineStr">
         <is>
-          <t>현대차</t>
+          <t>NAVER</t>
         </is>
       </c>
       <c r="D57" s="34" t="inlineStr">
         <is>
-          <t>운송장비·부품</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E57" s="28" t="n">
-        <v>-2614</v>
+        <v>-1327</v>
       </c>
       <c r="F57" s="28" t="n">
-        <v>-1925</v>
+        <v>-231</v>
       </c>
       <c r="G57" s="28" t="n">
-        <v>-689</v>
+        <v>-1096</v>
       </c>
       <c r="H57" s="29" t="n">
-        <v>1781</v>
+        <v>1356</v>
       </c>
       <c r="I57" s="31" t="n">
-        <v>1262.2</v>
+        <v>778.3</v>
       </c>
       <c r="J57" s="31" t="n">
-        <v>30043</v>
+        <v>11204.5</v>
       </c>
       <c r="K57" s="31" t="n">
-        <v>484.4</v>
+        <v>310.2</v>
       </c>
     </row>
     <row r="58">
@@ -2533,38 +2505,38 @@
         </is>
       </c>
       <c r="B58" s="31" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="C58" s="31" t="inlineStr">
         <is>
-          <t>NAVER</t>
+          <t>대우건설</t>
         </is>
       </c>
       <c r="D58" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E58" s="28" t="n">
-        <v>-2166</v>
+        <v>-1229</v>
       </c>
       <c r="F58" s="28" t="n">
-        <v>-836</v>
+        <v>-929</v>
       </c>
       <c r="G58" s="28" t="n">
-        <v>-1329</v>
+        <v>-300</v>
       </c>
       <c r="H58" s="29" t="n">
-        <v>1356</v>
+        <v>1225</v>
       </c>
       <c r="I58" s="31" t="n">
-        <v>778.3</v>
+        <v>504</v>
       </c>
       <c r="J58" s="31" t="n">
-        <v>11204.5</v>
+        <v>5249.2</v>
       </c>
       <c r="K58" s="31" t="n">
-        <v>310.2</v>
+        <v>-282.8</v>
       </c>
     </row>
     <row r="59">
@@ -2574,38 +2546,38 @@
         </is>
       </c>
       <c r="B59" s="31" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C59" s="31" t="inlineStr">
         <is>
-          <t>대우건설</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="D59" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E59" s="28" t="n">
-        <v>-1724</v>
+        <v>-1182</v>
       </c>
       <c r="F59" s="28" t="n">
-        <v>-1334</v>
+        <v>-281</v>
       </c>
       <c r="G59" s="28" t="n">
-        <v>-390</v>
+        <v>-902</v>
       </c>
       <c r="H59" s="29" t="n">
-        <v>1225</v>
+        <v>1213</v>
       </c>
       <c r="I59" s="31" t="n">
-        <v>504</v>
+        <v>435.7</v>
       </c>
       <c r="J59" s="31" t="n">
-        <v>5249.2</v>
+        <v>13102.5</v>
       </c>
       <c r="K59" s="31" t="n">
-        <v>-282.8</v>
+        <v>-87.90000000000001</v>
       </c>
     </row>
     <row r="60">
@@ -2615,38 +2587,38 @@
         </is>
       </c>
       <c r="B60" s="31" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C60" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>현대건설</t>
         </is>
       </c>
       <c r="D60" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="E60" s="28" t="n">
-        <v>-1427</v>
+        <v>-872</v>
       </c>
       <c r="F60" s="28" t="n">
-        <v>-327</v>
+        <v>-449</v>
       </c>
       <c r="G60" s="28" t="n">
-        <v>-1100</v>
+        <v>-423</v>
       </c>
       <c r="H60" s="29" t="n">
-        <v>1213</v>
+        <v>880</v>
       </c>
       <c r="I60" s="31" t="n">
-        <v>435.7</v>
+        <v>523.8</v>
       </c>
       <c r="J60" s="31" t="n">
-        <v>13102.5</v>
+        <v>8781.200000000001</v>
       </c>
       <c r="K60" s="31" t="n">
-        <v>-87.90000000000001</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61">
@@ -2656,38 +2628,38 @@
         </is>
       </c>
       <c r="B61" s="31" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C61" s="31" t="inlineStr">
         <is>
-          <t>현대건설</t>
+          <t>한화오션</t>
         </is>
       </c>
       <c r="D61" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="E61" s="28" t="n">
-        <v>-1342</v>
+        <v>-729</v>
       </c>
       <c r="F61" s="28" t="n">
-        <v>-769</v>
+        <v>-472</v>
       </c>
       <c r="G61" s="28" t="n">
-        <v>-573</v>
+        <v>-256</v>
       </c>
       <c r="H61" s="29" t="n">
-        <v>880</v>
+        <v>725</v>
       </c>
       <c r="I61" s="31" t="n">
-        <v>523.8</v>
+        <v>317.4</v>
       </c>
       <c r="J61" s="31" t="n">
-        <v>8781.200000000001</v>
+        <v>6927</v>
       </c>
       <c r="K61" s="31" t="n">
-        <v>319</v>
+        <v>-39.8</v>
       </c>
     </row>
     <row r="62">
@@ -2697,11 +2669,11 @@
         </is>
       </c>
       <c r="B62" s="31" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C62" s="31" t="inlineStr">
         <is>
-          <t>한화오션</t>
+          <t>기아</t>
         </is>
       </c>
       <c r="D62" s="34" t="inlineStr">
@@ -2710,25 +2682,25 @@
         </is>
       </c>
       <c r="E62" s="28" t="n">
-        <v>-1021</v>
+        <v>-716</v>
       </c>
       <c r="F62" s="28" t="n">
-        <v>-751</v>
+        <v>-322</v>
       </c>
       <c r="G62" s="28" t="n">
-        <v>-269</v>
+        <v>-394</v>
       </c>
       <c r="H62" s="29" t="n">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="I62" s="31" t="n">
-        <v>317.4</v>
+        <v>362.4</v>
       </c>
       <c r="J62" s="31" t="n">
-        <v>6927</v>
+        <v>7415.5</v>
       </c>
       <c r="K62" s="31" t="n">
-        <v>-39.8</v>
+        <v>-336.8</v>
       </c>
     </row>
     <row r="63">
@@ -2738,650 +2710,644 @@
         </is>
       </c>
       <c r="B63" s="31" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C63" s="31" t="inlineStr">
         <is>
-          <t>기아</t>
+          <t>대한전선</t>
         </is>
       </c>
       <c r="D63" s="34" t="inlineStr">
         <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="E63" s="28" t="n">
+        <v>-699</v>
+      </c>
+      <c r="F63" s="28" t="n">
+        <v>-590</v>
+      </c>
+      <c r="G63" s="28" t="n">
+        <v>-109</v>
+      </c>
+      <c r="H63" s="29" t="n">
+        <v>652</v>
+      </c>
+      <c r="I63" s="31" t="n">
+        <v>87.3</v>
+      </c>
+      <c r="J63" s="31" t="n">
+        <v>1830.2</v>
+      </c>
+      <c r="K63" s="31" t="n">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="64"/>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>07</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>섹터 시그널 종목 관찰</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr"/>
+      <c r="D65" s="3" t="inlineStr"/>
+      <c r="E65" s="3" t="inlineStr"/>
+      <c r="F65" s="3" t="inlineStr"/>
+      <c r="G65" s="18" t="inlineStr">
+        <is>
+          <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
+        </is>
+      </c>
+      <c r="H65" s="3" t="inlineStr"/>
+      <c r="I65" s="3" t="inlineStr"/>
+      <c r="J65" s="3" t="inlineStr"/>
+      <c r="K65" s="3" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="35" t="inlineStr">
+        <is>
+          <t>● 동반강세 — 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+      <c r="G66" s="3" t="inlineStr">
+        <is>
+          <t>● 수급유입 — 초기 유입형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>한화</t>
+        </is>
+      </c>
+      <c r="B67" s="34" t="inlineStr">
+        <is>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="C67" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D67" s="31" t="inlineStr"/>
+      <c r="E67" s="31" t="inlineStr"/>
+      <c r="G67" s="31" t="inlineStr">
+        <is>
+          <t>해당 섹터·조건 충족 종목 없음</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="31" customHeight="1" s="15">
+      <c r="A68" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +13억 순매수, 기관 +2억 순매수, 대차잔고 -52억 감소 — 화학(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="inlineStr">
+        <is>
+          <t>SK리츠</t>
+        </is>
+      </c>
+      <c r="B69" s="34" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="C69" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D69" s="31" t="inlineStr"/>
+      <c r="E69" s="31" t="inlineStr"/>
+    </row>
+    <row r="70" ht="31" customHeight="1" s="15">
+      <c r="A70" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +3억 순매수, 기관 +5억 순매수, 대차잔고 -7억 감소 — 부동산(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="31" customHeight="1" s="15">
+      <c r="A71" s="37" t="inlineStr">
+        <is>
+          <t>코람코라이프인프라리츠</t>
+        </is>
+      </c>
+      <c r="B71" s="34" t="inlineStr">
+        <is>
+          <t>부동산</t>
+        </is>
+      </c>
+      <c r="C71" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="D71" s="31" t="inlineStr"/>
+      <c r="E71" s="31" t="inlineStr"/>
+    </row>
+    <row r="72" ht="31" customHeight="1" s="15">
+      <c r="A72" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +0억 순매수, 기관 +3억 순매수, 대차잔고 -4억 감소 — 부동산(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="5" t="inlineStr">
+        <is>
+          <t>제주은행</t>
+        </is>
+      </c>
+      <c r="B73" s="34" t="inlineStr">
+        <is>
+          <t>금융</t>
+        </is>
+      </c>
+      <c r="C73" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="D73" s="31" t="inlineStr"/>
+      <c r="E73" s="31" t="inlineStr"/>
+    </row>
+    <row r="74" ht="31" customHeight="1" s="15">
+      <c r="A74" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +0억 순매수, 대차잔고 0억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="5" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
+        </is>
+      </c>
+      <c r="B75" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="C75" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="D75" s="31" t="inlineStr"/>
+      <c r="E75" s="31" t="inlineStr"/>
+    </row>
+    <row r="76" ht="31" customHeight="1" s="15">
+      <c r="A76" s="17" t="inlineStr">
+        <is>
+          <t>외국인 +1,076억 순매수, 기관 +2,989억 순매수 — 전기·전자(동반강세) 섹터 추세 지속형 상방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="77"/>
+    <row r="78">
+      <c r="A78" s="38" t="inlineStr">
+        <is>
+          <t>● 수급이탈 — 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G78" s="39" t="inlineStr">
+        <is>
+          <t>● 동반약세 — 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="31" customHeight="1" s="15">
+      <c r="A79" s="5" t="inlineStr">
+        <is>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="B79" s="34" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="C79" s="40" t="n">
+        <v>-4</v>
+      </c>
+      <c r="D79" s="31" t="inlineStr"/>
+      <c r="E79" s="31" t="inlineStr"/>
+      <c r="G79" s="5" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="H79" s="41" t="inlineStr">
+        <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="E63" s="28" t="n">
-        <v>-980</v>
-      </c>
-      <c r="F63" s="28" t="n">
-        <v>-544</v>
-      </c>
-      <c r="G63" s="28" t="n">
-        <v>-436</v>
-      </c>
-      <c r="H63" s="29" t="n">
-        <v>716</v>
-      </c>
-      <c r="I63" s="31" t="n">
-        <v>362.4</v>
-      </c>
-      <c r="J63" s="31" t="n">
-        <v>7415.5</v>
-      </c>
-      <c r="K63" s="31" t="n">
-        <v>-336.8</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="10" t="inlineStr">
-        <is>
-          <t>순매도 상위</t>
-        </is>
-      </c>
-      <c r="B64" s="31" t="n">
-        <v>10</v>
-      </c>
-      <c r="C64" s="31" t="inlineStr">
-        <is>
-          <t>대한전선</t>
-        </is>
-      </c>
-      <c r="D64" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E64" s="28" t="n">
-        <v>-940</v>
-      </c>
-      <c r="F64" s="28" t="n">
-        <v>-818</v>
-      </c>
-      <c r="G64" s="28" t="n">
-        <v>-121</v>
-      </c>
-      <c r="H64" s="29" t="n">
-        <v>652</v>
-      </c>
-      <c r="I64" s="31" t="n">
-        <v>87.3</v>
-      </c>
-      <c r="J64" s="31" t="n">
-        <v>1830.2</v>
-      </c>
-      <c r="K64" s="31" t="n">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="65"/>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>07</t>
-        </is>
-      </c>
-      <c r="B66" s="3" t="inlineStr">
-        <is>
-          <t>섹터 시그널 종목 관찰</t>
-        </is>
-      </c>
-      <c r="C66" s="3" t="inlineStr"/>
-      <c r="D66" s="3" t="inlineStr"/>
-      <c r="E66" s="3" t="inlineStr"/>
-      <c r="F66" s="3" t="inlineStr"/>
-      <c r="G66" s="18" t="inlineStr">
-        <is>
-          <t>섹터 상태 x 수급 x 공매도·대차 x 촉매</t>
-        </is>
-      </c>
-      <c r="H66" s="3" t="inlineStr"/>
-      <c r="I66" s="3" t="inlineStr"/>
-      <c r="J66" s="3" t="inlineStr"/>
-      <c r="K66" s="3" t="inlineStr"/>
-    </row>
-    <row r="67">
-      <c r="A67" s="35" t="inlineStr">
-        <is>
-          <t>● 동반강세 — 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-      <c r="G67" s="3" t="inlineStr">
-        <is>
-          <t>● 수급유입 — 초기 유입형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="5" t="inlineStr">
-        <is>
-          <t>한화</t>
-        </is>
-      </c>
-      <c r="B68" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D68" s="31" t="inlineStr"/>
-      <c r="E68" s="31" t="inlineStr"/>
-      <c r="G68" s="31" t="inlineStr">
-        <is>
-          <t>해당 섹터·조건 충족 종목 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="31" customHeight="1" s="15">
-      <c r="A69" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +13억 순매수, 기관 +2억 순매수, 대차잔고 -52억 감소 — 화학(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="5" t="inlineStr">
-        <is>
-          <t>SK리츠</t>
-        </is>
-      </c>
-      <c r="B70" s="34" t="inlineStr">
-        <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="C70" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D70" s="31" t="inlineStr"/>
-      <c r="E70" s="31" t="inlineStr"/>
-    </row>
-    <row r="71" ht="31" customHeight="1" s="15">
-      <c r="A71" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +3억 순매수, 기관 +5억 순매수, 대차잔고 -7억 감소 — 부동산(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="31" customHeight="1" s="15">
-      <c r="A72" s="37" t="inlineStr">
-        <is>
-          <t>코람코라이프인프라리츠</t>
-        </is>
-      </c>
-      <c r="B72" s="34" t="inlineStr">
-        <is>
-          <t>부동산</t>
-        </is>
-      </c>
-      <c r="C72" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="D72" s="31" t="inlineStr"/>
-      <c r="E72" s="31" t="inlineStr"/>
-    </row>
-    <row r="73" ht="31" customHeight="1" s="15">
-      <c r="A73" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +0억 순매수, 기관 +3억 순매수, 대차잔고 -4억 감소 — 부동산(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="5" t="inlineStr">
-        <is>
-          <t>제주은행</t>
-        </is>
-      </c>
-      <c r="B74" s="34" t="inlineStr">
-        <is>
-          <t>금융</t>
-        </is>
-      </c>
-      <c r="C74" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D74" s="31" t="inlineStr"/>
-      <c r="E74" s="31" t="inlineStr"/>
-    </row>
-    <row r="75" ht="31" customHeight="1" s="15">
-      <c r="A75" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +0억 순매수, 대차잔고 0억 감소 — 금융(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="5" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="B76" s="34" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="C76" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="D76" s="31" t="inlineStr"/>
-      <c r="E76" s="31" t="inlineStr"/>
-    </row>
-    <row r="77" ht="31" customHeight="1" s="15">
-      <c r="A77" s="17" t="inlineStr">
-        <is>
-          <t>외국인 +716억 순매수, 기관 +652억 순매수 — 운송·창고(동반강세) 섹터 추세 지속형 상방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="78"/>
-    <row r="79">
-      <c r="A79" s="38" t="inlineStr">
-        <is>
-          <t>● 수급이탈 — 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G79" s="39" t="inlineStr">
-        <is>
-          <t>● 동반약세 — 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="31" customHeight="1" s="15">
-      <c r="A80" s="5" t="inlineStr">
-        <is>
-          <t>현대건설</t>
-        </is>
-      </c>
-      <c r="B80" s="34" t="inlineStr">
+      <c r="I79" s="42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J79" s="31" t="inlineStr"/>
+      <c r="K79" s="31" t="inlineStr"/>
+    </row>
+    <row r="80" ht="44.5" customHeight="1" s="15">
+      <c r="A80" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -449억 순매도, 기관 -423억 순매도, 대차잔고 +319억 증가, 공매도 누적 상위 등재 — 건설(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G80" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -1,286억 순매도, 기관 -518억 순매도, 대차잔고 +484억 증가, 공매도 누적 상위 등재 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="5" t="inlineStr">
+        <is>
+          <t>쓰리빌리언</t>
+        </is>
+      </c>
+      <c r="B81" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C81" s="40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D81" s="31" t="inlineStr"/>
+      <c r="E81" s="31" t="inlineStr"/>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>NAVER</t>
+        </is>
+      </c>
+      <c r="H81" s="34" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="I81" s="42" t="n">
+        <v>-4</v>
+      </c>
+      <c r="J81" s="31" t="inlineStr"/>
+      <c r="K81" s="31" t="inlineStr"/>
+    </row>
+    <row r="82" ht="44.5" customHeight="1" s="15">
+      <c r="A82" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -25억 순매도, 기관 -9억 순매도, 대차잔고 +11억 증가 — 일반서비스(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G82" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -231억 순매도, 기관 -1,096억 순매도, 대차잔고 +310억 증가, 공매도 누적 상위 등재 — IT 서비스(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>보로노이</t>
+        </is>
+      </c>
+      <c r="B83" s="34" t="inlineStr">
+        <is>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="C83" s="40" t="n">
+        <v>-3</v>
+      </c>
+      <c r="D83" s="31" t="inlineStr"/>
+      <c r="E83" s="31" t="inlineStr"/>
+      <c r="G83" s="5" t="inlineStr">
+        <is>
+          <t>POSCO홀딩스</t>
+        </is>
+      </c>
+      <c r="H83" s="34" t="inlineStr">
+        <is>
+          <t>금속</t>
+        </is>
+      </c>
+      <c r="I83" s="42" t="n">
+        <v>-3</v>
+      </c>
+      <c r="J83" s="31" t="inlineStr"/>
+      <c r="K83" s="31" t="inlineStr"/>
+    </row>
+    <row r="84" ht="44.5" customHeight="1" s="15">
+      <c r="A84" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -8억 순매도, 기관 -23억 순매도, 대차잔고 +260억 증가 — 일반서비스(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G84" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -270억 순매도, 기관 -274억 순매도, 대차잔고 +122억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="31" customHeight="1" s="15">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>대우건설</t>
+        </is>
+      </c>
+      <c r="B85" s="34" t="inlineStr">
         <is>
           <t>건설</t>
         </is>
       </c>
-      <c r="C80" s="40" t="n">
-        <v>-4</v>
-      </c>
-      <c r="D80" s="31" t="inlineStr"/>
-      <c r="E80" s="31" t="inlineStr"/>
-      <c r="G80" s="5" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="H80" s="41" t="inlineStr">
+      <c r="C85" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D85" s="31" t="inlineStr"/>
+      <c r="E85" s="31" t="inlineStr"/>
+      <c r="G85" s="5" t="inlineStr">
+        <is>
+          <t>현대모비스</t>
+        </is>
+      </c>
+      <c r="H85" s="41" t="inlineStr">
         <is>
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="I80" s="42" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J80" s="31" t="inlineStr"/>
-      <c r="K80" s="31" t="inlineStr"/>
-    </row>
-    <row r="81" ht="44.5" customHeight="1" s="15">
-      <c r="A81" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -768억 순매도, 기관 -574억 순매도, 대차잔고 +319억 증가, 공매도 누적 상위 등재 — 건설(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G81" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -1,925억 순매도, 기관 -689억 순매도, 대차잔고 +484억 증가, 공매도 누적 상위 등재 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="5" t="inlineStr">
-        <is>
-          <t>쓰리빌리언</t>
-        </is>
-      </c>
-      <c r="B82" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="C82" s="40" t="n">
+      <c r="I85" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="D82" s="31" t="inlineStr"/>
-      <c r="E82" s="31" t="inlineStr"/>
-      <c r="G82" s="5" t="inlineStr">
-        <is>
-          <t>NAVER</t>
-        </is>
-      </c>
-      <c r="H82" s="34" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="I82" s="42" t="n">
-        <v>-4</v>
-      </c>
-      <c r="J82" s="31" t="inlineStr"/>
-      <c r="K82" s="31" t="inlineStr"/>
-    </row>
-    <row r="83" ht="44.5" customHeight="1" s="15">
-      <c r="A83" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -25억 순매도, 기관 -9억 순매도, 대차잔고 +11억 증가 — 일반서비스(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G83" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -836억 순매도, 기관 -1,329억 순매도, 대차잔고 +310억 증가, 공매도 누적 상위 등재 — IT 서비스(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="5" t="inlineStr">
-        <is>
-          <t>보로노이</t>
-        </is>
-      </c>
-      <c r="B84" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="C84" s="40" t="n">
+      <c r="J85" s="31" t="inlineStr"/>
+      <c r="K85" s="31" t="inlineStr"/>
+    </row>
+    <row r="86" ht="44.5" customHeight="1" s="15">
+      <c r="A86" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -929억 순매도, 기관 -300억 순매도 — 건설(수급이탈) 섹터 상승 후 약화 관찰</t>
+        </is>
+      </c>
+      <c r="G86" s="17" t="inlineStr">
+        <is>
+          <t>외국인 -208억 순매도, 기관 -181억 순매도, 대차잔고 +76억 증가 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="5" t="inlineStr">
+        <is>
+          <t>GS건설</t>
+        </is>
+      </c>
+      <c r="B87" s="34" t="inlineStr">
+        <is>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="C87" s="40" t="n">
+        <v>-1</v>
+      </c>
+      <c r="D87" s="31" t="inlineStr"/>
+      <c r="E87" s="31" t="inlineStr"/>
+      <c r="G87" s="5" t="inlineStr">
+        <is>
+          <t>HLB</t>
+        </is>
+      </c>
+      <c r="H87" s="34" t="inlineStr">
+        <is>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="I87" s="42" t="n">
         <v>-3</v>
       </c>
-      <c r="D84" s="31" t="inlineStr"/>
-      <c r="E84" s="31" t="inlineStr"/>
-      <c r="G84" s="5" t="inlineStr">
-        <is>
-          <t>POSCO홀딩스</t>
-        </is>
-      </c>
-      <c r="H84" s="34" t="inlineStr">
-        <is>
-          <t>금속</t>
-        </is>
-      </c>
-      <c r="I84" s="42" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J84" s="31" t="inlineStr"/>
-      <c r="K84" s="31" t="inlineStr"/>
-    </row>
-    <row r="85" ht="44.5" customHeight="1" s="15">
-      <c r="A85" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -8억 순매도, 기관 -23억 순매도, 대차잔고 +260억 증가 — 일반서비스(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G85" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -270억 순매도, 기관 -274억 순매도, 대차잔고 +122억 증가 — 금속(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="31" customHeight="1" s="15">
-      <c r="A86" s="5" t="inlineStr">
-        <is>
-          <t>대우건설</t>
-        </is>
-      </c>
-      <c r="B86" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="C86" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D86" s="31" t="inlineStr"/>
-      <c r="E86" s="31" t="inlineStr"/>
-      <c r="G86" s="5" t="inlineStr">
-        <is>
-          <t>현대모비스</t>
-        </is>
-      </c>
-      <c r="H86" s="41" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
-        </is>
-      </c>
-      <c r="I86" s="42" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J86" s="31" t="inlineStr"/>
-      <c r="K86" s="31" t="inlineStr"/>
-    </row>
-    <row r="87" ht="44.5" customHeight="1" s="15">
-      <c r="A87" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -1,334억 순매도, 기관 -390억 순매도 — 건설(수급이탈) 섹터 상승 후 약화 관찰</t>
-        </is>
-      </c>
-      <c r="G87" s="17" t="inlineStr">
-        <is>
-          <t>외국인 -208억 순매도, 기관 -181억 순매도, 대차잔고 +76억 증가 — 운송장비·부품(동반약세) 섹터 약세 지속형 하방 관찰</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="inlineStr">
-        <is>
-          <t>GS건설</t>
-        </is>
-      </c>
-      <c r="B88" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="C88" s="40" t="n">
-        <v>-1</v>
-      </c>
-      <c r="D88" s="31" t="inlineStr"/>
-      <c r="E88" s="31" t="inlineStr"/>
-      <c r="G88" s="5" t="inlineStr">
-        <is>
-          <t>HLB</t>
-        </is>
-      </c>
-      <c r="H88" s="34" t="inlineStr">
-        <is>
-          <t>제약</t>
-        </is>
-      </c>
-      <c r="I88" s="42" t="n">
-        <v>-3</v>
-      </c>
-      <c r="J88" s="31" t="inlineStr"/>
-      <c r="K88" s="31" t="inlineStr"/>
-    </row>
-    <row r="89" ht="44.5" customHeight="1" s="15">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="J87" s="31" t="inlineStr"/>
+      <c r="K87" s="31" t="inlineStr"/>
+    </row>
+    <row r="88" ht="44.5" customHeight="1" s="15">
+      <c r="A88" s="17" t="inlineStr">
         <is>
           <t>외국인 -289억 순매도, 기관 -91억 순매도 — 건설(수급이탈) 섹터 상승 후 약화 관찰</t>
         </is>
       </c>
-      <c r="G89" s="17" t="inlineStr">
+      <c r="G88" s="17" t="inlineStr">
         <is>
           <t>외국인 -164억 순매도, 기관 -5억 순매도, 대차잔고 +143억 증가 — 제약(동반약세) 섹터 약세 지속형 하방 관찰</t>
         </is>
       </c>
     </row>
-    <row r="90"/>
-    <row r="91" ht="31" customHeight="1" s="15">
-      <c r="A91" s="43" t="inlineStr">
+    <row r="89"/>
+    <row r="90" ht="31" customHeight="1" s="15">
+      <c r="A90" s="43" t="inlineStr">
         <is>
           <t>현재 확보된 주간 브리핑 데이터 유니버스(순매수 상위 30 등재 · 공매도/대차 랭킹 · 주간 촉매 · 신호 섹터 시총 상위 10) 기준 — 전 시장 스크리닝 아님 · 관찰 우선순위이며 매매 권유 아님</t>
         </is>
       </c>
     </row>
-    <row r="92"/>
+    <row r="91"/>
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
+        <is>
+          <t>08</t>
+        </is>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>주간 시장 흐름</t>
+        </is>
+      </c>
+      <c r="C92" s="3" t="inlineStr"/>
+      <c r="D92" s="3" t="inlineStr"/>
+      <c r="E92" s="3" t="inlineStr"/>
+      <c r="F92" s="3" t="inlineStr"/>
+      <c r="G92" s="3" t="inlineStr"/>
+      <c r="H92" s="3" t="inlineStr"/>
+      <c r="I92" s="3" t="inlineStr"/>
+      <c r="J92" s="3" t="inlineStr"/>
+      <c r="K92" s="3" t="inlineStr"/>
+    </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
-        <is>
-          <t>08</t>
-        </is>
-      </c>
-      <c r="B93" s="3" t="inlineStr">
-        <is>
-          <t>주간 시장 흐름</t>
-        </is>
-      </c>
-      <c r="C93" s="3" t="inlineStr"/>
-      <c r="D93" s="3" t="inlineStr"/>
-      <c r="E93" s="3" t="inlineStr"/>
-      <c r="F93" s="3" t="inlineStr"/>
-      <c r="G93" s="3" t="inlineStr"/>
-      <c r="H93" s="3" t="inlineStr"/>
-      <c r="I93" s="3" t="inlineStr"/>
-      <c r="J93" s="3" t="inlineStr"/>
-      <c r="K93" s="3" t="inlineStr"/>
-    </row>
-    <row r="94">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>No.</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B93" s="4" t="inlineStr">
         <is>
           <t>Market Flow</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="15" customHeight="1" s="15">
+      <c r="A94" s="17" t="inlineStr">
+        <is>
+          <t>- 미국 필라델피아 반도체 지수의 연이은 급등세가 국내 증시의 반도체 및 AI 관련주로 강력하게 전이됨.</t>
         </is>
       </c>
     </row>
     <row r="95" ht="15" customHeight="1" s="15">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t>- 코스피는 기관의 강한 매수세에 힘입어 7000선을 회복하며 주간 상승 흐름을 보임.</t>
+          <t>- 주 초반 기관의 강한 매수세가 지수 7000선 회복을 견인했으나, 주 후반 외국인의 대규모 매도세가 유입되며 상단이 제한됨.</t>
         </is>
       </c>
     </row>
     <row r="96" ht="15" customHeight="1" s="15">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>- 미국 반도체주 강세가 국내 반도체 소부장 및 AI 밸류체인으로 확산되며 관련주가 지수 상승을 견인함.</t>
+          <t>- 반도체 수출 호조와 AI 데이터센터 관련 수주 소식이 시장의 핵심 상승 동력으로 작용함.</t>
         </is>
       </c>
     </row>
     <row r="97" ht="15" customHeight="1" s="15">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t>- 외국인은 9/23~9/24 대규모 매도세로 전환하며 수급 부담을 가중시켰고, 환율 변동성 확대가 시장의 상단을 제한함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="98" ht="15" customHeight="1" s="15">
-      <c r="A98" s="17" t="inlineStr">
-        <is>
-          <t>- 건설 섹터는 프로젝트 관련 불확실성과 악재가 부각되며 급락하는 등 섹터 간 양극화가 심화됨.</t>
-        </is>
-      </c>
-    </row>
-    <row r="99"/>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+          <t>- 건설 및 산업재 섹터는 프로젝트 불확실성과 산업재해 이슈로 인해 주 후반 급락하며 섹터별 차별화가 심화됨.</t>
+        </is>
+      </c>
+    </row>
+    <row r="98"/>
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>09</t>
         </is>
       </c>
-      <c r="B100" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>섹터·테마 흐름</t>
         </is>
       </c>
-      <c r="C100" s="3" t="inlineStr"/>
-      <c r="D100" s="3" t="inlineStr"/>
-      <c r="E100" s="3" t="inlineStr"/>
-      <c r="F100" s="3" t="inlineStr"/>
-      <c r="G100" s="3" t="inlineStr"/>
-      <c r="H100" s="3" t="inlineStr"/>
-      <c r="I100" s="3" t="inlineStr"/>
-      <c r="J100" s="3" t="inlineStr"/>
-      <c r="K100" s="3" t="inlineStr"/>
+      <c r="C99" s="3" t="inlineStr"/>
+      <c r="D99" s="3" t="inlineStr"/>
+      <c r="E99" s="3" t="inlineStr"/>
+      <c r="F99" s="3" t="inlineStr"/>
+      <c r="G99" s="3" t="inlineStr"/>
+      <c r="H99" s="3" t="inlineStr"/>
+      <c r="I99" s="3" t="inlineStr"/>
+      <c r="J99" s="3" t="inlineStr"/>
+      <c r="K99" s="3" t="inlineStr"/>
+    </row>
+    <row r="100" ht="15" customHeight="1" s="15">
+      <c r="A100" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체·AI: 미국 기술주 랠리에 힘입어 삼성전자, 디아이, LG전자 등 관련주가 주간 내내 강세를 유지함.</t>
+        </is>
+      </c>
     </row>
     <row r="101" ht="15" customHeight="1" s="15">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t>- 반도체/AI: 주초부터 지속적인 강세 흐름을 보이며 삼성전자와 디아이 등이 상승을 주도함.</t>
+          <t>- 건설·기계: 데이터센터 인프라 기대감으로 초반 상승했으나, 주 후반 대형 건설사 프로젝트 불확실성으로 급락하며 수급이 이탈함.</t>
         </is>
       </c>
     </row>
     <row r="102" ht="15" customHeight="1" s="15">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>- 건설/기계: 주중반 이후 악재가 부각되며 외국인과 기관의 동반 매도세로 급락함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="103" ht="15" customHeight="1" s="15">
-      <c r="A103" s="17" t="inlineStr">
-        <is>
-          <t>- 의료·정밀기기: 기관의 순매수가 집중되며 주간 내내 강세를 유지함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="104"/>
+          <t>- 에너지·금속: 국제유가 변동성과 환율 하락에 따른 수출 채산성 우려로 차익 실현 매물이 출회되며 약세를 보임.</t>
+        </is>
+      </c>
+    </row>
+    <row r="103"/>
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B104" s="3" t="inlineStr">
+        <is>
+          <t>주간 촉매 타임라인</t>
+        </is>
+      </c>
+      <c r="C104" s="3" t="inlineStr"/>
+      <c r="D104" s="3" t="inlineStr"/>
+      <c r="E104" s="3" t="inlineStr"/>
+      <c r="F104" s="3" t="inlineStr"/>
+      <c r="G104" s="3" t="inlineStr"/>
+      <c r="H104" s="3" t="inlineStr"/>
+      <c r="I104" s="3" t="inlineStr"/>
+      <c r="J104" s="18" t="inlineStr">
+        <is>
+          <t>등락률 = 주간 누적</t>
+        </is>
+      </c>
+      <c r="K104" s="3" t="inlineStr"/>
+    </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B105" s="3" t="inlineStr">
-        <is>
-          <t>주간 촉매 타임라인</t>
-        </is>
-      </c>
-      <c r="C105" s="3" t="inlineStr"/>
-      <c r="D105" s="3" t="inlineStr"/>
-      <c r="E105" s="3" t="inlineStr"/>
-      <c r="F105" s="3" t="inlineStr"/>
-      <c r="G105" s="3" t="inlineStr"/>
-      <c r="H105" s="3" t="inlineStr"/>
-      <c r="I105" s="3" t="inlineStr"/>
-      <c r="J105" s="18" t="inlineStr">
-        <is>
-          <t>등락률 = 주간 누적</t>
-        </is>
-      </c>
-      <c r="K105" s="3" t="inlineStr"/>
-    </row>
-    <row r="106">
-      <c r="A106" s="4" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>날짜</t>
         </is>
       </c>
-      <c r="B106" s="4" t="inlineStr">
+      <c r="B105" s="4" t="inlineStr">
         <is>
           <t>종목명</t>
         </is>
       </c>
-      <c r="C106" s="4" t="inlineStr">
+      <c r="C105" s="4" t="inlineStr">
         <is>
           <t>시장</t>
         </is>
       </c>
-      <c r="D106" s="4" t="inlineStr">
+      <c r="D105" s="4" t="inlineStr">
         <is>
           <t>섹터명</t>
         </is>
       </c>
-      <c r="E106" s="4" t="inlineStr">
+      <c r="E105" s="4" t="inlineStr">
         <is>
           <t>별점</t>
         </is>
       </c>
-      <c r="F106" s="4" t="inlineStr">
+      <c r="F105" s="4" t="inlineStr">
         <is>
           <t>등락률(%)</t>
         </is>
       </c>
-      <c r="G106" s="4" t="inlineStr">
+      <c r="G105" s="4" t="inlineStr">
         <is>
           <t>핵심 촉매</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="31" customHeight="1" s="15">
+      <c r="A106" s="31" t="inlineStr">
+        <is>
+          <t>2026-09-21</t>
+        </is>
+      </c>
+      <c r="B106" s="31" t="inlineStr">
+        <is>
+          <t>토마토시스템</t>
+        </is>
+      </c>
+      <c r="C106" s="31" t="inlineStr">
+        <is>
+          <t>KOSDAQ</t>
+        </is>
+      </c>
+      <c r="D106" s="34" t="inlineStr">
+        <is>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="E106" s="14" t="inlineStr">
+        <is>
+          <t>★★★★★</t>
+        </is>
+      </c>
+      <c r="F106" s="29" t="n">
+        <v>88.67</v>
+      </c>
+      <c r="G106" s="17" t="inlineStr">
+        <is>
+          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
@@ -3393,7 +3359,7 @@
       </c>
       <c r="B107" s="31" t="inlineStr">
         <is>
-          <t>토마토시스템</t>
+          <t>비트플래닛</t>
         </is>
       </c>
       <c r="C107" s="31" t="inlineStr">
@@ -3412,11 +3378,11 @@
         </is>
       </c>
       <c r="F107" s="29" t="n">
-        <v>88.67</v>
+        <v>34.77</v>
       </c>
       <c r="G107" s="17" t="inlineStr">
         <is>
-          <t>투자한 미국 보험사의 사업 최종 승인이라는 확실한 대형 호재로 상한가를 기록함.</t>
+          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3394,7 @@
       </c>
       <c r="B108" s="31" t="inlineStr">
         <is>
-          <t>비트플래닛</t>
+          <t>시그네틱스</t>
         </is>
       </c>
       <c r="C108" s="31" t="inlineStr">
@@ -3438,7 +3404,7 @@
       </c>
       <c r="D108" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -3447,11 +3413,11 @@
         </is>
       </c>
       <c r="F108" s="29" t="n">
-        <v>34.77</v>
+        <v>29.93</v>
       </c>
       <c r="G108" s="17" t="inlineStr">
         <is>
-          <t>비트코인 가격 반등 및 규제 정비 기대감이라는 시장 모멘텀으로 상한가를 기록함.</t>
+          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
         </is>
       </c>
     </row>
@@ -3463,7 +3429,7 @@
       </c>
       <c r="B109" s="31" t="inlineStr">
         <is>
-          <t>시그네틱스</t>
+          <t>인벤테라</t>
         </is>
       </c>
       <c r="C109" s="31" t="inlineStr">
@@ -3473,7 +3439,7 @@
       </c>
       <c r="D109" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -3482,11 +3448,11 @@
         </is>
       </c>
       <c r="F109" s="29" t="n">
-        <v>29.93</v>
+        <v>19.61</v>
       </c>
       <c r="G109" s="17" t="inlineStr">
         <is>
-          <t>AI 시장 확대에 따른 첨단 패키징 수요 급증이라는 산업적 호재로 상한가를 기록함.</t>
+          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
         </is>
       </c>
     </row>
@@ -3498,30 +3464,30 @@
       </c>
       <c r="B110" s="31" t="inlineStr">
         <is>
-          <t>인벤테라</t>
+          <t>디아이</t>
         </is>
       </c>
       <c r="C110" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D110" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>의료·정밀기기</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F110" s="29" t="n">
-        <v>19.61</v>
+        <v>17.2</v>
       </c>
       <c r="G110" s="17" t="inlineStr">
         <is>
-          <t>조영제 임상 3상 결과 발표라는 제약·바이오 분야의 핵심적 성과가 주가 급등을 견인함.</t>
+          <t>AI 서버 투자 확대에 따른 반도체 장비 수요 증가라는 산업적 호재가 주가에 강하게 반영됨.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3499,7 @@
       </c>
       <c r="B111" s="31" t="inlineStr">
         <is>
-          <t>디아이</t>
+          <t>한섬</t>
         </is>
       </c>
       <c r="C111" s="31" t="inlineStr">
@@ -3543,7 +3509,7 @@
       </c>
       <c r="D111" s="34" t="inlineStr">
         <is>
-          <t>의료·정밀기기</t>
+          <t>섬유·의류</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
@@ -3552,11 +3518,11 @@
         </is>
       </c>
       <c r="F111" s="29" t="n">
-        <v>17.2</v>
+        <v>12.18</v>
       </c>
       <c r="G111" s="17" t="inlineStr">
         <is>
-          <t>AI 서버 투자 확대에 따른 반도체 장비 수요 증가라는 산업적 호재가 주가에 강하게 반영됨.</t>
+          <t>자사주 매입·소각 및 배당 확대 등 구체적인 주주환원 정책 발표가 주가 상승을 이끎.</t>
         </is>
       </c>
     </row>
@@ -3568,7 +3534,7 @@
       </c>
       <c r="B112" s="31" t="inlineStr">
         <is>
-          <t>한섬</t>
+          <t>삼성물산</t>
         </is>
       </c>
       <c r="C112" s="31" t="inlineStr">
@@ -3578,7 +3544,7 @@
       </c>
       <c r="D112" s="34" t="inlineStr">
         <is>
-          <t>섬유·의류</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
@@ -3587,46 +3553,46 @@
         </is>
       </c>
       <c r="F112" s="29" t="n">
-        <v>12.18</v>
+        <v>4.39</v>
       </c>
       <c r="G112" s="17" t="inlineStr">
         <is>
-          <t>자사주 매입·소각 및 배당 확대 등 구체적인 주주환원 정책 발표가 주가 상승을 이끎.</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" ht="31" customHeight="1" s="15">
+          <t>1.8조 원 규모의 대형 재개발 사업 시공권 확보라는 확정적 수주 공시가 주가를 견인함.</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="15" customHeight="1" s="15">
       <c r="A113" s="31" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B113" s="31" t="inlineStr">
         <is>
-          <t>삼성물산</t>
+          <t>노타</t>
         </is>
       </c>
       <c r="C113" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D113" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>IT 서비스</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F113" s="29" t="n">
-        <v>4.39</v>
+        <v>16.44</v>
       </c>
       <c r="G113" s="17" t="inlineStr">
         <is>
-          <t>1.8조 원 규모의 대형 재개발 사업 시공권 확보라는 확정적 수주 공시가 주가를 견인함.</t>
+          <t>퀄컴 칩 기반 휴머노이드 AI 가속 기술 부각.</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3604,7 @@
       </c>
       <c r="B114" s="31" t="inlineStr">
         <is>
-          <t>노타</t>
+          <t>더블유에스아이</t>
         </is>
       </c>
       <c r="C114" s="31" t="inlineStr">
@@ -3648,7 +3614,7 @@
       </c>
       <c r="D114" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>유통</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -3657,11 +3623,11 @@
         </is>
       </c>
       <c r="F114" s="29" t="n">
-        <v>16.44</v>
+        <v>14.05</v>
       </c>
       <c r="G114" s="17" t="inlineStr">
         <is>
-          <t>퀄컴 칩 기반 휴머노이드 AI 가속 기술 부각.</t>
+          <t>자회사 수술용 로봇의 유럽 19개국 특허 등록.</t>
         </is>
       </c>
     </row>
@@ -3673,7 +3639,7 @@
       </c>
       <c r="B115" s="31" t="inlineStr">
         <is>
-          <t>더블유에스아이</t>
+          <t>셀리드</t>
         </is>
       </c>
       <c r="C115" s="31" t="inlineStr">
@@ -3683,7 +3649,7 @@
       </c>
       <c r="D115" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -3692,15 +3658,15 @@
         </is>
       </c>
       <c r="F115" s="29" t="n">
-        <v>14.05</v>
+        <v>13.02</v>
       </c>
       <c r="G115" s="17" t="inlineStr">
         <is>
-          <t>자회사 수술용 로봇의 유럽 19개국 특허 등록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="116" ht="15" customHeight="1" s="15">
+          <t>최대주주 변경을 수반하는 제3자 배정 유상증자 결정.</t>
+        </is>
+      </c>
+    </row>
+    <row r="116" ht="31" customHeight="1" s="15">
       <c r="A116" s="31" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -3708,30 +3674,30 @@
       </c>
       <c r="B116" s="31" t="inlineStr">
         <is>
-          <t>셀리드</t>
+          <t>코리아써키트</t>
         </is>
       </c>
       <c r="C116" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D116" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F116" s="29" t="n">
-        <v>13.02</v>
+        <v>24.9</v>
       </c>
       <c r="G116" s="17" t="inlineStr">
         <is>
-          <t>최대주주 변경을 수반하는 제3자 배정 유상증자 결정.</t>
+          <t>미국 CPU 관련주 급등에 따른 반도체 기판 수요 확대 기대감.</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3709,7 @@
       </c>
       <c r="B117" s="31" t="inlineStr">
         <is>
-          <t>코리아써키트</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C117" s="31" t="inlineStr">
@@ -3762,11 +3728,11 @@
         </is>
       </c>
       <c r="F117" s="29" t="n">
-        <v>24.9</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="G117" s="17" t="inlineStr">
         <is>
-          <t>미국 CPU 관련주 급등에 따른 반도체 기판 수요 확대 기대감.</t>
+          <t>AI 서버용 MLCC 및 FC-BGA 공급 부족에 따른 실적 기대감.</t>
         </is>
       </c>
     </row>
@@ -3778,7 +3744,7 @@
       </c>
       <c r="B118" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C118" s="31" t="inlineStr">
@@ -3788,7 +3754,7 @@
       </c>
       <c r="D118" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -3797,15 +3763,15 @@
         </is>
       </c>
       <c r="F118" s="29" t="n">
-        <v>8.140000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="G118" s="17" t="inlineStr">
         <is>
-          <t>AI 서버용 MLCC 및 FC-BGA 공급 부족에 따른 실적 기대감.</t>
-        </is>
-      </c>
-    </row>
-    <row r="119" ht="31" customHeight="1" s="15">
+          <t>원/달러 환율 하락에 따른 외화 부채 감소 및 재무 개선 기대.</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="15" customHeight="1" s="15">
       <c r="A119" s="31" t="inlineStr">
         <is>
           <t>2026-09-22</t>
@@ -3813,7 +3779,7 @@
       </c>
       <c r="B119" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C119" s="31" t="inlineStr">
@@ -3823,7 +3789,7 @@
       </c>
       <c r="D119" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -3832,28 +3798,28 @@
         </is>
       </c>
       <c r="F119" s="29" t="n">
-        <v>8.06</v>
+        <v>6.19</v>
       </c>
       <c r="G119" s="17" t="inlineStr">
         <is>
-          <t>원/달러 환율 하락에 따른 외화 부채 감소 및 재무 개선 기대.</t>
-        </is>
-      </c>
-    </row>
-    <row r="120" ht="15" customHeight="1" s="15">
+          <t>엔비디아 AI 데이터센터용 냉각 솔루션 규격 승인 획득.</t>
+        </is>
+      </c>
+    </row>
+    <row r="120" ht="31" customHeight="1" s="15">
       <c r="A120" s="31" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B120" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="C120" s="31" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="D120" s="34" t="inlineStr">
@@ -3863,15 +3829,15 @@
       </c>
       <c r="E120" s="14" t="inlineStr">
         <is>
-          <t>★★★★</t>
+          <t>★★★★★</t>
         </is>
       </c>
       <c r="F120" s="29" t="n">
-        <v>6.19</v>
+        <v>33.44</v>
       </c>
       <c r="G120" s="17" t="inlineStr">
         <is>
-          <t>엔비디아 AI 데이터센터용 냉각 솔루션 규격 승인 획득.</t>
+          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
         </is>
       </c>
     </row>
@@ -3883,7 +3849,7 @@
       </c>
       <c r="B121" s="31" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>쓰리빌리언</t>
         </is>
       </c>
       <c r="C121" s="31" t="inlineStr">
@@ -3893,7 +3859,7 @@
       </c>
       <c r="D121" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>일반서비스</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -3902,11 +3868,11 @@
         </is>
       </c>
       <c r="F121" s="29" t="n">
-        <v>33.44</v>
+        <v>18.84</v>
       </c>
       <c r="G121" s="17" t="inlineStr">
         <is>
-          <t>메타의 AI 에이전트 '뮤즈' 흥행에 따른 eSSD 컨트롤러 공급 수혜 기대감.</t>
+          <t>한국형 ARPA-H 희귀질환 치료제 개발 국책과제 공동연구기관 선정.</t>
         </is>
       </c>
     </row>
@@ -3918,7 +3884,7 @@
       </c>
       <c r="B122" s="31" t="inlineStr">
         <is>
-          <t>쓰리빌리언</t>
+          <t>우리넷</t>
         </is>
       </c>
       <c r="C122" s="31" t="inlineStr">
@@ -3928,7 +3894,7 @@
       </c>
       <c r="D122" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -3937,11 +3903,11 @@
         </is>
       </c>
       <c r="F122" s="29" t="n">
-        <v>18.84</v>
+        <v>18.59</v>
       </c>
       <c r="G122" s="17" t="inlineStr">
         <is>
-          <t>한국형 ARPA-H 희귀질환 치료제 개발 국책과제 공동연구기관 선정.</t>
+          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
         </is>
       </c>
     </row>
@@ -3953,17 +3919,17 @@
       </c>
       <c r="B123" s="31" t="inlineStr">
         <is>
-          <t>우리넷</t>
+          <t>KSS해운</t>
         </is>
       </c>
       <c r="C123" s="31" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="D123" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>운송·창고</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -3972,15 +3938,15 @@
         </is>
       </c>
       <c r="F123" s="29" t="n">
-        <v>18.59</v>
+        <v>16.37</v>
       </c>
       <c r="G123" s="17" t="inlineStr">
         <is>
-          <t>양자암호 전송장비 수요 확대 및 실적 턴어라운드 기대감으로 상한가 기록.</t>
-        </is>
-      </c>
-    </row>
-    <row r="124" ht="31" customHeight="1" s="15">
+          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
+        </is>
+      </c>
+    </row>
+    <row r="124" ht="44.5" customHeight="1" s="15">
       <c r="A124" s="31" t="inlineStr">
         <is>
           <t>2026-09-23</t>
@@ -3988,7 +3954,7 @@
       </c>
       <c r="B124" s="31" t="inlineStr">
         <is>
-          <t>KSS해운</t>
+          <t>삼성전자 (2회)</t>
         </is>
       </c>
       <c r="C124" s="31" t="inlineStr">
@@ -3998,20 +3964,21 @@
       </c>
       <c r="D124" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
         <is>
-          <t>★★★★★</t>
+          <t>★★★★</t>
         </is>
       </c>
       <c r="F124" s="29" t="n">
-        <v>16.37</v>
+        <v>10.19</v>
       </c>
       <c r="G124" s="17" t="inlineStr">
         <is>
-          <t>약 200억 원 규모의 대규모 자사주 매입 결정에 따른 주주가치 제고 기대감.</t>
+          <t>국가반도체연구소 설립 가시화 및 HBM4·파운드리 부문 중장기 성장성 부각.
+(09-21) 반도체 수출 호조 및 특별배당 기대감 등 실질적 모멘텀이 복합적으로 작용함.</t>
         </is>
       </c>
     </row>
@@ -4050,231 +4017,141 @@
         </is>
       </c>
     </row>
-    <row r="126" ht="71.5" customHeight="1" s="15">
-      <c r="A126" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B126" s="31" t="inlineStr">
-        <is>
-          <t>삼성전자 (3회)</t>
-        </is>
-      </c>
-      <c r="C126" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D126" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="E126" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F126" s="29" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="G126" s="17" t="inlineStr">
-        <is>
-          <t>AI 메모리 호황 및 성과급 지급 기대감에 기관의 대규모 매수세가 집중되었습니다.
-(09-21) 반도체 수출 호조 및 특별배당 기대감 등 실질적 모멘텀이 복합적으로 작용함.
-(09-23) 국가반도체연구소 설립 가시화 및 HBM4·파운드리 부문 중장기 성장성 부각.</t>
-        </is>
-      </c>
-    </row>
-    <row r="127" ht="31" customHeight="1" s="15">
-      <c r="A127" s="31" t="inlineStr">
-        <is>
-          <t>2026-09-24</t>
-        </is>
-      </c>
-      <c r="B127" s="31" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
-        </is>
-      </c>
-      <c r="C127" s="31" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="D127" s="34" t="inlineStr">
-        <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="E127" s="14" t="inlineStr">
-        <is>
-          <t>★★★★</t>
-        </is>
-      </c>
-      <c r="F127" s="29" t="n">
-        <v>8.539999999999999</v>
-      </c>
-      <c r="G127" s="17" t="inlineStr">
-        <is>
-          <t>외국인과 기관의 동반 순매수 유입과 그룹사 차원의 AI 전략 강화가 주가 상승을 이끌었습니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="128"/>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126"/>
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B129" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>다음 주 프리뷰</t>
         </is>
       </c>
-      <c r="C129" s="3" t="inlineStr"/>
-      <c r="D129" s="3" t="inlineStr"/>
-      <c r="E129" s="3" t="inlineStr"/>
-      <c r="F129" s="3" t="inlineStr"/>
-      <c r="G129" s="3" t="inlineStr"/>
-      <c r="H129" s="3" t="inlineStr"/>
-      <c r="I129" s="3" t="inlineStr"/>
-      <c r="J129" s="3" t="inlineStr"/>
-      <c r="K129" s="3" t="inlineStr"/>
+      <c r="C127" s="3" t="inlineStr"/>
+      <c r="D127" s="3" t="inlineStr"/>
+      <c r="E127" s="3" t="inlineStr"/>
+      <c r="F127" s="3" t="inlineStr"/>
+      <c r="G127" s="3" t="inlineStr"/>
+      <c r="H127" s="3" t="inlineStr"/>
+      <c r="I127" s="3" t="inlineStr"/>
+      <c r="J127" s="3" t="inlineStr"/>
+      <c r="K127" s="3" t="inlineStr"/>
+    </row>
+    <row r="128" ht="15" customHeight="1" s="15">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>- 반도체 및 AI 모멘텀 지속 시 지수 7000선 안착 및 추가 상승 시도</t>
+        </is>
+      </c>
+    </row>
+    <row r="129" ht="15" customHeight="1" s="15">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>- 외국인 매도세 지속 및 매크로 지표 부진 시 단기 조정 가능성</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1" s="15">
       <c r="A130" s="17" t="inlineStr">
         <is>
-          <t>- 반도체 및 AI 관련주로 외국인 수급이 재유입되면 지수 추가 상승 시도</t>
+          <t>- 외국인의 반도체 섹터 순매수 전환 여부</t>
         </is>
       </c>
     </row>
     <row r="131" ht="15" customHeight="1" s="15">
       <c r="A131" s="17" t="inlineStr">
         <is>
-          <t>- 미-중 정상회담 기대감이 글로벌 공급망 우려를 완화하면 수출주 중심의 반등</t>
+          <t>- 미국 신규 실업수당청구건수 (9/24 21:30 KST)</t>
         </is>
       </c>
     </row>
     <row r="132" ht="15" customHeight="1" s="15">
       <c r="A132" s="17" t="inlineStr">
         <is>
-          <t>- 외국인의 대규모 매도세가 전기·전자 섹터까지 확산되면 지수 하방 압력 확대</t>
+          <t>- 미국 내구재 수주 (9/25 21:30 KST)</t>
         </is>
       </c>
     </row>
     <row r="133" ht="15" customHeight="1" s="15">
       <c r="A133" s="17" t="inlineStr">
         <is>
-          <t>- 중동 지정학적 리스크 고조로 유가 급등 시 인플레이션 우려 재점화</t>
-        </is>
-      </c>
-    </row>
-    <row r="134" ht="15" customHeight="1" s="15">
-      <c r="A134" s="17" t="inlineStr">
-        <is>
-          <t>- 외국인의 전기·전자 섹터 순매수 지속 여부와 환율의 1,360원대 안착 여부</t>
-        </is>
-      </c>
-    </row>
-    <row r="135" ht="15" customHeight="1" s="15">
-      <c r="A135" s="17" t="inlineStr">
-        <is>
-          <t>- 10/1 미국 ISM 제조업 PMI</t>
-        </is>
-      </c>
-    </row>
-    <row r="136" ht="15" customHeight="1" s="15">
-      <c r="A136" s="17" t="inlineStr">
-        <is>
-          <t>- 9/29 한국 기업심리지수</t>
-        </is>
-      </c>
-    </row>
-    <row r="137" ht="15" customHeight="1" s="15">
-      <c r="A137" s="17" t="inlineStr">
-        <is>
-          <t>- 10/1 한국 수출 전년대비</t>
+          <t>- 한국 수출입 전년대비 (10/1 09:00 KST)</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="73">
-    <mergeCell ref="A77:E77"/>
-    <mergeCell ref="A83:E83"/>
+  <mergeCells count="69">
+    <mergeCell ref="G105:K105"/>
     <mergeCell ref="A1:G2"/>
-    <mergeCell ref="A73:E73"/>
+    <mergeCell ref="A130:K130"/>
     <mergeCell ref="A39:K39"/>
-    <mergeCell ref="G81:K81"/>
-    <mergeCell ref="A130:K130"/>
+    <mergeCell ref="A82:E82"/>
+    <mergeCell ref="G86:K86"/>
     <mergeCell ref="G115:K115"/>
     <mergeCell ref="G117:K117"/>
     <mergeCell ref="G106:K106"/>
     <mergeCell ref="G120:K120"/>
-    <mergeCell ref="A98:K98"/>
     <mergeCell ref="G67:K67"/>
     <mergeCell ref="G107:K107"/>
-    <mergeCell ref="G126:K126"/>
-    <mergeCell ref="A103:K103"/>
+    <mergeCell ref="A88:E88"/>
+    <mergeCell ref="A94:K94"/>
+    <mergeCell ref="A70:E70"/>
     <mergeCell ref="A132:K132"/>
-    <mergeCell ref="A79:E79"/>
-    <mergeCell ref="B94:K94"/>
-    <mergeCell ref="A69:E69"/>
-    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="G82:K82"/>
+    <mergeCell ref="A78:E78"/>
+    <mergeCell ref="G116:K116"/>
     <mergeCell ref="G122:K122"/>
-    <mergeCell ref="G116:K116"/>
     <mergeCell ref="G125:K125"/>
     <mergeCell ref="I1:K1"/>
-    <mergeCell ref="A41:K41"/>
+    <mergeCell ref="A128:K128"/>
+    <mergeCell ref="G66:K66"/>
     <mergeCell ref="G112:K112"/>
-    <mergeCell ref="A137:K137"/>
-    <mergeCell ref="A75:E75"/>
+    <mergeCell ref="A84:E84"/>
+    <mergeCell ref="A90:K90"/>
+    <mergeCell ref="A66:E66"/>
     <mergeCell ref="A133:K133"/>
-    <mergeCell ref="A89:E89"/>
+    <mergeCell ref="A74:E74"/>
+    <mergeCell ref="A80:E80"/>
     <mergeCell ref="G118:K118"/>
-    <mergeCell ref="G87:K87"/>
-    <mergeCell ref="G127:K127"/>
-    <mergeCell ref="A136:K136"/>
-    <mergeCell ref="G68:K68"/>
-    <mergeCell ref="G83:K83"/>
+    <mergeCell ref="G78:K78"/>
+    <mergeCell ref="G121:K121"/>
     <mergeCell ref="G34:K34"/>
+    <mergeCell ref="B93:K93"/>
+    <mergeCell ref="A86:E86"/>
     <mergeCell ref="A101:K101"/>
     <mergeCell ref="G108:K108"/>
-    <mergeCell ref="G121:K121"/>
+    <mergeCell ref="G84:K84"/>
+    <mergeCell ref="A76:E76"/>
     <mergeCell ref="A95:K95"/>
-    <mergeCell ref="A71:E71"/>
     <mergeCell ref="G33:K33"/>
-    <mergeCell ref="G89:K89"/>
-    <mergeCell ref="A85:E85"/>
     <mergeCell ref="G124:K124"/>
+    <mergeCell ref="A129:K129"/>
+    <mergeCell ref="G80:K80"/>
     <mergeCell ref="G114:K114"/>
     <mergeCell ref="G110:K110"/>
-    <mergeCell ref="G79:K79"/>
     <mergeCell ref="G123:K123"/>
+    <mergeCell ref="G88:K88"/>
     <mergeCell ref="A4:B4"/>
-    <mergeCell ref="A91:K91"/>
     <mergeCell ref="A97:K97"/>
-    <mergeCell ref="G35:K35"/>
+    <mergeCell ref="A131:K131"/>
     <mergeCell ref="I2:K2"/>
-    <mergeCell ref="A81:E81"/>
+    <mergeCell ref="A100:K100"/>
     <mergeCell ref="G113:K113"/>
     <mergeCell ref="A96:K96"/>
-    <mergeCell ref="A131:K131"/>
+    <mergeCell ref="A72:E72"/>
     <mergeCell ref="G109:K109"/>
-    <mergeCell ref="A135:K135"/>
-    <mergeCell ref="G85:K85"/>
-    <mergeCell ref="A134:K134"/>
     <mergeCell ref="G119:K119"/>
     <mergeCell ref="G32:K32"/>
-    <mergeCell ref="B38:K38"/>
+    <mergeCell ref="A38:K38"/>
+    <mergeCell ref="A68:E68"/>
     <mergeCell ref="G31:K31"/>
     <mergeCell ref="C4:K4"/>
     <mergeCell ref="A102:K102"/>
     <mergeCell ref="A40:K40"/>
-    <mergeCell ref="A67:E67"/>
     <mergeCell ref="G111:K111"/>
+    <mergeCell ref="B37:K37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4286,7 +4163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L36"/>
+  <dimension ref="A1:L32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelCol="0"/>
   <cols>
     <col width="18.5" customWidth="1" style="15" min="1" max="1"/>
@@ -4316,7 +4193,7 @@
       </c>
       <c r="K1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21 ~ 2026-09-24</t>
+          <t>2026-09-21 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -4429,171 +4306,171 @@
     <row r="6">
       <c r="A6" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="B6" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
+          <t>와이즈플래닛컴퍼니</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="inlineStr"/>
       <c r="C6" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>화학</t>
         </is>
       </c>
       <c r="D6" s="45" t="n">
-        <v>2368</v>
+        <v>-91</v>
       </c>
       <c r="E6" s="45" t="n">
-        <v>2757</v>
-      </c>
-      <c r="F6" s="46" t="n">
-        <v>-389</v>
+        <v>-5</v>
+      </c>
+      <c r="F6" s="45" t="n">
+        <v>-86</v>
       </c>
       <c r="G6" s="46" t="n">
-        <v>-2364</v>
-      </c>
-      <c r="H6" s="47" t="n">
-        <v>445.1</v>
-      </c>
-      <c r="I6" s="47" t="n">
-        <v>28532.1</v>
-      </c>
-      <c r="J6" s="48" t="n">
-        <v>716.2</v>
-      </c>
-      <c r="K6" s="49" t="n">
-        <v>12.75</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="H6" s="47" t="inlineStr"/>
+      <c r="I6" s="47" t="inlineStr"/>
+      <c r="J6" s="48" t="inlineStr"/>
+      <c r="K6" s="49" t="inlineStr"/>
       <c r="L6" s="50" t="n">
-        <v>-9.68</v>
+        <v>-5.26</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="31" t="inlineStr">
         <is>
-          <t>와이즈플래닛컴퍼니</t>
-        </is>
-      </c>
-      <c r="B7" s="30" t="inlineStr"/>
+          <t>신한지주</t>
+        </is>
+      </c>
+      <c r="B7" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
       <c r="C7" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D7" s="46" t="n">
-        <v>-183</v>
-      </c>
-      <c r="E7" s="46" t="n">
-        <v>-11</v>
-      </c>
-      <c r="F7" s="46" t="n">
-        <v>-172</v>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D7" s="45" t="n">
+        <v>-93</v>
+      </c>
+      <c r="E7" s="45" t="n">
+        <v>-432</v>
+      </c>
+      <c r="F7" s="51" t="n">
+        <v>339</v>
       </c>
       <c r="G7" s="51" t="n">
+        <v>97</v>
+      </c>
+      <c r="H7" s="47" t="n">
+        <v>324.4</v>
+      </c>
+      <c r="I7" s="47" t="n">
+        <v>7455.8</v>
+      </c>
+      <c r="J7" s="52" t="n">
+        <v>344.1</v>
+      </c>
+      <c r="K7" s="53" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="L7" s="50" t="n">
+        <v>-6.3</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="31" t="inlineStr">
+        <is>
+          <t>하나금융지주</t>
+        </is>
+      </c>
+      <c r="B8" s="30" t="inlineStr">
+        <is>
+          <t>KOSPI</t>
+        </is>
+      </c>
+      <c r="C8" s="34" t="inlineStr">
+        <is>
+          <t>기타금융</t>
+        </is>
+      </c>
+      <c r="D8" s="45" t="n">
+        <v>-48</v>
+      </c>
+      <c r="E8" s="45" t="n">
+        <v>-333</v>
+      </c>
+      <c r="F8" s="51" t="n">
+        <v>285</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>46</v>
+      </c>
+      <c r="H8" s="47" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="I8" s="47" t="n">
+        <v>7059.1</v>
+      </c>
+      <c r="J8" s="52" t="n">
+        <v>506.1</v>
+      </c>
+      <c r="K8" s="49" t="n">
         <v>0</v>
       </c>
-      <c r="H7" s="47" t="inlineStr"/>
-      <c r="I7" s="47" t="inlineStr"/>
-      <c r="J7" s="52" t="inlineStr"/>
-      <c r="K7" s="53" t="inlineStr"/>
-      <c r="L7" s="50" t="n">
-        <v>-5.03</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>대한항공</t>
-        </is>
-      </c>
-      <c r="B8" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C8" s="34" t="inlineStr">
-        <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D8" s="45" t="n">
-        <v>1291</v>
-      </c>
-      <c r="E8" s="45" t="n">
-        <v>687</v>
-      </c>
-      <c r="F8" s="45" t="n">
-        <v>604</v>
-      </c>
-      <c r="G8" s="46" t="n">
-        <v>-1266</v>
-      </c>
-      <c r="H8" s="47" t="n">
-        <v>67.7</v>
-      </c>
-      <c r="I8" s="47" t="n">
-        <v>1997.5</v>
-      </c>
-      <c r="J8" s="48" t="n">
-        <v>248.8</v>
-      </c>
-      <c r="K8" s="49" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="L8" s="54" t="n">
-        <v>-1.9</v>
+      <c r="L8" s="50" t="n">
+        <v>-6.82</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="31" t="inlineStr">
         <is>
-          <t>신한지주</t>
+          <t>메가터치</t>
         </is>
       </c>
       <c r="B9" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>-93</v>
-      </c>
-      <c r="E9" s="46" t="n">
-        <v>-432</v>
-      </c>
-      <c r="F9" s="45" t="n">
-        <v>339</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D9" s="51" t="n">
+        <v>45</v>
+      </c>
+      <c r="E9" s="51" t="n">
+        <v>44</v>
+      </c>
+      <c r="F9" s="51" t="n">
+        <v>1</v>
       </c>
       <c r="G9" s="45" t="n">
-        <v>97</v>
+        <v>-43</v>
       </c>
       <c r="H9" s="47" t="n">
-        <v>324.4</v>
+        <v>2.8</v>
       </c>
       <c r="I9" s="47" t="n">
-        <v>7455.8</v>
-      </c>
-      <c r="J9" s="48" t="n">
-        <v>344.1</v>
-      </c>
-      <c r="K9" s="55" t="n">
-        <v>-0.9</v>
+        <v>52.9</v>
+      </c>
+      <c r="J9" s="52" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="K9" s="54" t="n">
+        <v>27.22</v>
       </c>
       <c r="L9" s="50" t="n">
-        <v>-5.81</v>
+        <v>-6.29</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B10" s="30" t="inlineStr">
@@ -4603,85 +4480,85 @@
       </c>
       <c r="C10" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D10" s="45" t="n">
-        <v>644</v>
-      </c>
-      <c r="E10" s="45" t="n">
-        <v>650</v>
-      </c>
-      <c r="F10" s="46" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G10" s="46" t="n">
-        <v>-625</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D10" s="51" t="n">
+        <v>49</v>
+      </c>
+      <c r="E10" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="51" t="n">
+        <v>49</v>
+      </c>
+      <c r="G10" s="45" t="n">
+        <v>-50</v>
       </c>
       <c r="H10" s="47" t="n">
-        <v>157</v>
+        <v>1.1</v>
       </c>
       <c r="I10" s="47" t="n">
-        <v>9939.5</v>
-      </c>
-      <c r="J10" s="48" t="n">
-        <v>2396.1</v>
-      </c>
-      <c r="K10" s="49" t="n">
-        <v>18.76</v>
-      </c>
-      <c r="L10" s="50" t="n">
-        <v>-9.91</v>
+        <v>103.7</v>
+      </c>
+      <c r="J10" s="52" t="n">
+        <v>25.6</v>
+      </c>
+      <c r="K10" s="54" t="n">
+        <v>33.94</v>
+      </c>
+      <c r="L10" s="55" t="n">
+        <v>-3.51</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="31" t="inlineStr">
         <is>
-          <t>하나금융지주</t>
+          <t>지엔씨에너지</t>
         </is>
       </c>
       <c r="B11" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D11" s="46" t="n">
-        <v>-48</v>
-      </c>
-      <c r="E11" s="46" t="n">
-        <v>-333</v>
-      </c>
-      <c r="F11" s="45" t="n">
-        <v>285</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D11" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="E11" s="45" t="n">
+        <v>-23</v>
+      </c>
+      <c r="F11" s="51" t="n">
+        <v>22</v>
       </c>
       <c r="G11" s="45" t="n">
-        <v>46</v>
+        <v>-5</v>
       </c>
       <c r="H11" s="47" t="n">
-        <v>103.6</v>
+        <v>34.2</v>
       </c>
       <c r="I11" s="47" t="n">
-        <v>7059.1</v>
-      </c>
-      <c r="J11" s="48" t="n">
-        <v>506.1</v>
-      </c>
-      <c r="K11" s="53" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="50" t="n">
-        <v>-6.58</v>
+        <v>723.6</v>
+      </c>
+      <c r="J11" s="52" t="n">
+        <v>31.5</v>
+      </c>
+      <c r="K11" s="54" t="n">
+        <v>3.89</v>
+      </c>
+      <c r="L11" s="55" t="n">
+        <v>-3.39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="31" t="inlineStr">
         <is>
-          <t>메가터치</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B12" s="30" t="inlineStr">
@@ -4691,41 +4568,41 @@
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D12" s="45" t="n">
-        <v>45</v>
-      </c>
-      <c r="E12" s="45" t="n">
-        <v>44</v>
-      </c>
-      <c r="F12" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="G12" s="46" t="n">
-        <v>-43</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D12" s="51" t="n">
+        <v>156</v>
+      </c>
+      <c r="E12" s="51" t="n">
+        <v>137</v>
+      </c>
+      <c r="F12" s="51" t="n">
+        <v>19</v>
+      </c>
+      <c r="G12" s="45" t="n">
+        <v>-131</v>
       </c>
       <c r="H12" s="47" t="n">
-        <v>2.8</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="I12" s="47" t="n">
-        <v>52.9</v>
-      </c>
-      <c r="J12" s="48" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="K12" s="49" t="n">
-        <v>27.22</v>
-      </c>
-      <c r="L12" s="50" t="n">
-        <v>-7.07</v>
+        <v>176.7</v>
+      </c>
+      <c r="J12" s="52" t="n">
+        <v>36.2</v>
+      </c>
+      <c r="K12" s="54" t="n">
+        <v>24.93</v>
+      </c>
+      <c r="L12" s="55" t="n">
+        <v>-4.08</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="31" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>마이크로컨텍솔</t>
         </is>
       </c>
       <c r="B13" s="30" t="inlineStr">
@@ -4735,41 +4612,41 @@
       </c>
       <c r="C13" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D13" s="45" t="n">
-        <v>49</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D13" s="51" t="n">
+        <v>23</v>
       </c>
       <c r="E13" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="45" t="n">
-        <v>49</v>
-      </c>
-      <c r="G13" s="46" t="n">
-        <v>-50</v>
+        <v>19</v>
+      </c>
+      <c r="F13" s="51" t="n">
+        <v>4</v>
+      </c>
+      <c r="G13" s="45" t="n">
+        <v>-37</v>
       </c>
       <c r="H13" s="47" t="n">
-        <v>1.1</v>
+        <v>5.1</v>
       </c>
       <c r="I13" s="47" t="n">
-        <v>103.7</v>
-      </c>
-      <c r="J13" s="48" t="n">
-        <v>25.6</v>
-      </c>
-      <c r="K13" s="49" t="n">
-        <v>33.94</v>
+        <v>199.1</v>
+      </c>
+      <c r="J13" s="52" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="K13" s="54" t="n">
+        <v>10.34</v>
       </c>
       <c r="L13" s="50" t="n">
-        <v>-5.27</v>
+        <v>-6.54</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="31" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>인텍플러스</t>
         </is>
       </c>
       <c r="B14" s="30" t="inlineStr">
@@ -4779,129 +4656,129 @@
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D14" s="45" t="n">
-        <v>77</v>
-      </c>
-      <c r="E14" s="45" t="n">
-        <v>29</v>
+          <t>기계·장비</t>
+        </is>
+      </c>
+      <c r="D14" s="51" t="n">
+        <v>91</v>
+      </c>
+      <c r="E14" s="51" t="n">
+        <v>130</v>
       </c>
       <c r="F14" s="45" t="n">
-        <v>49</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>-76</v>
+        <v>-39</v>
+      </c>
+      <c r="G14" s="45" t="n">
+        <v>-93</v>
       </c>
       <c r="H14" s="47" t="n">
-        <v>6.9</v>
+        <v>28.9</v>
       </c>
       <c r="I14" s="47" t="n">
-        <v>258.2</v>
-      </c>
-      <c r="J14" s="48" t="n">
-        <v>28.5</v>
-      </c>
-      <c r="K14" s="49" t="n">
-        <v>13.09</v>
+        <v>878.1</v>
+      </c>
+      <c r="J14" s="52" t="n">
+        <v>188.7</v>
+      </c>
+      <c r="K14" s="54" t="n">
+        <v>17.52</v>
       </c>
       <c r="L14" s="50" t="n">
-        <v>-9.779999999999999</v>
+        <v>-5.44</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="31" t="inlineStr">
         <is>
-          <t>지엔씨에너지</t>
+          <t>코웨이</t>
         </is>
       </c>
       <c r="B15" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="n">
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D15" s="51" t="n">
+        <v>2</v>
+      </c>
+      <c r="E15" s="51" t="n">
+        <v>17</v>
+      </c>
+      <c r="F15" s="45" t="n">
+        <v>-15</v>
+      </c>
+      <c r="G15" s="45" t="n">
         <v>-1</v>
       </c>
-      <c r="E15" s="46" t="n">
-        <v>-23</v>
-      </c>
-      <c r="F15" s="45" t="n">
-        <v>22</v>
-      </c>
-      <c r="G15" s="46" t="n">
-        <v>-5</v>
-      </c>
       <c r="H15" s="47" t="n">
-        <v>34.2</v>
+        <v>35.4</v>
       </c>
       <c r="I15" s="47" t="n">
-        <v>723.6</v>
-      </c>
-      <c r="J15" s="48" t="n">
-        <v>31.5</v>
-      </c>
-      <c r="K15" s="49" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="L15" s="56" t="n">
-        <v>-3.39</v>
+        <v>882</v>
+      </c>
+      <c r="J15" s="56" t="n">
+        <v>-30</v>
+      </c>
+      <c r="K15" s="53" t="n">
+        <v>-1.67</v>
+      </c>
+      <c r="L15" s="50" t="n">
+        <v>-9.42</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="31" t="inlineStr">
         <is>
-          <t>코웨이</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B16" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C16" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D16" s="45" t="n">
-        <v>2</v>
-      </c>
-      <c r="E16" s="45" t="n">
-        <v>17</v>
-      </c>
-      <c r="F16" s="46" t="n">
-        <v>-15</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>-1</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D16" s="51" t="n">
+        <v>50</v>
+      </c>
+      <c r="E16" s="51" t="n">
+        <v>28</v>
+      </c>
+      <c r="F16" s="51" t="n">
+        <v>21</v>
+      </c>
+      <c r="G16" s="45" t="n">
+        <v>-45</v>
       </c>
       <c r="H16" s="47" t="n">
-        <v>35.4</v>
+        <v>11.6</v>
       </c>
       <c r="I16" s="47" t="n">
-        <v>882</v>
-      </c>
-      <c r="J16" s="57" t="n">
-        <v>-30</v>
-      </c>
-      <c r="K16" s="55" t="n">
-        <v>-1.67</v>
-      </c>
-      <c r="L16" s="50" t="n">
-        <v>-9.529999999999999</v>
+        <v>283.3</v>
+      </c>
+      <c r="J16" s="52" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="K16" s="54" t="n">
+        <v>4.68</v>
+      </c>
+      <c r="L16" s="55" t="n">
+        <v>-2.21</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="31" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>안랩</t>
         </is>
       </c>
       <c r="B17" s="30" t="inlineStr">
@@ -4911,173 +4788,173 @@
       </c>
       <c r="C17" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D17" s="45" t="n">
-        <v>156</v>
-      </c>
-      <c r="E17" s="45" t="n">
-        <v>137</v>
-      </c>
-      <c r="F17" s="45" t="n">
-        <v>19</v>
-      </c>
-      <c r="G17" s="46" t="n">
-        <v>-131</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D17" s="51" t="n">
+        <v>133</v>
+      </c>
+      <c r="E17" s="51" t="n">
+        <v>93</v>
+      </c>
+      <c r="F17" s="51" t="n">
+        <v>40</v>
+      </c>
+      <c r="G17" s="45" t="n">
+        <v>-138</v>
       </c>
       <c r="H17" s="47" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="I17" s="47" t="n">
-        <v>176.7</v>
-      </c>
-      <c r="J17" s="48" t="n">
-        <v>36.2</v>
-      </c>
-      <c r="K17" s="49" t="n">
-        <v>24.93</v>
-      </c>
-      <c r="L17" s="56" t="n">
-        <v>-3.91</v>
+        <v>388.8</v>
+      </c>
+      <c r="J17" s="52" t="n">
+        <v>32.7</v>
+      </c>
+      <c r="K17" s="54" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="L17" s="55" t="n">
+        <v>-2.58</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="31" t="inlineStr">
         <is>
-          <t>마이크로컨텍솔</t>
+          <t>유니퀘스트</t>
         </is>
       </c>
       <c r="B18" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C18" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D18" s="45" t="n">
-        <v>23</v>
-      </c>
-      <c r="E18" s="45" t="n">
-        <v>19</v>
-      </c>
-      <c r="F18" s="45" t="n">
-        <v>4</v>
-      </c>
-      <c r="G18" s="46" t="n">
-        <v>-37</v>
+          <t>유통</t>
+        </is>
+      </c>
+      <c r="D18" s="51" t="n">
+        <v>20</v>
+      </c>
+      <c r="E18" s="51" t="n">
+        <v>14</v>
+      </c>
+      <c r="F18" s="51" t="n">
+        <v>6</v>
+      </c>
+      <c r="G18" s="45" t="n">
+        <v>-21</v>
       </c>
       <c r="H18" s="47" t="n">
-        <v>5.1</v>
+        <v>0.1</v>
       </c>
       <c r="I18" s="47" t="n">
-        <v>199.1</v>
-      </c>
-      <c r="J18" s="48" t="n">
-        <v>16.3</v>
-      </c>
-      <c r="K18" s="49" t="n">
-        <v>10.34</v>
-      </c>
-      <c r="L18" s="50" t="n">
-        <v>-5.45</v>
+        <v>60.3</v>
+      </c>
+      <c r="J18" s="52" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" s="54" t="n">
+        <v>10.64</v>
+      </c>
+      <c r="L18" s="55" t="n">
+        <v>-4.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="31" t="inlineStr">
         <is>
-          <t>인텍플러스</t>
+          <t>드림텍</t>
         </is>
       </c>
       <c r="B19" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C19" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
-        </is>
-      </c>
-      <c r="D19" s="45" t="n">
-        <v>91</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D19" s="51" t="n">
+        <v>107</v>
       </c>
       <c r="E19" s="45" t="n">
-        <v>130</v>
-      </c>
-      <c r="F19" s="46" t="n">
-        <v>-39</v>
-      </c>
-      <c r="G19" s="46" t="n">
-        <v>-93</v>
+        <v>-37</v>
+      </c>
+      <c r="F19" s="51" t="n">
+        <v>144</v>
+      </c>
+      <c r="G19" s="45" t="n">
+        <v>-108</v>
       </c>
       <c r="H19" s="47" t="n">
-        <v>28.9</v>
+        <v>15.1</v>
       </c>
       <c r="I19" s="47" t="n">
-        <v>878.1</v>
-      </c>
-      <c r="J19" s="48" t="n">
-        <v>188.7</v>
-      </c>
-      <c r="K19" s="49" t="n">
-        <v>17.52</v>
+        <v>182.1</v>
+      </c>
+      <c r="J19" s="52" t="n">
+        <v>26.3</v>
+      </c>
+      <c r="K19" s="54" t="n">
+        <v>11.11</v>
       </c>
       <c r="L19" s="50" t="n">
-        <v>-5.64</v>
+        <v>-7.93</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>샘씨엔에스</t>
+          <t>S-Oil우</t>
         </is>
       </c>
       <c r="B20" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C20" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D20" s="45" t="n">
-        <v>50</v>
-      </c>
-      <c r="E20" s="45" t="n">
-        <v>28</v>
-      </c>
-      <c r="F20" s="45" t="n">
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D20" s="51" t="n">
+        <v>37</v>
+      </c>
+      <c r="E20" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="G20" s="46" t="n">
-        <v>-45</v>
+      <c r="F20" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="G20" s="45" t="n">
+        <v>-37</v>
       </c>
       <c r="H20" s="47" t="n">
-        <v>11.6</v>
+        <v>0.3</v>
       </c>
       <c r="I20" s="47" t="n">
-        <v>283.3</v>
-      </c>
-      <c r="J20" s="48" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="K20" s="49" t="n">
-        <v>4.68</v>
-      </c>
-      <c r="L20" s="54" t="n">
-        <v>-1.93</v>
+        <v>211.9</v>
+      </c>
+      <c r="J20" s="52" t="n">
+        <v>27.6</v>
+      </c>
+      <c r="K20" s="54" t="n">
+        <v>11.76</v>
+      </c>
+      <c r="L20" s="57" t="n">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="31" t="inlineStr">
         <is>
-          <t>안랩</t>
+          <t>씨젠</t>
         </is>
       </c>
       <c r="B21" s="30" t="inlineStr">
@@ -5087,261 +4964,261 @@
       </c>
       <c r="C21" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D21" s="45" t="n">
-        <v>133</v>
-      </c>
-      <c r="E21" s="45" t="n">
-        <v>93</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D21" s="51" t="n">
+        <v>47</v>
+      </c>
+      <c r="E21" s="51" t="n">
+        <v>50</v>
       </c>
       <c r="F21" s="45" t="n">
-        <v>40</v>
-      </c>
-      <c r="G21" s="46" t="n">
-        <v>-138</v>
+        <v>-3</v>
+      </c>
+      <c r="G21" s="45" t="n">
+        <v>-49</v>
       </c>
       <c r="H21" s="47" t="n">
-        <v>9.6</v>
+        <v>16.4</v>
       </c>
       <c r="I21" s="47" t="n">
-        <v>388.8</v>
-      </c>
-      <c r="J21" s="48" t="n">
-        <v>32.7</v>
-      </c>
-      <c r="K21" s="49" t="n">
-        <v>9.359999999999999</v>
-      </c>
-      <c r="L21" s="56" t="n">
-        <v>-2.58</v>
+        <v>758.6</v>
+      </c>
+      <c r="J21" s="56" t="n">
+        <v>-4.3</v>
+      </c>
+      <c r="K21" s="53" t="n">
+        <v>-0.15</v>
+      </c>
+      <c r="L21" s="50" t="n">
+        <v>-5.3</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="31" t="inlineStr">
         <is>
-          <t>유니퀘스트</t>
+          <t>코미팜</t>
         </is>
       </c>
       <c r="B22" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C22" s="34" t="inlineStr">
         <is>
-          <t>유통</t>
-        </is>
-      </c>
-      <c r="D22" s="45" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="45" t="n">
-        <v>14</v>
-      </c>
-      <c r="F22" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G22" s="46" t="n">
-        <v>-21</v>
+          <t>제약</t>
+        </is>
+      </c>
+      <c r="D22" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="E22" s="51" t="n">
+        <v>8</v>
+      </c>
+      <c r="F22" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="45" t="n">
+        <v>-8</v>
       </c>
       <c r="H22" s="47" t="n">
-        <v>0.1</v>
+        <v>4.3</v>
       </c>
       <c r="I22" s="47" t="n">
-        <v>60.3</v>
-      </c>
-      <c r="J22" s="48" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K22" s="49" t="n">
-        <v>10.64</v>
-      </c>
-      <c r="L22" s="56" t="n">
-        <v>-4.04</v>
+        <v>242</v>
+      </c>
+      <c r="J22" s="52" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K22" s="54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="L22" s="50" t="n">
+        <v>-9.1</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="31" t="inlineStr">
         <is>
-          <t>드림텍</t>
+          <t>한국알콜</t>
         </is>
       </c>
       <c r="B23" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D23" s="45" t="n">
-        <v>107</v>
-      </c>
-      <c r="E23" s="46" t="n">
-        <v>-37</v>
-      </c>
-      <c r="F23" s="45" t="n">
-        <v>144</v>
-      </c>
-      <c r="G23" s="46" t="n">
-        <v>-108</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D23" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="E23" s="51" t="n">
+        <v>18</v>
+      </c>
+      <c r="F23" s="46" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="45" t="n">
+        <v>-18</v>
       </c>
       <c r="H23" s="47" t="n">
-        <v>15.1</v>
+        <v>1.5</v>
       </c>
       <c r="I23" s="47" t="n">
-        <v>182.1</v>
-      </c>
-      <c r="J23" s="48" t="n">
-        <v>26.3</v>
-      </c>
-      <c r="K23" s="49" t="n">
-        <v>11.11</v>
+        <v>82.5</v>
+      </c>
+      <c r="J23" s="52" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="K23" s="54" t="n">
+        <v>7.83</v>
       </c>
       <c r="L23" s="50" t="n">
-        <v>-7.29</v>
+        <v>-5.69</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>S-Oil우</t>
+      <c r="A24" s="31" t="inlineStr">
+        <is>
+          <t>디지털대성</t>
         </is>
       </c>
       <c r="B24" s="30" t="inlineStr">
         <is>
-          <t>KOSPI</t>
+          <t>KOSDAQ</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D24" s="45" t="n">
-        <v>37</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D24" s="51" t="n">
+        <v>11</v>
       </c>
       <c r="E24" s="45" t="n">
-        <v>21</v>
-      </c>
-      <c r="F24" s="45" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F24" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="G24" s="46" t="n">
-        <v>-37</v>
+      <c r="G24" s="45" t="n">
+        <v>-19</v>
       </c>
       <c r="H24" s="47" t="n">
-        <v>0.3</v>
+        <v>0.1</v>
       </c>
       <c r="I24" s="47" t="n">
-        <v>211.9</v>
-      </c>
-      <c r="J24" s="48" t="n">
-        <v>27.6</v>
-      </c>
-      <c r="K24" s="49" t="n">
-        <v>11.76</v>
-      </c>
-      <c r="L24" s="54" t="n">
-        <v>-1.08</v>
+        <v>28.3</v>
+      </c>
+      <c r="J24" s="52" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K24" s="54" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="L24" s="55" t="n">
+        <v>-2.68</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="31" t="inlineStr">
         <is>
-          <t>씨젠</t>
+          <t>코리안리</t>
         </is>
       </c>
       <c r="B25" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>보험</t>
         </is>
       </c>
       <c r="D25" s="45" t="n">
-        <v>47</v>
+        <v>-21</v>
       </c>
       <c r="E25" s="45" t="n">
-        <v>50</v>
-      </c>
-      <c r="F25" s="46" t="n">
         <v>-3</v>
       </c>
-      <c r="G25" s="46" t="n">
-        <v>-49</v>
+      <c r="F25" s="45" t="n">
+        <v>-17</v>
+      </c>
+      <c r="G25" s="51" t="n">
+        <v>12</v>
       </c>
       <c r="H25" s="47" t="n">
-        <v>16.4</v>
+        <v>2.6</v>
       </c>
       <c r="I25" s="47" t="n">
-        <v>758.6</v>
-      </c>
-      <c r="J25" s="57" t="n">
-        <v>-4.3</v>
-      </c>
-      <c r="K25" s="55" t="n">
-        <v>-0.15</v>
+        <v>809.5</v>
+      </c>
+      <c r="J25" s="56" t="n">
+        <v>-6.4</v>
+      </c>
+      <c r="K25" s="53" t="n">
+        <v>-1.74</v>
       </c>
       <c r="L25" s="50" t="n">
-        <v>-5.61</v>
+        <v>-6.82</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="31" t="inlineStr">
         <is>
-          <t>코미팜</t>
+          <t>IPARK현대산업개발</t>
         </is>
       </c>
       <c r="B26" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
         <is>
-          <t>제약</t>
+          <t>건설</t>
         </is>
       </c>
       <c r="D26" s="45" t="n">
-        <v>8</v>
+        <v>-1</v>
       </c>
       <c r="E26" s="45" t="n">
-        <v>8</v>
-      </c>
-      <c r="F26" s="51" t="n">
+        <v>-1</v>
+      </c>
+      <c r="F26" s="46" t="n">
         <v>0</v>
       </c>
-      <c r="G26" s="46" t="n">
-        <v>-8</v>
+      <c r="G26" s="45" t="n">
+        <v>-12</v>
       </c>
       <c r="H26" s="47" t="n">
-        <v>4.3</v>
+        <v>6.6</v>
       </c>
       <c r="I26" s="47" t="n">
-        <v>242</v>
-      </c>
-      <c r="J26" s="48" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="K26" s="49" t="n">
-        <v>1.02</v>
+        <v>423.5</v>
+      </c>
+      <c r="J26" s="56" t="n">
+        <v>-1.8</v>
+      </c>
+      <c r="K26" s="53" t="n">
+        <v>-0.42</v>
       </c>
       <c r="L26" s="50" t="n">
-        <v>-8.66</v>
+        <v>-8.210000000000001</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="31" t="inlineStr">
         <is>
-          <t>한국알콜</t>
+          <t>지어소프트</t>
         </is>
       </c>
       <c r="B27" s="30" t="inlineStr">
@@ -5351,85 +5228,85 @@
       </c>
       <c r="C27" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D27" s="45" t="n">
-        <v>18</v>
-      </c>
-      <c r="E27" s="45" t="n">
-        <v>18</v>
-      </c>
-      <c r="F27" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" s="46" t="n">
-        <v>-18</v>
+          <t>IT 서비스</t>
+        </is>
+      </c>
+      <c r="D27" s="51" t="n">
+        <v>15</v>
+      </c>
+      <c r="E27" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="F27" s="45" t="n">
+        <v>-1</v>
+      </c>
+      <c r="G27" s="45" t="n">
+        <v>-15</v>
       </c>
       <c r="H27" s="47" t="n">
-        <v>1.5</v>
+        <v>2.2</v>
       </c>
       <c r="I27" s="47" t="n">
-        <v>82.5</v>
-      </c>
-      <c r="J27" s="48" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="K27" s="49" t="n">
-        <v>7.83</v>
+        <v>39.9</v>
+      </c>
+      <c r="J27" s="56" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="K27" s="53" t="n">
+        <v>-1.5</v>
       </c>
       <c r="L27" s="50" t="n">
-        <v>-5.48</v>
+        <v>-6.7</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="31" t="inlineStr">
         <is>
-          <t>디지털대성</t>
+          <t>동아지질</t>
         </is>
       </c>
       <c r="B28" s="30" t="inlineStr">
         <is>
-          <t>KOSDAQ</t>
+          <t>KOSPI</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D28" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="E28" s="46" t="n">
-        <v>-4</v>
-      </c>
-      <c r="F28" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="G28" s="46" t="n">
-        <v>-19</v>
+          <t>건설</t>
+        </is>
+      </c>
+      <c r="D28" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="51" t="n">
+        <v>1</v>
+      </c>
+      <c r="F28" s="51" t="n">
+        <v>9</v>
+      </c>
+      <c r="G28" s="45" t="n">
+        <v>-9</v>
       </c>
       <c r="H28" s="47" t="n">
-        <v>0.1</v>
+        <v>0.4</v>
       </c>
       <c r="I28" s="47" t="n">
-        <v>28.3</v>
-      </c>
-      <c r="J28" s="48" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K28" s="49" t="n">
-        <v>8.92</v>
-      </c>
-      <c r="L28" s="56" t="n">
-        <v>-3.11</v>
+        <v>63.1</v>
+      </c>
+      <c r="J28" s="56" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="K28" s="54" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="L28" s="50" t="n">
+        <v>-5.17</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="31" t="inlineStr">
         <is>
-          <t>코리안리</t>
+          <t>케이씨</t>
         </is>
       </c>
       <c r="B29" s="30" t="inlineStr">
@@ -5439,41 +5316,41 @@
       </c>
       <c r="C29" s="34" t="inlineStr">
         <is>
-          <t>보험</t>
-        </is>
-      </c>
-      <c r="D29" s="46" t="n">
-        <v>-21</v>
-      </c>
-      <c r="E29" s="46" t="n">
-        <v>-3</v>
-      </c>
-      <c r="F29" s="46" t="n">
-        <v>-17</v>
+          <t>의료·정밀기기</t>
+        </is>
+      </c>
+      <c r="D29" s="51" t="n">
+        <v>16</v>
+      </c>
+      <c r="E29" s="51" t="n">
+        <v>11</v>
+      </c>
+      <c r="F29" s="51" t="n">
+        <v>6</v>
       </c>
       <c r="G29" s="45" t="n">
-        <v>12</v>
+        <v>-15</v>
       </c>
       <c r="H29" s="47" t="n">
-        <v>2.6</v>
+        <v>0.4</v>
       </c>
       <c r="I29" s="47" t="n">
-        <v>809.5</v>
-      </c>
-      <c r="J29" s="57" t="n">
-        <v>-6.4</v>
-      </c>
-      <c r="K29" s="55" t="n">
-        <v>-1.74</v>
-      </c>
-      <c r="L29" s="50" t="n">
-        <v>-7.04</v>
+        <v>96.90000000000001</v>
+      </c>
+      <c r="J29" s="52" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K29" s="54" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="L29" s="55" t="n">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="31" t="inlineStr">
         <is>
-          <t>IPARK현대산업개발</t>
+          <t>롯데렌탈</t>
         </is>
       </c>
       <c r="B30" s="30" t="inlineStr">
@@ -5483,228 +5360,52 @@
       </c>
       <c r="C30" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D30" s="46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="E30" s="46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="F30" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="46" t="n">
-        <v>-12</v>
+          <t>일반서비스</t>
+        </is>
+      </c>
+      <c r="D30" s="45" t="n">
+        <v>-16</v>
+      </c>
+      <c r="E30" s="45" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F30" s="45" t="n">
+        <v>-6</v>
+      </c>
+      <c r="G30" s="51" t="n">
+        <v>15</v>
       </c>
       <c r="H30" s="47" t="n">
-        <v>6.6</v>
+        <v>24.6</v>
       </c>
       <c r="I30" s="47" t="n">
-        <v>423.5</v>
-      </c>
-      <c r="J30" s="57" t="n">
-        <v>-1.8</v>
-      </c>
-      <c r="K30" s="55" t="n">
-        <v>-0.42</v>
+        <v>625.2</v>
+      </c>
+      <c r="J30" s="52" t="n">
+        <v>31.9</v>
+      </c>
+      <c r="K30" s="54" t="n">
+        <v>1.43</v>
       </c>
       <c r="L30" s="50" t="n">
-        <v>-6.6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="31" t="inlineStr">
-        <is>
-          <t>지어소프트</t>
-        </is>
-      </c>
-      <c r="B31" s="30" t="inlineStr">
-        <is>
-          <t>KOSDAQ</t>
-        </is>
-      </c>
-      <c r="C31" s="34" t="inlineStr">
-        <is>
-          <t>IT 서비스</t>
-        </is>
-      </c>
-      <c r="D31" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="E31" s="45" t="n">
-        <v>16</v>
-      </c>
-      <c r="F31" s="46" t="n">
-        <v>-1</v>
-      </c>
-      <c r="G31" s="46" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H31" s="47" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="I31" s="47" t="n">
-        <v>39.9</v>
-      </c>
-      <c r="J31" s="57" t="n">
-        <v>-0.6</v>
-      </c>
-      <c r="K31" s="55" t="n">
-        <v>-1.5</v>
-      </c>
-      <c r="L31" s="50" t="n">
-        <v>-9.039999999999999</v>
-      </c>
-    </row>
+        <v>-6.95</v>
+      </c>
+    </row>
+    <row r="31"/>
     <row r="32">
-      <c r="A32" s="31" t="inlineStr">
-        <is>
-          <t>동아지질</t>
-        </is>
-      </c>
-      <c r="B32" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C32" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
-        </is>
-      </c>
-      <c r="D32" s="45" t="n">
-        <v>9</v>
-      </c>
-      <c r="E32" s="45" t="n">
-        <v>1</v>
-      </c>
-      <c r="F32" s="45" t="n">
-        <v>9</v>
-      </c>
-      <c r="G32" s="46" t="n">
-        <v>-9</v>
-      </c>
-      <c r="H32" s="47" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I32" s="47" t="n">
-        <v>63.1</v>
-      </c>
-      <c r="J32" s="57" t="n">
-        <v>-1.2</v>
-      </c>
-      <c r="K32" s="49" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L32" s="50" t="n">
-        <v>-6.14</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="31" t="inlineStr">
-        <is>
-          <t>케이씨</t>
-        </is>
-      </c>
-      <c r="B33" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C33" s="34" t="inlineStr">
-        <is>
-          <t>의료·정밀기기</t>
-        </is>
-      </c>
-      <c r="D33" s="45" t="n">
-        <v>16</v>
-      </c>
-      <c r="E33" s="45" t="n">
-        <v>11</v>
-      </c>
-      <c r="F33" s="45" t="n">
-        <v>6</v>
-      </c>
-      <c r="G33" s="46" t="n">
-        <v>-15</v>
-      </c>
-      <c r="H33" s="47" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="I33" s="47" t="n">
-        <v>96.90000000000001</v>
-      </c>
-      <c r="J33" s="48" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="K33" s="49" t="n">
-        <v>6.1</v>
-      </c>
-      <c r="L33" s="56" t="n">
-        <v>-3.45</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="31" t="inlineStr">
-        <is>
-          <t>롯데렌탈</t>
-        </is>
-      </c>
-      <c r="B34" s="30" t="inlineStr">
-        <is>
-          <t>KOSPI</t>
-        </is>
-      </c>
-      <c r="C34" s="34" t="inlineStr">
-        <is>
-          <t>일반서비스</t>
-        </is>
-      </c>
-      <c r="D34" s="46" t="n">
-        <v>-16</v>
-      </c>
-      <c r="E34" s="46" t="n">
-        <v>-10</v>
-      </c>
-      <c r="F34" s="46" t="n">
-        <v>-6</v>
-      </c>
-      <c r="G34" s="45" t="n">
-        <v>15</v>
-      </c>
-      <c r="H34" s="47" t="n">
-        <v>24.6</v>
-      </c>
-      <c r="I34" s="47" t="n">
-        <v>625.2</v>
-      </c>
-      <c r="J34" s="48" t="n">
-        <v>31.9</v>
-      </c>
-      <c r="K34" s="49" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="L34" s="50" t="n">
-        <v>-7.06</v>
-      </c>
-    </row>
-    <row r="35"/>
-    <row r="36">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A32" s="18" t="inlineStr">
         <is>
           <t>최신 거래일 기준 · 52주 신고가 대비 -10% 이내 (KIS 랭킹) · ETF·ETN 제외 · 수급=주간 누적 확정(억원) · 동반 순매수(외인·기관 동일 방향)=합산 굵게</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A5:L34"/>
+  <autoFilter ref="A5:L30"/>
   <mergeCells count="6">
     <mergeCell ref="D4:J4"/>
     <mergeCell ref="K1:L1"/>
+    <mergeCell ref="A32:L32"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A36:L36"/>
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A4:C4"/>
   </mergeCells>
@@ -5753,7 +5454,7 @@
       </c>
       <c r="O1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21 ~ 2026-09-24</t>
+          <t>2026-09-21 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -5898,8 +5599,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D6" s="46" t="n">
-        <v>31006</v>
+      <c r="D6" s="45" t="n">
+        <v>25488</v>
       </c>
       <c r="E6" s="30" t="n">
         <v>1</v>
@@ -5915,7 +5616,7 @@
         </is>
       </c>
       <c r="H6" s="61" t="n">
-        <v>-34214</v>
+        <v>-24228</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>1</v>
@@ -5930,13 +5631,13 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M6" s="46" t="n">
-        <v>18113</v>
+      <c r="M6" s="45" t="n">
+        <v>15850</v>
       </c>
       <c r="N6" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="O6" s="1" t="inlineStr">
+      <c r="O6" s="31" t="inlineStr">
         <is>
           <t>NAVER</t>
         </is>
@@ -5947,7 +5648,7 @@
         </is>
       </c>
       <c r="Q6" s="61" t="n">
-        <v>-1329</v>
+        <v>-1096</v>
       </c>
     </row>
     <row r="7">
@@ -5964,8 +5665,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D7" s="46" t="n">
-        <v>4636</v>
+      <c r="D7" s="45" t="n">
+        <v>3048</v>
       </c>
       <c r="E7" s="30" t="n">
         <v>2</v>
@@ -5981,12 +5682,12 @@
         </is>
       </c>
       <c r="H7" s="61" t="n">
-        <v>-3029</v>
+        <v>-2057</v>
       </c>
       <c r="J7" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="K7" s="31" t="inlineStr">
+      <c r="K7" s="1" t="inlineStr">
         <is>
           <t>삼성전기</t>
         </is>
@@ -5996,8 +5697,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M7" s="46" t="n">
-        <v>3304</v>
+      <c r="M7" s="45" t="n">
+        <v>2989</v>
       </c>
       <c r="N7" s="30" t="n">
         <v>2</v>
@@ -6013,7 +5714,7 @@
         </is>
       </c>
       <c r="Q7" s="61" t="n">
-        <v>-1151</v>
+        <v>-964</v>
       </c>
     </row>
     <row r="8" ht="31" customHeight="1" s="15">
@@ -6030,8 +5731,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D8" s="46" t="n">
-        <v>2108</v>
+      <c r="D8" s="45" t="n">
+        <v>2380</v>
       </c>
       <c r="E8" s="30" t="n">
         <v>3</v>
@@ -6047,7 +5748,7 @@
         </is>
       </c>
       <c r="H8" s="61" t="n">
-        <v>-1925</v>
+        <v>-1286</v>
       </c>
       <c r="J8" s="30" t="n">
         <v>3</v>
@@ -6062,8 +5763,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M8" s="46" t="n">
-        <v>2804</v>
+      <c r="M8" s="45" t="n">
+        <v>1109</v>
       </c>
       <c r="N8" s="30" t="n">
         <v>3</v>
@@ -6079,25 +5780,25 @@
         </is>
       </c>
       <c r="Q8" s="61" t="n">
-        <v>-1100</v>
-      </c>
-    </row>
-    <row r="9" ht="31" customHeight="1" s="15">
+        <v>-902</v>
+      </c>
+    </row>
+    <row r="9">
       <c r="A9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="31" t="inlineStr">
-        <is>
-          <t>SK이노베이션</t>
+      <c r="B9" s="1" t="inlineStr">
+        <is>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C9" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D9" s="46" t="n">
-        <v>818</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D9" s="45" t="n">
+        <v>1076</v>
       </c>
       <c r="E9" s="30" t="n">
         <v>4</v>
@@ -6113,7 +5814,7 @@
         </is>
       </c>
       <c r="H9" s="61" t="n">
-        <v>-1334</v>
+        <v>-929</v>
       </c>
       <c r="J9" s="30" t="n">
         <v>4</v>
@@ -6128,27 +5829,27 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M9" s="46" t="n">
-        <v>1235</v>
+      <c r="M9" s="45" t="n">
+        <v>1046</v>
       </c>
       <c r="N9" s="30" t="n">
         <v>4</v>
       </c>
-      <c r="O9" s="1" t="inlineStr">
-        <is>
-          <t>현대차</t>
-        </is>
-      </c>
-      <c r="P9" s="41" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+      <c r="O9" s="31" t="inlineStr">
+        <is>
+          <t>삼양식품</t>
+        </is>
+      </c>
+      <c r="P9" s="34" t="inlineStr">
+        <is>
+          <t>음식료·담배</t>
         </is>
       </c>
       <c r="Q9" s="61" t="n">
-        <v>-689</v>
-      </c>
-    </row>
-    <row r="10">
+        <v>-562</v>
+      </c>
+    </row>
+    <row r="10" ht="31" customHeight="1" s="15">
       <c r="A10" s="30" t="n">
         <v>5</v>
       </c>
@@ -6162,29 +5863,29 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D10" s="46" t="n">
-        <v>717</v>
+      <c r="D10" s="45" t="n">
+        <v>742</v>
       </c>
       <c r="E10" s="30" t="n">
         <v>5</v>
       </c>
       <c r="F10" s="31" t="inlineStr">
         <is>
-          <t>리노공업</t>
-        </is>
-      </c>
-      <c r="G10" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>한화에어로스페이스</t>
+        </is>
+      </c>
+      <c r="G10" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="H10" s="61" t="n">
-        <v>-1143</v>
+        <v>-687</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="K10" s="31" t="inlineStr">
+      <c r="K10" s="1" t="inlineStr">
         <is>
           <t>LG전자</t>
         </is>
@@ -6194,33 +5895,33 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M10" s="46" t="n">
+      <c r="M10" s="45" t="n">
         <v>723</v>
       </c>
       <c r="N10" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="O10" s="31" t="inlineStr">
-        <is>
-          <t>삼양식품</t>
-        </is>
-      </c>
-      <c r="P10" s="34" t="inlineStr">
-        <is>
-          <t>음식료·담배</t>
+      <c r="O10" s="1" t="inlineStr">
+        <is>
+          <t>현대차</t>
+        </is>
+      </c>
+      <c r="P10" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q10" s="61" t="n">
-        <v>-623</v>
+        <v>-518</v>
       </c>
     </row>
     <row r="11" ht="31" customHeight="1" s="15">
       <c r="A11" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="31" t="inlineStr">
-        <is>
-          <t>SFA반도체</t>
+      <c r="B11" s="1" t="inlineStr">
+        <is>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C11" s="34" t="inlineStr">
@@ -6228,24 +5929,24 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D11" s="46" t="n">
-        <v>563</v>
+      <c r="D11" s="45" t="n">
+        <v>687</v>
       </c>
       <c r="E11" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F11" s="31" t="inlineStr">
         <is>
-          <t>한화에어로스페이스</t>
-        </is>
-      </c>
-      <c r="G11" s="41" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>대한광통신</t>
+        </is>
+      </c>
+      <c r="G11" s="34" t="inlineStr">
+        <is>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H11" s="61" t="n">
-        <v>-997</v>
+        <v>-675</v>
       </c>
       <c r="J11" s="30" t="n">
         <v>6</v>
@@ -6260,42 +5961,42 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M11" s="46" t="n">
-        <v>668</v>
+      <c r="M11" s="45" t="n">
+        <v>670</v>
       </c>
       <c r="N11" s="30" t="n">
         <v>6</v>
       </c>
-      <c r="O11" s="1" t="inlineStr">
-        <is>
-          <t>현대건설</t>
-        </is>
-      </c>
-      <c r="P11" s="34" t="inlineStr">
-        <is>
-          <t>건설</t>
+      <c r="O11" s="31" t="inlineStr">
+        <is>
+          <t>HD현대중공업</t>
+        </is>
+      </c>
+      <c r="P11" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q11" s="61" t="n">
-        <v>-573</v>
-      </c>
-    </row>
-    <row r="12" ht="31" customHeight="1" s="15">
+        <v>-426</v>
+      </c>
+    </row>
+    <row r="12">
       <c r="A12" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>이수페타시스</t>
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>SK이노베이션</t>
         </is>
       </c>
       <c r="C12" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D12" s="46" t="n">
-        <v>544</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D12" s="45" t="n">
+        <v>578</v>
       </c>
       <c r="E12" s="30" t="n">
         <v>7</v>
@@ -6311,7 +6012,7 @@
         </is>
       </c>
       <c r="H12" s="61" t="n">
-        <v>-892</v>
+        <v>-629</v>
       </c>
       <c r="J12" s="30" t="n">
         <v>7</v>
@@ -6326,33 +6027,33 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="M12" s="46" t="n">
-        <v>652</v>
+      <c r="M12" s="45" t="n">
+        <v>583</v>
       </c>
       <c r="N12" s="30" t="n">
         <v>7</v>
       </c>
       <c r="O12" s="31" t="inlineStr">
         <is>
-          <t>HD현대중공업</t>
-        </is>
-      </c>
-      <c r="P12" s="41" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>현대건설</t>
+        </is>
+      </c>
+      <c r="P12" s="34" t="inlineStr">
+        <is>
+          <t>건설</t>
         </is>
       </c>
       <c r="Q12" s="61" t="n">
-        <v>-497</v>
-      </c>
-    </row>
-    <row r="13">
+        <v>-423</v>
+      </c>
+    </row>
+    <row r="13" ht="31" customHeight="1" s="15">
       <c r="A13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="B13" s="31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>SFA반도체</t>
         </is>
       </c>
       <c r="C13" s="34" t="inlineStr">
@@ -6360,29 +6061,29 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D13" s="46" t="n">
-        <v>467</v>
+      <c r="D13" s="45" t="n">
+        <v>515</v>
       </c>
       <c r="E13" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="F13" s="1" t="inlineStr">
-        <is>
-          <t>NAVER</t>
+      <c r="F13" s="31" t="inlineStr">
+        <is>
+          <t>리노공업</t>
         </is>
       </c>
       <c r="G13" s="34" t="inlineStr">
         <is>
-          <t>IT 서비스</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H13" s="61" t="n">
-        <v>-836</v>
+        <v>-611</v>
       </c>
       <c r="J13" s="30" t="n">
         <v>8</v>
       </c>
-      <c r="K13" s="1" t="inlineStr">
+      <c r="K13" s="31" t="inlineStr">
         <is>
           <t>이수페타시스</t>
         </is>
@@ -6392,42 +6093,42 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M13" s="46" t="n">
-        <v>584</v>
+      <c r="M13" s="45" t="n">
+        <v>537</v>
       </c>
       <c r="N13" s="30" t="n">
         <v>8</v>
       </c>
       <c r="O13" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
-        </is>
-      </c>
-      <c r="P13" s="34" t="inlineStr">
-        <is>
-          <t>전기·전자</t>
+          <t>기아</t>
+        </is>
+      </c>
+      <c r="P13" s="41" t="inlineStr">
+        <is>
+          <t>운송장비·부품</t>
         </is>
       </c>
       <c r="Q13" s="61" t="n">
-        <v>-496</v>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1" s="15">
+        <v>-394</v>
+      </c>
+    </row>
+    <row r="14">
       <c r="A14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="31" t="inlineStr">
         <is>
-          <t>GS</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C14" s="34" t="inlineStr">
         <is>
-          <t>기타금융</t>
-        </is>
-      </c>
-      <c r="D14" s="46" t="n">
-        <v>457</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D14" s="45" t="n">
+        <v>467</v>
       </c>
       <c r="E14" s="30" t="n">
         <v>9</v>
@@ -6443,7 +6144,7 @@
         </is>
       </c>
       <c r="H14" s="61" t="n">
-        <v>-818</v>
+        <v>-590</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>9</v>
@@ -6458,24 +6159,24 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M14" s="46" t="n">
-        <v>383</v>
+      <c r="M14" s="45" t="n">
+        <v>305</v>
       </c>
       <c r="N14" s="30" t="n">
         <v>9</v>
       </c>
       <c r="O14" s="31" t="inlineStr">
         <is>
-          <t>기아</t>
-        </is>
-      </c>
-      <c r="P14" s="41" t="inlineStr">
-        <is>
-          <t>운송장비·부품</t>
+          <t>GS</t>
+        </is>
+      </c>
+      <c r="P14" s="34" t="inlineStr">
+        <is>
+          <t>기타금융</t>
         </is>
       </c>
       <c r="Q14" s="61" t="n">
-        <v>-436</v>
+        <v>-385</v>
       </c>
     </row>
     <row r="15">
@@ -6484,32 +6185,32 @@
       </c>
       <c r="B15" s="31" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C15" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D15" s="46" t="n">
-        <v>424</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D15" s="45" t="n">
+        <v>367</v>
       </c>
       <c r="E15" s="30" t="n">
         <v>10</v>
       </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>현대건설</t>
+      <c r="F15" s="31" t="inlineStr">
+        <is>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="G15" s="34" t="inlineStr">
         <is>
-          <t>건설</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H15" s="61" t="n">
-        <v>-769</v>
+        <v>-563</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>10</v>
@@ -6524,8 +6225,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M15" s="46" t="n">
-        <v>330</v>
+      <c r="M15" s="45" t="n">
+        <v>296</v>
       </c>
       <c r="N15" s="30" t="n">
         <v>10</v>
@@ -6541,7 +6242,7 @@
         </is>
       </c>
       <c r="Q15" s="61" t="n">
-        <v>-416</v>
+        <v>-384</v>
       </c>
     </row>
     <row r="16"/>
@@ -6685,8 +6386,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D20" s="46" t="n">
-        <v>49119</v>
+      <c r="D20" s="45" t="n">
+        <v>41338</v>
       </c>
       <c r="E20" s="30" t="n">
         <v>1</v>
@@ -6702,7 +6403,7 @@
         </is>
       </c>
       <c r="H20" s="61" t="n">
-        <v>-31410</v>
+        <v>-23119</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>1</v>
@@ -6717,7 +6418,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M20" s="46" t="n">
+      <c r="M20" s="45" t="n">
         <v>2994</v>
       </c>
       <c r="N20" s="30" t="n">
@@ -6743,7 +6444,7 @@
       </c>
       <c r="B21" s="31" t="inlineStr">
         <is>
-          <t>삼성전자우</t>
+          <t>삼성전기</t>
         </is>
       </c>
       <c r="C21" s="34" t="inlineStr">
@@ -6751,8 +6452,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D21" s="46" t="n">
-        <v>4139</v>
+      <c r="D21" s="45" t="n">
+        <v>4065</v>
       </c>
       <c r="E21" s="30" t="n">
         <v>2</v>
@@ -6768,7 +6469,7 @@
         </is>
       </c>
       <c r="H21" s="61" t="n">
-        <v>-4180</v>
+        <v>-3021</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>2</v>
@@ -6783,7 +6484,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M21" s="46" t="n">
+      <c r="M21" s="45" t="n">
         <v>1781</v>
       </c>
       <c r="N21" s="30" t="n">
@@ -6817,8 +6518,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D22" s="46" t="n">
-        <v>3343</v>
+      <c r="D22" s="45" t="n">
+        <v>3426</v>
       </c>
       <c r="E22" s="30" t="n">
         <v>3</v>
@@ -6834,7 +6535,7 @@
         </is>
       </c>
       <c r="H22" s="61" t="n">
-        <v>-2614</v>
+        <v>-1804</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>3</v>
@@ -6849,7 +6550,7 @@
           <t>IT 서비스</t>
         </is>
       </c>
-      <c r="M22" s="46" t="n">
+      <c r="M22" s="45" t="n">
         <v>1356</v>
       </c>
       <c r="N22" s="30" t="n">
@@ -6875,7 +6576,7 @@
       </c>
       <c r="B23" s="31" t="inlineStr">
         <is>
-          <t>삼성전기</t>
+          <t>삼성전자우</t>
         </is>
       </c>
       <c r="C23" s="34" t="inlineStr">
@@ -6883,8 +6584,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D23" s="46" t="n">
-        <v>2954</v>
+      <c r="D23" s="45" t="n">
+        <v>2668</v>
       </c>
       <c r="E23" s="30" t="n">
         <v>4</v>
@@ -6900,7 +6601,7 @@
         </is>
       </c>
       <c r="H23" s="61" t="n">
-        <v>-2166</v>
+        <v>-1327</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>4</v>
@@ -6915,7 +6616,7 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="M23" s="46" t="n">
+      <c r="M23" s="45" t="n">
         <v>1225</v>
       </c>
       <c r="N23" s="30" t="n">
@@ -6941,16 +6642,16 @@
       </c>
       <c r="B24" s="31" t="inlineStr">
         <is>
-          <t>대한항공</t>
+          <t>LG전자</t>
         </is>
       </c>
       <c r="C24" s="34" t="inlineStr">
         <is>
-          <t>운송·창고</t>
-        </is>
-      </c>
-      <c r="D24" s="46" t="n">
-        <v>1369</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D24" s="45" t="n">
+        <v>1410</v>
       </c>
       <c r="E24" s="30" t="n">
         <v>5</v>
@@ -6966,7 +6667,7 @@
         </is>
       </c>
       <c r="H24" s="61" t="n">
-        <v>-1724</v>
+        <v>-1229</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>5</v>
@@ -6981,7 +6682,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M24" s="46" t="n">
+      <c r="M24" s="45" t="n">
         <v>1213</v>
       </c>
       <c r="N24" s="30" t="n">
@@ -7007,16 +6708,16 @@
       </c>
       <c r="B25" s="31" t="inlineStr">
         <is>
-          <t>이수페타시스</t>
+          <t>대한항공</t>
         </is>
       </c>
       <c r="C25" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
-        </is>
-      </c>
-      <c r="D25" s="46" t="n">
-        <v>1128</v>
+          <t>운송·창고</t>
+        </is>
+      </c>
+      <c r="D25" s="45" t="n">
+        <v>1325</v>
       </c>
       <c r="E25" s="30" t="n">
         <v>6</v>
@@ -7032,7 +6733,7 @@
         </is>
       </c>
       <c r="H25" s="61" t="n">
-        <v>-1427</v>
+        <v>-1182</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>6</v>
@@ -7047,7 +6748,7 @@
           <t>건설</t>
         </is>
       </c>
-      <c r="M25" s="46" t="n">
+      <c r="M25" s="45" t="n">
         <v>880</v>
       </c>
       <c r="N25" s="30" t="n">
@@ -7073,7 +6774,7 @@
       </c>
       <c r="B26" s="31" t="inlineStr">
         <is>
-          <t>LG전자</t>
+          <t>이수페타시스</t>
         </is>
       </c>
       <c r="C26" s="34" t="inlineStr">
@@ -7081,8 +6782,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D26" s="46" t="n">
-        <v>1124</v>
+      <c r="D26" s="45" t="n">
+        <v>871</v>
       </c>
       <c r="E26" s="30" t="n">
         <v>7</v>
@@ -7098,7 +6799,7 @@
         </is>
       </c>
       <c r="H26" s="61" t="n">
-        <v>-1342</v>
+        <v>-872</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>7</v>
@@ -7113,7 +6814,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M26" s="46" t="n">
+      <c r="M26" s="45" t="n">
         <v>725</v>
       </c>
       <c r="N26" s="30" t="n">
@@ -7147,8 +6848,8 @@
           <t>화학</t>
         </is>
       </c>
-      <c r="D27" s="46" t="n">
-        <v>1041</v>
+      <c r="D27" s="45" t="n">
+        <v>718</v>
       </c>
       <c r="E27" s="30" t="n">
         <v>8</v>
@@ -7164,7 +6865,7 @@
         </is>
       </c>
       <c r="H27" s="61" t="n">
-        <v>-1021</v>
+        <v>-729</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>8</v>
@@ -7179,7 +6880,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="M27" s="46" t="n">
+      <c r="M27" s="45" t="n">
         <v>716</v>
       </c>
       <c r="N27" s="30" t="n">
@@ -7205,16 +6906,16 @@
       </c>
       <c r="B28" s="31" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="C28" s="34" t="inlineStr">
         <is>
-          <t>증권</t>
-        </is>
-      </c>
-      <c r="D28" s="46" t="n">
-        <v>550</v>
+          <t>전기·전자</t>
+        </is>
+      </c>
+      <c r="D28" s="45" t="n">
+        <v>537</v>
       </c>
       <c r="E28" s="30" t="n">
         <v>9</v>
@@ -7230,7 +6931,7 @@
         </is>
       </c>
       <c r="H28" s="61" t="n">
-        <v>-980</v>
+        <v>-716</v>
       </c>
       <c r="J28" s="30" t="n">
         <v>9</v>
@@ -7245,7 +6946,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M28" s="46" t="n">
+      <c r="M28" s="45" t="n">
         <v>653</v>
       </c>
       <c r="N28" s="30" t="n">
@@ -7271,7 +6972,7 @@
       </c>
       <c r="B29" s="31" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>하나마이크론</t>
         </is>
       </c>
       <c r="C29" s="34" t="inlineStr">
@@ -7279,8 +6980,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D29" s="46" t="n">
-        <v>537</v>
+      <c r="D29" s="45" t="n">
+        <v>462</v>
       </c>
       <c r="E29" s="30" t="n">
         <v>10</v>
@@ -7296,7 +6997,7 @@
         </is>
       </c>
       <c r="H29" s="61" t="n">
-        <v>-940</v>
+        <v>-699</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>10</v>
@@ -7311,7 +7012,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M29" s="46" t="n">
+      <c r="M29" s="45" t="n">
         <v>652</v>
       </c>
       <c r="N29" s="30" t="n">
@@ -7472,7 +7173,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D34" s="46" t="n">
+      <c r="D34" s="45" t="n">
         <v>11284</v>
       </c>
       <c r="E34" s="30" t="n">
@@ -7504,7 +7205,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M34" s="46" t="n">
+      <c r="M34" s="45" t="n">
         <v>3403</v>
       </c>
       <c r="N34" s="30" t="n">
@@ -7538,7 +7239,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D35" s="46" t="n">
+      <c r="D35" s="45" t="n">
         <v>840</v>
       </c>
       <c r="E35" s="30" t="n">
@@ -7570,7 +7271,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M35" s="46" t="n">
+      <c r="M35" s="45" t="n">
         <v>1802</v>
       </c>
       <c r="N35" s="30" t="n">
@@ -7604,7 +7305,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D36" s="46" t="n">
+      <c r="D36" s="45" t="n">
         <v>605</v>
       </c>
       <c r="E36" s="30" t="n">
@@ -7636,7 +7337,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M36" s="46" t="n">
+      <c r="M36" s="45" t="n">
         <v>915</v>
       </c>
       <c r="N36" s="30" t="n">
@@ -7670,7 +7371,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D37" s="46" t="n">
+      <c r="D37" s="45" t="n">
         <v>489</v>
       </c>
       <c r="E37" s="30" t="n">
@@ -7702,7 +7403,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M37" s="46" t="n">
+      <c r="M37" s="45" t="n">
         <v>673</v>
       </c>
       <c r="N37" s="30" t="n">
@@ -7736,7 +7437,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D38" s="46" t="n">
+      <c r="D38" s="45" t="n">
         <v>484</v>
       </c>
       <c r="E38" s="30" t="n">
@@ -7768,7 +7469,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M38" s="46" t="n">
+      <c r="M38" s="45" t="n">
         <v>263</v>
       </c>
       <c r="N38" s="30" t="n">
@@ -7802,7 +7503,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D39" s="46" t="n">
+      <c r="D39" s="45" t="n">
         <v>279</v>
       </c>
       <c r="E39" s="30" t="n">
@@ -7834,7 +7535,7 @@
           <t>유통</t>
         </is>
       </c>
-      <c r="M39" s="46" t="n">
+      <c r="M39" s="45" t="n">
         <v>228</v>
       </c>
       <c r="N39" s="30" t="n">
@@ -7868,7 +7569,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D40" s="46" t="n">
+      <c r="D40" s="45" t="n">
         <v>246</v>
       </c>
       <c r="E40" s="30" t="n">
@@ -7900,7 +7601,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="M40" s="46" t="n">
+      <c r="M40" s="45" t="n">
         <v>222</v>
       </c>
       <c r="N40" s="30" t="n">
@@ -7934,7 +7635,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D41" s="46" t="n">
+      <c r="D41" s="45" t="n">
         <v>219</v>
       </c>
       <c r="E41" s="30" t="n">
@@ -7966,7 +7667,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M41" s="46" t="n">
+      <c r="M41" s="45" t="n">
         <v>195</v>
       </c>
       <c r="N41" s="30" t="n">
@@ -8000,7 +7701,7 @@
           <t>운송장비·부품</t>
         </is>
       </c>
-      <c r="D42" s="46" t="n">
+      <c r="D42" s="45" t="n">
         <v>195</v>
       </c>
       <c r="E42" s="30" t="n">
@@ -8032,7 +7733,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M42" s="46" t="n">
+      <c r="M42" s="45" t="n">
         <v>194</v>
       </c>
       <c r="N42" s="30" t="n">
@@ -8066,7 +7767,7 @@
           <t>금속</t>
         </is>
       </c>
-      <c r="D43" s="46" t="n">
+      <c r="D43" s="45" t="n">
         <v>155</v>
       </c>
       <c r="E43" s="30" t="n">
@@ -8098,7 +7799,7 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="M43" s="46" t="n">
+      <c r="M43" s="45" t="n">
         <v>174</v>
       </c>
       <c r="N43" s="30" t="n">
@@ -8259,8 +7960,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D48" s="46" t="n">
-        <v>1893</v>
+      <c r="D48" s="45" t="n">
+        <v>1114</v>
       </c>
       <c r="E48" s="30" t="n">
         <v>1</v>
@@ -8276,7 +7977,7 @@
         </is>
       </c>
       <c r="H48" s="61" t="n">
-        <v>-1120</v>
+        <v>-820</v>
       </c>
       <c r="J48" s="30" t="n">
         <v>1</v>
@@ -8291,7 +7992,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M48" s="46" t="n">
+      <c r="M48" s="45" t="n">
         <v>299</v>
       </c>
       <c r="N48" s="30" t="n">
@@ -8325,8 +8026,8 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D49" s="46" t="n">
-        <v>476</v>
+      <c r="D49" s="45" t="n">
+        <v>405</v>
       </c>
       <c r="E49" s="30" t="n">
         <v>2</v>
@@ -8342,7 +8043,7 @@
         </is>
       </c>
       <c r="H49" s="61" t="n">
-        <v>-650</v>
+        <v>-519</v>
       </c>
       <c r="J49" s="30" t="n">
         <v>2</v>
@@ -8357,7 +8058,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="M49" s="46" t="n">
+      <c r="M49" s="45" t="n">
         <v>110</v>
       </c>
       <c r="N49" s="30" t="n">
@@ -8391,8 +8092,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D50" s="46" t="n">
-        <v>459</v>
+      <c r="D50" s="45" t="n">
+        <v>384</v>
       </c>
       <c r="E50" s="30" t="n">
         <v>3</v>
@@ -8408,7 +8109,7 @@
         </is>
       </c>
       <c r="H50" s="61" t="n">
-        <v>-483</v>
+        <v>-400</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>3</v>
@@ -8423,7 +8124,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M50" s="46" t="n">
+      <c r="M50" s="45" t="n">
         <v>38</v>
       </c>
       <c r="N50" s="30" t="n">
@@ -8457,7 +8158,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D51" s="46" t="n">
+      <c r="D51" s="45" t="n">
         <v>358</v>
       </c>
       <c r="E51" s="30" t="n">
@@ -8465,16 +8166,16 @@
       </c>
       <c r="F51" s="31" t="inlineStr">
         <is>
-          <t>POSCO홀딩스</t>
+          <t>SK하이닉스</t>
         </is>
       </c>
       <c r="G51" s="34" t="inlineStr">
         <is>
-          <t>금속</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H51" s="61" t="n">
-        <v>-330</v>
+        <v>-327</v>
       </c>
       <c r="J51" s="30" t="n">
         <v>4</v>
@@ -8489,7 +8190,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M51" s="46" t="n">
+      <c r="M51" s="45" t="n">
         <v>32</v>
       </c>
       <c r="N51" s="30" t="n">
@@ -8523,8 +8224,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D52" s="46" t="n">
-        <v>318</v>
+      <c r="D52" s="45" t="n">
+        <v>308</v>
       </c>
       <c r="E52" s="30" t="n">
         <v>5</v>
@@ -8540,7 +8241,7 @@
         </is>
       </c>
       <c r="H52" s="61" t="n">
-        <v>-299</v>
+        <v>-277</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>5</v>
@@ -8555,7 +8256,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M52" s="46" t="n">
+      <c r="M52" s="45" t="n">
         <v>31</v>
       </c>
       <c r="N52" s="30" t="n">
@@ -8589,24 +8290,24 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="D53" s="46" t="n">
-        <v>284</v>
+      <c r="D53" s="45" t="n">
+        <v>254</v>
       </c>
       <c r="E53" s="30" t="n">
         <v>6</v>
       </c>
       <c r="F53" s="31" t="inlineStr">
         <is>
-          <t>LG에너지솔루션</t>
+          <t>POSCO홀딩스</t>
         </is>
       </c>
       <c r="G53" s="34" t="inlineStr">
         <is>
-          <t>전기·전자</t>
+          <t>금속</t>
         </is>
       </c>
       <c r="H53" s="61" t="n">
-        <v>-270</v>
+        <v>-255</v>
       </c>
       <c r="J53" s="30" t="n">
         <v>6</v>
@@ -8621,7 +8322,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M53" s="46" t="n">
+      <c r="M53" s="45" t="n">
         <v>30</v>
       </c>
       <c r="N53" s="30" t="n">
@@ -8647,7 +8348,7 @@
       </c>
       <c r="B54" s="31" t="inlineStr">
         <is>
-          <t>대덕전자</t>
+          <t>한화시스템</t>
         </is>
       </c>
       <c r="C54" s="34" t="inlineStr">
@@ -8655,8 +8356,8 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D54" s="46" t="n">
-        <v>212</v>
+      <c r="D54" s="45" t="n">
+        <v>197</v>
       </c>
       <c r="E54" s="30" t="n">
         <v>7</v>
@@ -8672,7 +8373,7 @@
         </is>
       </c>
       <c r="H54" s="61" t="n">
-        <v>-267</v>
+        <v>-255</v>
       </c>
       <c r="J54" s="30" t="n">
         <v>7</v>
@@ -8687,7 +8388,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M54" s="46" t="n">
+      <c r="M54" s="45" t="n">
         <v>30</v>
       </c>
       <c r="N54" s="30" t="n">
@@ -8713,7 +8414,7 @@
       </c>
       <c r="B55" s="31" t="inlineStr">
         <is>
-          <t>한화시스템</t>
+          <t>대덕전자</t>
         </is>
       </c>
       <c r="C55" s="34" t="inlineStr">
@@ -8721,15 +8422,15 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D55" s="46" t="n">
-        <v>211</v>
+      <c r="D55" s="45" t="n">
+        <v>184</v>
       </c>
       <c r="E55" s="30" t="n">
         <v>8</v>
       </c>
       <c r="F55" s="31" t="inlineStr">
         <is>
-          <t>삼성SDI</t>
+          <t>LG에너지솔루션</t>
         </is>
       </c>
       <c r="G55" s="34" t="inlineStr">
@@ -8738,7 +8439,7 @@
         </is>
       </c>
       <c r="H55" s="61" t="n">
-        <v>-266</v>
+        <v>-246</v>
       </c>
       <c r="J55" s="30" t="n">
         <v>8</v>
@@ -8753,7 +8454,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="M55" s="46" t="n">
+      <c r="M55" s="45" t="n">
         <v>30</v>
       </c>
       <c r="N55" s="30" t="n">
@@ -8779,16 +8480,16 @@
       </c>
       <c r="B56" s="31" t="inlineStr">
         <is>
-          <t>삼성증권</t>
+          <t>S-Oil</t>
         </is>
       </c>
       <c r="C56" s="34" t="inlineStr">
         <is>
-          <t>증권</t>
-        </is>
-      </c>
-      <c r="D56" s="46" t="n">
-        <v>127</v>
+          <t>화학</t>
+        </is>
+      </c>
+      <c r="D56" s="45" t="n">
+        <v>104</v>
       </c>
       <c r="E56" s="30" t="n">
         <v>9</v>
@@ -8804,7 +8505,7 @@
         </is>
       </c>
       <c r="H56" s="61" t="n">
-        <v>-215</v>
+        <v>-207</v>
       </c>
       <c r="J56" s="30" t="n">
         <v>9</v>
@@ -8819,7 +8520,7 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="M56" s="46" t="n">
+      <c r="M56" s="45" t="n">
         <v>29</v>
       </c>
       <c r="N56" s="30" t="n">
@@ -8845,32 +8546,32 @@
       </c>
       <c r="B57" s="31" t="inlineStr">
         <is>
-          <t>S-Oil</t>
+          <t>삼성증권</t>
         </is>
       </c>
       <c r="C57" s="34" t="inlineStr">
         <is>
-          <t>화학</t>
-        </is>
-      </c>
-      <c r="D57" s="46" t="n">
-        <v>113</v>
+          <t>증권</t>
+        </is>
+      </c>
+      <c r="D57" s="45" t="n">
+        <v>102</v>
       </c>
       <c r="E57" s="30" t="n">
         <v>10</v>
       </c>
       <c r="F57" s="31" t="inlineStr">
         <is>
-          <t>두산에너빌리티</t>
+          <t>삼성SDI</t>
         </is>
       </c>
       <c r="G57" s="34" t="inlineStr">
         <is>
-          <t>기계·장비</t>
+          <t>전기·전자</t>
         </is>
       </c>
       <c r="H57" s="61" t="n">
-        <v>-200</v>
+        <v>-188</v>
       </c>
       <c r="J57" s="30" t="n">
         <v>10</v>
@@ -8885,7 +8586,7 @@
           <t>운송·창고</t>
         </is>
       </c>
-      <c r="M57" s="46" t="n">
+      <c r="M57" s="45" t="n">
         <v>28</v>
       </c>
       <c r="N57" s="30" t="n">
@@ -8986,7 +8687,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D62" s="46" t="n">
+      <c r="D62" s="45" t="n">
         <v>33778</v>
       </c>
       <c r="E62" s="30" t="n">
@@ -9020,7 +8721,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D63" s="46" t="n">
+      <c r="D63" s="45" t="n">
         <v>15217</v>
       </c>
       <c r="E63" s="30" t="n">
@@ -9054,7 +8755,7 @@
           <t>음식료·담배</t>
         </is>
       </c>
-      <c r="D64" s="46" t="n">
+      <c r="D64" s="45" t="n">
         <v>78</v>
       </c>
       <c r="E64" s="30" t="n">
@@ -9088,7 +8789,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="D65" s="46" t="n">
+      <c r="D65" s="45" t="n">
         <v>48</v>
       </c>
       <c r="E65" s="30" t="n">
@@ -9122,7 +8823,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D66" s="46" t="n">
+      <c r="D66" s="45" t="n">
         <v>47</v>
       </c>
       <c r="E66" s="30" t="n">
@@ -9156,7 +8857,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D67" s="46" t="n">
+      <c r="D67" s="45" t="n">
         <v>45</v>
       </c>
       <c r="E67" s="30" t="n">
@@ -9190,7 +8891,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D68" s="46" t="n">
+      <c r="D68" s="45" t="n">
         <v>32</v>
       </c>
       <c r="E68" s="30" t="n">
@@ -9224,7 +8925,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="D69" s="46" t="n">
+      <c r="D69" s="45" t="n">
         <v>30</v>
       </c>
       <c r="E69" s="30" t="n">
@@ -9258,7 +8959,7 @@
           <t>일반서비스</t>
         </is>
       </c>
-      <c r="D70" s="46" t="n">
+      <c r="D70" s="45" t="n">
         <v>29</v>
       </c>
       <c r="E70" s="30" t="n">
@@ -9292,7 +8993,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="D71" s="46" t="n">
+      <c r="D71" s="45" t="n">
         <v>27</v>
       </c>
       <c r="E71" s="30" t="n">
@@ -9409,7 +9110,7 @@
       </c>
       <c r="Q1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21 ~ 2026-09-24</t>
+          <t>2026-09-21 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -9551,7 +9252,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J5" s="46" t="n">
+      <c r="J5" s="45" t="n">
         <v>6734.3</v>
       </c>
       <c r="K5" s="65" t="n">
@@ -9616,7 +9317,7 @@
           <t>기타금융</t>
         </is>
       </c>
-      <c r="J6" s="46" t="n">
+      <c r="J6" s="45" t="n">
         <v>3512.1</v>
       </c>
       <c r="K6" s="65" t="n">
@@ -9681,7 +9382,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J7" s="46" t="n">
+      <c r="J7" s="45" t="n">
         <v>2854.7</v>
       </c>
       <c r="K7" s="65" t="n">
@@ -9742,7 +9443,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J8" s="46" t="n">
+      <c r="J8" s="45" t="n">
         <v>2396.1</v>
       </c>
       <c r="K8" s="65" t="n">
@@ -9807,7 +9508,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J9" s="46" t="n">
+      <c r="J9" s="45" t="n">
         <v>1727</v>
       </c>
       <c r="K9" s="65" t="n">
@@ -9868,7 +9569,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J10" s="46" t="n">
+      <c r="J10" s="45" t="n">
         <v>1580.7</v>
       </c>
       <c r="K10" s="65" t="n">
@@ -9933,7 +9634,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J11" s="46" t="n">
+      <c r="J11" s="45" t="n">
         <v>1288.2</v>
       </c>
       <c r="K11" s="65" t="n">
@@ -9998,7 +9699,7 @@
           <t>기계·장비</t>
         </is>
       </c>
-      <c r="J12" s="46" t="n">
+      <c r="J12" s="45" t="n">
         <v>733.3</v>
       </c>
       <c r="K12" s="65" t="n">
@@ -10063,7 +9764,7 @@
           <t>전기·전자</t>
         </is>
       </c>
-      <c r="J13" s="46" t="n">
+      <c r="J13" s="45" t="n">
         <v>721.7</v>
       </c>
       <c r="K13" s="65" t="n">
@@ -10124,7 +9825,7 @@
         </is>
       </c>
       <c r="I14" s="34" t="inlineStr"/>
-      <c r="J14" s="46" t="n">
+      <c r="J14" s="45" t="n">
         <v>716.2</v>
       </c>
       <c r="K14" s="65" t="n">
@@ -10216,7 +9917,7 @@
       </c>
       <c r="L1" s="25" t="inlineStr">
         <is>
-          <t>2026-09-21 ~ 2026-09-24</t>
+          <t>2026-09-21 ~ 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -11551,7 +11252,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{2984B989-8769-4A12-B6C8-62BECDB24C1C}</x14:id>
+          <x14:id>{9DA787CD-8A5E-4F13-8D53-539D4FE166AF}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11565,7 +11266,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{EC2E9FD6-422A-4147-9285-FAA305F2659B}</x14:id>
+          <x14:id>{B4B60FBA-AA05-4E50-9168-9EC719FAD6E7}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11579,7 +11280,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{A92D1540-EC35-4EA8-9400-D685C9DB7F52}</x14:id>
+          <x14:id>{0D036BDC-A79A-4A0C-96A1-3BC607F585D6}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11593,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{C73105BF-B99A-4BAD-8FA6-C787E5616F87}</x14:id>
+          <x14:id>{D42676F0-B450-4A68-A5EA-A761A52DBE84}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11603,7 +11304,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{2984B989-8769-4A12-B6C8-62BECDB24C1C}">
+          <x14:cfRule type="dataBar" id="{9DA787CD-8A5E-4F13-8D53-539D4FE166AF}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11616,7 +11317,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{EC2E9FD6-422A-4147-9285-FAA305F2659B}">
+          <x14:cfRule type="dataBar" id="{B4B60FBA-AA05-4E50-9168-9EC719FAD6E7}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11629,7 +11330,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{A92D1540-EC35-4EA8-9400-D685C9DB7F52}">
+          <x14:cfRule type="dataBar" id="{0D036BDC-A79A-4A0C-96A1-3BC607F585D6}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11642,7 +11343,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{C73105BF-B99A-4BAD-8FA6-C787E5616F87}">
+          <x14:cfRule type="dataBar" id="{D42676F0-B450-4A68-A5EA-A761A52DBE84}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>

--- a/public/reports/weekly_briefing/2026-09-21.xlsx
+++ b/public/reports/weekly_briefing/2026-09-21.xlsx
@@ -1028,7 +1028,7 @@
       <c r="G6" s="3" t="inlineStr"/>
       <c r="H6" s="18" t="inlineStr">
         <is>
-          <t>미국 종가 기준 09/18 → 09/23, %</t>
+          <t>미국 종가 기준 09/18 → 09/25, %</t>
         </is>
       </c>
       <c r="I6" s="18" t="inlineStr"/>
@@ -1098,19 +1098,19 @@
         <v>16901</v>
       </c>
       <c r="E8" s="29" t="n">
-        <v>0.73</v>
-      </c>
-      <c r="F8" s="28" t="n">
-        <v>-0.33</v>
+        <v>1.21</v>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>0.28</v>
       </c>
       <c r="G8" s="29" t="n">
-        <v>1.56</v>
+        <v>2.06</v>
       </c>
       <c r="H8" s="29" t="n">
-        <v>6.68</v>
+        <v>0.41</v>
       </c>
       <c r="I8" s="29" t="n">
-        <v>5.14</v>
+        <v>6.27</v>
       </c>
     </row>
     <row r="9">
@@ -1169,7 +1169,7 @@
         </is>
       </c>
       <c r="D12" s="32" t="n">
-        <v>4.96</v>
+        <v>5.86</v>
       </c>
     </row>
     <row r="13">
@@ -1189,7 +1189,7 @@
         </is>
       </c>
       <c r="D13" s="32" t="n">
-        <v>3.15</v>
+        <v>3.64</v>
       </c>
     </row>
     <row r="14">
@@ -1205,11 +1205,11 @@
       </c>
       <c r="C14" s="31" t="inlineStr">
         <is>
-          <t>소재</t>
+          <t>헬스케어</t>
         </is>
       </c>
       <c r="D14" s="32" t="n">
-        <v>1.04</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="15">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="D15" s="33" t="n">
-        <v>-2.44</v>
+        <v>-2.96</v>
       </c>
     </row>
     <row r="16">
@@ -1249,7 +1249,7 @@
         </is>
       </c>
       <c r="D16" s="33" t="n">
-        <v>-2.02</v>
+        <v>-1.48</v>
       </c>
     </row>
     <row r="17">
@@ -1269,7 +1269,7 @@
         </is>
       </c>
       <c r="D17" s="33" t="n">
-        <v>-0.97</v>
+        <v>-1.08</v>
       </c>
     </row>
     <row r="18">
@@ -11252,7 +11252,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{9DA787CD-8A5E-4F13-8D53-539D4FE166AF}</x14:id>
+          <x14:id>{3F13C55D-0746-4EC0-8B69-BBDC340D7B12}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11266,7 +11266,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{B4B60FBA-AA05-4E50-9168-9EC719FAD6E7}</x14:id>
+          <x14:id>{4896E0A4-6A93-4372-B48D-565D1EA8ACAB}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11280,7 +11280,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{0D036BDC-A79A-4A0C-96A1-3BC607F585D6}</x14:id>
+          <x14:id>{75A179DD-CD7C-467D-BFEC-3EB09BAEC858}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11294,7 +11294,7 @@
       </dataBar>
       <extLst>
         <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{B025F937-C7B1-47D3-B67F-A62EFF666E3E}">
-          <x14:id>{D42676F0-B450-4A68-A5EA-A761A52DBE84}</x14:id>
+          <x14:id>{9797D8CE-C476-481A-88E1-78D483D0FE4B}</x14:id>
         </ext>
       </extLst>
     </cfRule>
@@ -11304,7 +11304,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{9DA787CD-8A5E-4F13-8D53-539D4FE166AF}">
+          <x14:cfRule type="dataBar" id="{3F13C55D-0746-4EC0-8B69-BBDC340D7B12}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11317,7 +11317,7 @@
           <xm:sqref>B5:B28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{B4B60FBA-AA05-4E50-9168-9EC719FAD6E7}">
+          <x14:cfRule type="dataBar" id="{4896E0A4-6A93-4372-B48D-565D1EA8ACAB}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11330,7 +11330,7 @@
           <xm:sqref>C5:C28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{0D036BDC-A79A-4A0C-96A1-3BC607F585D6}">
+          <x14:cfRule type="dataBar" id="{75A179DD-CD7C-467D-BFEC-3EB09BAEC858}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
@@ -11343,7 +11343,7 @@
           <xm:sqref>D5:D28</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" id="{D42676F0-B450-4A68-A5EA-A761A52DBE84}">
+          <x14:cfRule type="dataBar" id="{9797D8CE-C476-481A-88E1-78D483D0FE4B}">
             <x14:dataBar minLength="0" maxLength="100" border="1" axisPosition="automatic" negativeBarColorSameAsPositive="0" negativeBarBorderColorSameAsPositive="0">
               <x14:cfvo type="autoMin"/>
               <x14:cfvo type="autoMax"/>
